--- a/백업_기준가격.xlsx
+++ b/백업_기준가격.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\hotel-code\hotel-cmscontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DA973F-C9B0-4BE7-87B4-AAB5D2D43760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2859FA-C28F-4AAC-8768-42007C4602B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1724,6 +1724,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{94A4766E-0561-4D48-A781-E2572C4ABDF3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/22 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0" xr:uid="{8A3AB455-14B2-4FED-AF79-843444B0E8D1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/22 13&gt;14</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F36" authorId="0" shapeId="0" xr:uid="{A0A4DBFC-6470-4977-91E7-EA2A31353232}">
       <text>
         <r>
@@ -1911,6 +1959,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{70BD7A20-F0B4-42FA-8585-43E29020C9CA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/22 12&gt;14</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F39" authorId="0" shapeId="0" xr:uid="{7F9179A8-6EAB-419C-8D01-E0FCBBFBC6F4}">
       <text>
         <r>
@@ -1973,6 +2045,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="B40" authorId="0" shapeId="0" xr:uid="{4C63E04C-FAC7-4458-8608-09A62D295469}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/22 12&gt;14</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F40" authorId="0" shapeId="0" xr:uid="{CB792A16-A7AC-47CC-9C18-B782E03A82E4}">
       <text>
         <r>
@@ -3115,7 +3211,8 @@
           </rPr>
           <t xml:space="preserve">
 1/15 13&gt;15
-1/17 15&gt;16</t>
+1/17 15&gt;16
+1/22 16&gt;17</t>
         </r>
       </text>
     </comment>
@@ -3182,7 +3279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{969C3D25-DFE2-4E79-B8C6-46B8CF73AF84}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{D6BD911A-CA66-4B94-8976-6C20CCFED429}">
       <text>
         <r>
           <rPr>
@@ -3203,7 +3300,8 @@
           </rPr>
           <t xml:space="preserve">
 1/15 13&gt;15
-1/17 15&gt;16</t>
+1/17 15&gt;16
+1/22 16&gt;17</t>
         </r>
       </text>
     </comment>
@@ -3270,6 +3368,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="B54" authorId="0" shapeId="0" xr:uid="{BCFE29B3-12FB-4ED2-A1A2-282F4A08DCC8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/22 14&gt;!7</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C54" authorId="0" shapeId="0" xr:uid="{164E1845-CA7E-4D67-B698-344577FE2758}">
       <text>
         <r>
@@ -3482,7 +3604,8 @@
           </rPr>
           <t xml:space="preserve">
 1/15 13&gt;15
-1/17 15&gt;16</t>
+1/17 15&gt;16
+1/22 16&gt;17</t>
         </r>
       </text>
     </comment>
@@ -3778,6 +3901,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{6EDE9B6E-C7D8-4B86-9384-ACB42B1A942D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/12 25&gt;38
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B62" authorId="0" shapeId="0" xr:uid="{8B36548D-29FA-4068-8933-43A9AF4FC0D5}">
       <text>
         <r>
@@ -3836,7 +3984,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 160,000 &gt; 170,000</t>
+          <t xml:space="preserve"> 160,000 &gt; 170,000
+1/22 17&gt;18</t>
         </r>
       </text>
     </comment>
@@ -7159,6 +7308,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{787EE105-3924-41C1-8519-9BC174333CD2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/23 20&gt;30</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D105" authorId="0" shapeId="0" xr:uid="{3C9422D7-18AF-4691-8E06-89554C26F849}">
       <text>
         <r>
@@ -7284,7 +7457,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0" xr:uid="{F610258F-98DF-43AE-949A-6AC365A7758F}">
+    <comment ref="F105" authorId="0" shapeId="0" xr:uid="{4559D9A2-C02A-4488-8099-1D34D91D9E38}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/23 21&gt;30</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0" xr:uid="{7C9D32B0-AEAD-4AA5-9635-6F6ECB1571BB}">
       <text>
         <r>
           <rPr>
@@ -7295,6 +7492,21 @@
             <scheme val="minor"/>
           </rPr>
           <t>HP:
+1월 14일 120,000 &gt; 160,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C106" authorId="0" shapeId="0" xr:uid="{F610258F-98DF-43AE-949A-6AC365A7758F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
 1월 14일 150,000 &gt; 170,000</t>
         </r>
       </text>
@@ -8000,6 +8212,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="D111" authorId="0" shapeId="0" xr:uid="{F56A8742-2580-4724-843D-1BA65E7C8315}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/123 20&gt;24</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E111" authorId="0" shapeId="0" xr:uid="{9DB7A357-9319-4EBA-83B7-3D19AE4579BC}">
       <text>
         <r>
@@ -8062,6 +8298,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="F111" authorId="0" shapeId="0" xr:uid="{8BEDF578-995B-4F68-B65B-879BCB5C43B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/23 22&gt;30</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D112" authorId="0" shapeId="0" xr:uid="{5E3E3CEC-3F9E-42C7-92DB-E0C9C2C75F3E}">
       <text>
         <r>
@@ -8183,7 +8443,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 200,000 &gt; 25
-0,000</t>
+0,000
+1/23 25&gt;26</t>
         </r>
       </text>
     </comment>
@@ -9098,7 +9359,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 150,000 &gt; 170,000</t>
+          <t xml:space="preserve"> 150,000 &gt; 170,000
+1/23 15&gt;18</t>
         </r>
       </text>
     </comment>
@@ -37840,7 +38102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -37856,9 +38118,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -39059,9 +39318,9 @@
         <v>41</v>
       </c>
       <c r="B35" s="4">
-        <v>140000</v>
-      </c>
-      <c r="C35" s="4">
+        <v>150000</v>
+      </c>
+      <c r="C35" s="7">
         <v>150000</v>
       </c>
       <c r="D35" s="4">
@@ -39073,7 +39332,7 @@
       <c r="F35" s="4">
         <v>360000</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="7">
         <v>550000</v>
       </c>
       <c r="H35" s="4">
@@ -39085,9 +39344,9 @@
         <v>42</v>
       </c>
       <c r="B36" s="2">
-        <v>130000</v>
-      </c>
-      <c r="C36" s="2">
+        <v>140000</v>
+      </c>
+      <c r="C36" s="6">
         <v>130000</v>
       </c>
       <c r="D36" s="2">
@@ -39163,9 +39422,9 @@
         <v>45</v>
       </c>
       <c r="B39" s="2">
-        <v>120000</v>
-      </c>
-      <c r="C39" s="2">
+        <v>140000</v>
+      </c>
+      <c r="C39" s="6">
         <v>140000</v>
       </c>
       <c r="D39" s="2">
@@ -39177,7 +39436,7 @@
       <c r="F39" s="2">
         <v>160000</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="6">
         <v>400000</v>
       </c>
       <c r="H39" s="2">
@@ -39189,9 +39448,9 @@
         <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>120000</v>
-      </c>
-      <c r="C40" s="2">
+        <v>140000</v>
+      </c>
+      <c r="C40" s="6">
         <v>130000</v>
       </c>
       <c r="D40" s="2">
@@ -39203,7 +39462,7 @@
       <c r="F40" s="2">
         <v>160000</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="6">
         <v>400000</v>
       </c>
       <c r="H40" s="2">
@@ -39217,7 +39476,7 @@
       <c r="B41" s="4">
         <v>170000</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="7">
         <v>150000</v>
       </c>
       <c r="D41" s="4">
@@ -39376,7 +39635,7 @@
       <c r="C47" s="2">
         <v>170000</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="6">
         <v>210000</v>
       </c>
       <c r="E47" s="2">
@@ -39422,10 +39681,10 @@
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="7">
         <v>180000</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="7">
         <v>190000</v>
       </c>
       <c r="D49" s="4">
@@ -39501,7 +39760,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="2">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="C52" s="2">
         <v>170000</v>
@@ -39527,7 +39786,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="2">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="C53" s="2">
         <v>170000</v>
@@ -39545,17 +39804,17 @@
         <v>450000</v>
       </c>
       <c r="H53" s="2">
-        <v>500000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="6">
-        <v>140000</v>
-      </c>
-      <c r="C54" s="2">
+      <c r="B54" s="2">
+        <v>170000</v>
+      </c>
+      <c r="C54" s="6">
         <v>170000</v>
       </c>
       <c r="D54" s="2">
@@ -39587,7 +39846,7 @@
       <c r="D55" s="7">
         <v>210000</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="7">
         <v>270000</v>
       </c>
       <c r="F55" s="4">
@@ -39610,13 +39869,13 @@
       <c r="C56" s="7">
         <v>160000</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="7">
         <v>240000</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="7">
         <v>270000</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="7">
         <v>380000</v>
       </c>
       <c r="G56" s="7">
@@ -39631,7 +39890,7 @@
         <v>63</v>
       </c>
       <c r="B57" s="2">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="C57" s="6">
         <v>140000</v>
@@ -39747,7 +40006,7 @@
         <v>230000</v>
       </c>
       <c r="F61" s="2">
-        <v>250000</v>
+        <v>380000</v>
       </c>
       <c r="G61" s="2">
         <v>450000</v>
@@ -39761,7 +40020,7 @@
         <v>68</v>
       </c>
       <c r="B62" s="4">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="C62" s="4">
         <v>180000</v>
@@ -39887,7 +40146,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="10" t="s">
+      <c r="A67" t="s">
         <v>73</v>
       </c>
       <c r="B67" s="2">
@@ -39948,7 +40207,7 @@
       <c r="C69" s="7">
         <v>160000</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="7">
         <v>240000</v>
       </c>
       <c r="E69" s="7">
@@ -40153,7 +40412,7 @@
       <c r="B77" s="7">
         <v>150000</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="4">
         <v>160000</v>
       </c>
       <c r="D77" s="4">
@@ -40179,7 +40438,7 @@
       <c r="B78" s="6">
         <v>160000</v>
       </c>
-      <c r="C78" s="13">
+      <c r="C78" s="2">
         <v>140000</v>
       </c>
       <c r="D78" s="2">
@@ -40205,7 +40464,7 @@
       <c r="B79" s="6">
         <v>160000</v>
       </c>
-      <c r="C79" s="13">
+      <c r="C79" s="2">
         <v>180000</v>
       </c>
       <c r="D79" s="2">
@@ -40277,7 +40536,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="14" t="s">
+      <c r="A82" t="s">
         <v>88</v>
       </c>
       <c r="B82" s="2">
@@ -40865,7 +41124,7 @@
         <v>260000</v>
       </c>
       <c r="F104" s="4">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="G104" s="4">
         <v>650000</v>
@@ -40878,8 +41137,8 @@
       <c r="A105" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B105" s="7">
-        <v>150000</v>
+      <c r="B105" s="12">
+        <v>180000</v>
       </c>
       <c r="C105" s="7">
         <v>160000</v>
@@ -40891,7 +41150,7 @@
         <v>260000</v>
       </c>
       <c r="F105" s="4">
-        <v>210000</v>
+        <v>300000</v>
       </c>
       <c r="G105" s="4">
         <v>700000</v>
@@ -40904,8 +41163,8 @@
       <c r="A106" t="s">
         <v>112</v>
       </c>
-      <c r="B106" s="6">
-        <v>120000</v>
+      <c r="B106" s="2">
+        <v>160000</v>
       </c>
       <c r="C106" s="2">
         <v>170000</v>
@@ -41041,13 +41300,13 @@
         <v>170000</v>
       </c>
       <c r="D111" s="4">
-        <v>200000</v>
-      </c>
-      <c r="E111" s="4">
+        <v>240000</v>
+      </c>
+      <c r="E111" s="7">
         <v>250000</v>
       </c>
       <c r="F111" s="4">
-        <v>220000</v>
+        <v>300000</v>
       </c>
       <c r="G111" s="4">
         <v>650000</v>
@@ -41070,7 +41329,7 @@
         <v>240000</v>
       </c>
       <c r="E112" s="4">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="F112" s="4">
         <v>300000</v>
@@ -41217,7 +41476,7 @@
         <v>124</v>
       </c>
       <c r="B118" s="4">
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="C118" s="4">
         <v>190000</v>
@@ -41863,7 +42122,7 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="14" t="s">
+      <c r="A143" t="s">
         <v>149</v>
       </c>
       <c r="B143" s="2">
@@ -41889,7 +42148,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="14" t="s">
+      <c r="A144" t="s">
         <v>150</v>
       </c>
       <c r="B144" s="2">
@@ -41915,7 +42174,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="14" t="s">
+      <c r="A145" t="s">
         <v>151</v>
       </c>
       <c r="B145" s="2">
@@ -41941,7 +42200,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="15" t="s">
+      <c r="A146" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B146" s="4">
@@ -41967,7 +42226,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="15" t="s">
+      <c r="A147" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B147" s="4">
@@ -41993,7 +42252,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="14" t="s">
+      <c r="A148" t="s">
         <v>154</v>
       </c>
       <c r="B148" s="2">
@@ -42019,7 +42278,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="14" t="s">
+      <c r="A149" t="s">
         <v>155</v>
       </c>
       <c r="B149" s="2">
@@ -42045,7 +42304,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="14" t="s">
+      <c r="A150" t="s">
         <v>156</v>
       </c>
       <c r="B150" s="2">
@@ -42071,7 +42330,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="14" t="s">
+      <c r="A151" t="s">
         <v>157</v>
       </c>
       <c r="B151" s="2">
@@ -42097,7 +42356,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="14" t="s">
+      <c r="A152" t="s">
         <v>158</v>
       </c>
       <c r="B152" s="2">
@@ -42123,7 +42382,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="15" t="s">
+      <c r="A153" s="3" t="s">
         <v>159</v>
       </c>
       <c r="B153" s="4">
@@ -42149,7 +42408,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="15" t="s">
+      <c r="A154" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B154" s="4">
@@ -42175,7 +42434,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="14" t="s">
+      <c r="A155" t="s">
         <v>161</v>
       </c>
       <c r="B155" s="2">
@@ -42201,7 +42460,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="14" t="s">
+      <c r="A156" t="s">
         <v>162</v>
       </c>
       <c r="B156" s="2">
@@ -42227,7 +42486,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="14" t="s">
+      <c r="A157" t="s">
         <v>163</v>
       </c>
       <c r="B157" s="2">
@@ -42253,7 +42512,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="14" t="s">
+      <c r="A158" t="s">
         <v>164</v>
       </c>
       <c r="B158" s="2">
@@ -42279,7 +42538,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="14" t="s">
+      <c r="A159" t="s">
         <v>165</v>
       </c>
       <c r="B159" s="2">
@@ -42305,7 +42564,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B160" s="4">
@@ -42331,7 +42590,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="15" t="s">
+      <c r="A161" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B161" s="4">
@@ -42357,7 +42616,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="14" t="s">
+      <c r="A162" t="s">
         <v>168</v>
       </c>
       <c r="B162" s="2">
@@ -42383,7 +42642,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="14" t="s">
+      <c r="A163" t="s">
         <v>169</v>
       </c>
       <c r="B163" s="2">
@@ -44541,7 +44800,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A246" s="14" t="s">
+      <c r="A246" t="s">
         <v>252</v>
       </c>
       <c r="B246" s="2">
@@ -44567,7 +44826,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A247" s="14" t="s">
+      <c r="A247" t="s">
         <v>253</v>
       </c>
       <c r="B247" s="2">
@@ -44593,7 +44852,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A248" s="14" t="s">
+      <c r="A248" t="s">
         <v>254</v>
       </c>
       <c r="B248" s="2">
@@ -44619,7 +44878,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" s="14" t="s">
+      <c r="A249" t="s">
         <v>255</v>
       </c>
       <c r="B249" s="2">
@@ -44645,7 +44904,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" s="14" t="s">
+      <c r="A250" t="s">
         <v>256</v>
       </c>
       <c r="B250" s="2">
@@ -44671,7 +44930,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="15" t="s">
+      <c r="A251" s="3" t="s">
         <v>257</v>
       </c>
       <c r="B251" s="4">
@@ -44697,7 +44956,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="15" t="s">
+      <c r="A252" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B252" s="4">
@@ -44723,7 +44982,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="14" t="s">
+      <c r="A253" t="s">
         <v>259</v>
       </c>
       <c r="B253" s="2">
@@ -44749,7 +45008,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="14" t="s">
+      <c r="A254" t="s">
         <v>260</v>
       </c>
       <c r="B254" s="2">
@@ -44775,7 +45034,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" s="14" t="s">
+      <c r="A255" t="s">
         <v>261</v>
       </c>
       <c r="B255" s="2">
@@ -44801,7 +45060,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A256" s="14" t="s">
+      <c r="A256" t="s">
         <v>262</v>
       </c>
       <c r="B256" s="2">
@@ -44827,7 +45086,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="14" t="s">
+      <c r="A257" t="s">
         <v>263</v>
       </c>
       <c r="B257" s="2">
@@ -44853,7 +45112,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="15" t="s">
+      <c r="A258" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B258" s="4">
@@ -44879,7 +45138,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="15" t="s">
+      <c r="A259" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B259" s="4">
@@ -44905,7 +45164,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A260" s="14" t="s">
+      <c r="A260" t="s">
         <v>266</v>
       </c>
       <c r="B260" s="2">
@@ -44931,7 +45190,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="14" t="s">
+      <c r="A261" t="s">
         <v>267</v>
       </c>
       <c r="B261" s="2">
@@ -44957,7 +45216,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" s="14" t="s">
+      <c r="A262" t="s">
         <v>268</v>
       </c>
       <c r="B262" s="2">
@@ -44983,7 +45242,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" s="14" t="s">
+      <c r="A263" t="s">
         <v>269</v>
       </c>
       <c r="B263" s="2">
@@ -45009,7 +45268,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="14" t="s">
+      <c r="A264" t="s">
         <v>270</v>
       </c>
       <c r="B264" s="2">
@@ -45035,7 +45294,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="15" t="s">
+      <c r="A265" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B265" s="4">
@@ -45061,7 +45320,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="15" t="s">
+      <c r="A266" s="3" t="s">
         <v>272</v>
       </c>
       <c r="B266" s="4">
@@ -45087,7 +45346,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" s="14" t="s">
+      <c r="A267" t="s">
         <v>273</v>
       </c>
       <c r="B267" s="2">
@@ -45113,7 +45372,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="14" t="s">
+      <c r="A268" t="s">
         <v>274</v>
       </c>
       <c r="B268" s="2">
@@ -45139,7 +45398,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="14" t="s">
+      <c r="A269" t="s">
         <v>275</v>
       </c>
       <c r="B269" s="2">
@@ -45165,7 +45424,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="14" t="s">
+      <c r="A270" t="s">
         <v>276</v>
       </c>
       <c r="B270" s="2">
@@ -45191,7 +45450,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A271" s="14" t="s">
+      <c r="A271" t="s">
         <v>277</v>
       </c>
       <c r="B271" s="2">
@@ -45217,7 +45476,7 @@
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A272" s="15" t="s">
+      <c r="A272" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B272" s="4">
@@ -45243,7 +45502,7 @@
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A273" s="15" t="s">
+      <c r="A273" s="3" t="s">
         <v>279</v>
       </c>
       <c r="B273" s="4">
@@ -45269,7 +45528,7 @@
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A274" s="14" t="s">
+      <c r="A274" t="s">
         <v>280</v>
       </c>
       <c r="B274" s="2">
@@ -45295,7 +45554,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A275" s="14" t="s">
+      <c r="A275" t="s">
         <v>281</v>
       </c>
       <c r="B275" s="2">
@@ -45321,7 +45580,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A276" s="14" t="s">
+      <c r="A276" t="s">
         <v>282</v>
       </c>
       <c r="B276" s="2">
@@ -45347,7 +45606,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A277" s="14" t="s">
+      <c r="A277" t="s">
         <v>283</v>
       </c>
       <c r="B277" s="2">
@@ -45373,7 +45632,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A278" s="14" t="s">
+      <c r="A278" t="s">
         <v>284</v>
       </c>
       <c r="B278" s="2">
@@ -45399,7 +45658,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A279" s="15" t="s">
+      <c r="A279" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B279" s="4">
@@ -45425,7 +45684,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A280" s="15" t="s">
+      <c r="A280" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B280" s="4">
@@ -45451,7 +45710,7 @@
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A281" s="14" t="s">
+      <c r="A281" t="s">
         <v>287</v>
       </c>
       <c r="B281" s="2">
@@ -45477,7 +45736,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A282" s="14" t="s">
+      <c r="A282" t="s">
         <v>288</v>
       </c>
       <c r="B282" s="2">
@@ -45503,7 +45762,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A283" s="14" t="s">
+      <c r="A283" t="s">
         <v>289</v>
       </c>
       <c r="B283" s="2">
@@ -45529,7 +45788,7 @@
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A284" s="14" t="s">
+      <c r="A284" t="s">
         <v>290</v>
       </c>
       <c r="B284" s="2">
@@ -45555,7 +45814,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A285" s="14" t="s">
+      <c r="A285" t="s">
         <v>291</v>
       </c>
       <c r="B285" s="2">
@@ -45581,7 +45840,7 @@
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A286" s="15" t="s">
+      <c r="A286" s="3" t="s">
         <v>292</v>
       </c>
       <c r="B286" s="4">
@@ -45607,7 +45866,7 @@
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A287" s="15" t="s">
+      <c r="A287" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B287" s="4">
@@ -45633,7 +45892,7 @@
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A288" s="14" t="s">
+      <c r="A288" t="s">
         <v>294</v>
       </c>
       <c r="B288" s="2">
@@ -45659,7 +45918,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A289" s="14" t="s">
+      <c r="A289" t="s">
         <v>295</v>
       </c>
       <c r="B289" s="2">
@@ -45685,7 +45944,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A290" s="14" t="s">
+      <c r="A290" t="s">
         <v>296</v>
       </c>
       <c r="B290" s="2">
@@ -45711,7 +45970,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A291" s="14" t="s">
+      <c r="A291" t="s">
         <v>297</v>
       </c>
       <c r="B291" s="2">
@@ -45737,7 +45996,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A292" s="14" t="s">
+      <c r="A292" t="s">
         <v>298</v>
       </c>
       <c r="B292" s="2">
@@ -45763,7 +46022,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A293" s="15" t="s">
+      <c r="A293" s="3" t="s">
         <v>299</v>
       </c>
       <c r="B293" s="4">
@@ -45789,7 +46048,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A294" s="15" t="s">
+      <c r="A294" s="3" t="s">
         <v>300</v>
       </c>
       <c r="B294" s="4">
@@ -45815,7 +46074,7 @@
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A295" s="14" t="s">
+      <c r="A295" t="s">
         <v>301</v>
       </c>
       <c r="B295" s="2">
@@ -45841,7 +46100,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A296" s="14" t="s">
+      <c r="A296" t="s">
         <v>302</v>
       </c>
       <c r="B296" s="2">
@@ -45867,7 +46126,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A297" s="14" t="s">
+      <c r="A297" t="s">
         <v>303</v>
       </c>
       <c r="B297" s="2">
@@ -45893,7 +46152,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A298" s="14" t="s">
+      <c r="A298" t="s">
         <v>304</v>
       </c>
       <c r="B298" s="2">
@@ -45919,7 +46178,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A299" s="14" t="s">
+      <c r="A299" t="s">
         <v>305</v>
       </c>
       <c r="B299" s="2">
@@ -45945,7 +46204,7 @@
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A300" s="15" t="s">
+      <c r="A300" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B300" s="4">
@@ -45971,7 +46230,7 @@
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A301" s="15" t="s">
+      <c r="A301" s="3" t="s">
         <v>307</v>
       </c>
       <c r="B301" s="4">
@@ -45997,7 +46256,7 @@
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A302" s="14" t="s">
+      <c r="A302" t="s">
         <v>308</v>
       </c>
       <c r="B302" s="2">
@@ -46023,7 +46282,7 @@
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A303" s="14" t="s">
+      <c r="A303" t="s">
         <v>309</v>
       </c>
       <c r="B303" s="2">
@@ -46049,7 +46308,7 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A304" s="14" t="s">
+      <c r="A304" t="s">
         <v>310</v>
       </c>
       <c r="B304" s="2">
@@ -46075,7 +46334,7 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A305" s="14" t="s">
+      <c r="A305" t="s">
         <v>311</v>
       </c>
       <c r="B305" s="2">
@@ -46101,7 +46360,7 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A306" s="14" t="s">
+      <c r="A306" t="s">
         <v>312</v>
       </c>
       <c r="B306" s="2">
@@ -46127,7 +46386,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A307" s="15" t="s">
+      <c r="A307" s="3" t="s">
         <v>313</v>
       </c>
       <c r="B307" s="4">
@@ -46153,7 +46412,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A308" s="15" t="s">
+      <c r="A308" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B308" s="4">
@@ -46179,7 +46438,7 @@
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A309" s="14" t="s">
+      <c r="A309" t="s">
         <v>315</v>
       </c>
       <c r="B309" s="2">
@@ -46205,7 +46464,7 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A310" s="14" t="s">
+      <c r="A310" t="s">
         <v>316</v>
       </c>
       <c r="B310" s="2">
@@ -46231,7 +46490,7 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A311" s="14" t="s">
+      <c r="A311" t="s">
         <v>317</v>
       </c>
       <c r="B311" s="2">
@@ -46257,7 +46516,7 @@
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A312" s="14" t="s">
+      <c r="A312" t="s">
         <v>318</v>
       </c>
       <c r="B312" s="2">
@@ -46283,7 +46542,7 @@
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A313" s="14" t="s">
+      <c r="A313" t="s">
         <v>319</v>
       </c>
       <c r="B313" s="2">
@@ -46309,7 +46568,7 @@
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A314" s="15" t="s">
+      <c r="A314" s="3" t="s">
         <v>320</v>
       </c>
       <c r="B314" s="4">
@@ -46335,7 +46594,7 @@
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A315" s="15" t="s">
+      <c r="A315" s="3" t="s">
         <v>321</v>
       </c>
       <c r="B315" s="4">
@@ -46361,7 +46620,7 @@
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A316" s="14" t="s">
+      <c r="A316" t="s">
         <v>322</v>
       </c>
       <c r="B316" s="2">
@@ -46387,7 +46646,7 @@
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A317" s="14" t="s">
+      <c r="A317" t="s">
         <v>323</v>
       </c>
       <c r="B317" s="2">
@@ -46413,7 +46672,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A318" s="14" t="s">
+      <c r="A318" t="s">
         <v>324</v>
       </c>
       <c r="B318" s="2">
@@ -46439,7 +46698,7 @@
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A319" s="14" t="s">
+      <c r="A319" t="s">
         <v>325</v>
       </c>
       <c r="B319" s="2">
@@ -46465,7 +46724,7 @@
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A320" s="14" t="s">
+      <c r="A320" t="s">
         <v>326</v>
       </c>
       <c r="B320" s="2">
@@ -46491,7 +46750,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A321" s="15" t="s">
+      <c r="A321" s="3" t="s">
         <v>327</v>
       </c>
       <c r="B321" s="4">
@@ -46517,7 +46776,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A322" s="15" t="s">
+      <c r="A322" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B322" s="4">
@@ -46543,7 +46802,7 @@
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A323" s="14" t="s">
+      <c r="A323" t="s">
         <v>329</v>
       </c>
       <c r="B323" s="2">
@@ -46569,7 +46828,7 @@
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A324" s="14" t="s">
+      <c r="A324" t="s">
         <v>330</v>
       </c>
       <c r="B324" s="2">
@@ -46595,7 +46854,7 @@
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A325" s="14" t="s">
+      <c r="A325" t="s">
         <v>331</v>
       </c>
       <c r="B325" s="2">
@@ -46621,7 +46880,7 @@
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A326" s="14" t="s">
+      <c r="A326" t="s">
         <v>332</v>
       </c>
       <c r="B326" s="2">
@@ -46647,7 +46906,7 @@
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A327" s="14" t="s">
+      <c r="A327" t="s">
         <v>333</v>
       </c>
       <c r="B327" s="2">
@@ -46673,7 +46932,7 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A328" s="15" t="s">
+      <c r="A328" s="3" t="s">
         <v>334</v>
       </c>
       <c r="B328" s="5">
@@ -46699,7 +46958,7 @@
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A329" s="15" t="s">
+      <c r="A329" s="3" t="s">
         <v>335</v>
       </c>
       <c r="B329" s="5">
@@ -46725,378 +46984,378 @@
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A330" s="14" t="s">
+      <c r="A330" s="10" t="s">
         <v>336</v>
       </c>
       <c r="B330" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C330" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D330" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E330" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F330" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G330" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H330" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A331" s="14" t="s">
+      <c r="A331" s="10" t="s">
         <v>337</v>
       </c>
       <c r="B331" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C331" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D331" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E331" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F331" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G331" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H331" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A332" s="14" t="s">
+      <c r="A332" s="10" t="s">
         <v>338</v>
       </c>
       <c r="B332" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C332" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D332" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E332" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F332" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G332" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H332" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A333" s="14" t="s">
+      <c r="A333" s="10" t="s">
         <v>339</v>
       </c>
       <c r="B333" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C333" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D333" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E333" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F333" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G333" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H333" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A334" s="14" t="s">
+      <c r="A334" s="10" t="s">
         <v>340</v>
       </c>
       <c r="B334" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C334" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D334" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E334" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F334" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G334" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H334" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A335" s="15" t="s">
+      <c r="A335" s="11" t="s">
         <v>341</v>
       </c>
       <c r="B335" s="5">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="C335" s="4">
-        <v>170000</v>
+        <v>240000</v>
       </c>
       <c r="D335" s="4">
-        <v>240000</v>
+        <v>280000</v>
       </c>
       <c r="E335" s="5">
-        <v>250000</v>
+        <v>290000</v>
       </c>
       <c r="F335" s="5">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G335" s="4">
-        <v>750000</v>
+        <v>950000</v>
       </c>
       <c r="H335" s="4">
-        <v>900000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A336" s="15" t="s">
+      <c r="A336" s="11" t="s">
         <v>342</v>
       </c>
       <c r="B336" s="5">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="C336" s="4">
-        <v>170000</v>
+        <v>240000</v>
       </c>
       <c r="D336" s="4">
-        <v>240000</v>
+        <v>280000</v>
       </c>
       <c r="E336" s="5">
-        <v>250000</v>
+        <v>290000</v>
       </c>
       <c r="F336" s="5">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G336" s="4">
-        <v>800000</v>
+        <v>950000</v>
       </c>
       <c r="H336" s="4">
-        <v>950000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A337" s="14" t="s">
+      <c r="A337" s="10" t="s">
         <v>343</v>
       </c>
       <c r="B337" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C337" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D337" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E337" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F337" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G337" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H337" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A338" s="14" t="s">
+      <c r="A338" s="10" t="s">
         <v>344</v>
       </c>
       <c r="B338" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C338" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D338" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E338" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F338" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G338" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H338" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A339" s="14" t="s">
+      <c r="A339" s="10" t="s">
         <v>345</v>
       </c>
       <c r="B339" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C339" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D339" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E339" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F339" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G339" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H339" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A340" s="14" t="s">
+      <c r="A340" s="10" t="s">
         <v>346</v>
       </c>
       <c r="B340" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C340" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D340" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E340" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F340" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G340" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H340" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A341" s="14" t="s">
+      <c r="A341" s="10" t="s">
         <v>347</v>
       </c>
       <c r="B341" s="2">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="C341" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D341" s="2">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="E341" s="2">
-        <v>210000</v>
+        <v>250000</v>
       </c>
       <c r="F341" s="2">
-        <v>240000</v>
+        <v>320000</v>
       </c>
       <c r="G341" s="2">
-        <v>550000</v>
+        <v>700000</v>
       </c>
       <c r="H341" s="2">
-        <v>700000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A342" s="15" t="s">
+      <c r="A342" s="11" t="s">
         <v>348</v>
       </c>
       <c r="B342" s="5">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="C342" s="4">
-        <v>170000</v>
+        <v>240000</v>
       </c>
       <c r="D342" s="4">
-        <v>240000</v>
+        <v>280000</v>
       </c>
       <c r="E342" s="5">
-        <v>250000</v>
+        <v>290000</v>
       </c>
       <c r="F342" s="5">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G342" s="4">
-        <v>750000</v>
+        <v>950000</v>
       </c>
       <c r="H342" s="4">
-        <v>900000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A343" s="15" t="s">
+      <c r="A343" s="11" t="s">
         <v>349</v>
       </c>
       <c r="B343" s="5">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="C343" s="4">
-        <v>170000</v>
+        <v>240000</v>
       </c>
       <c r="D343" s="4">
-        <v>240000</v>
+        <v>280000</v>
       </c>
       <c r="E343" s="5">
-        <v>250000</v>
+        <v>290000</v>
       </c>
       <c r="F343" s="5">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G343" s="4">
-        <v>800000</v>
+        <v>950000</v>
       </c>
       <c r="H343" s="4">
-        <v>950000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A344" s="14" t="s">
+      <c r="A344" t="s">
         <v>350</v>
       </c>
       <c r="B344" s="2">
         <v>140000</v>
       </c>
       <c r="C344" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D344" s="2">
         <v>190000</v>
@@ -47115,14 +47374,14 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A345" s="14" t="s">
+      <c r="A345" t="s">
         <v>351</v>
       </c>
       <c r="B345" s="2">
         <v>140000</v>
       </c>
       <c r="C345" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D345" s="2">
         <v>190000</v>
@@ -47141,14 +47400,14 @@
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A346" s="14" t="s">
+      <c r="A346" t="s">
         <v>352</v>
       </c>
       <c r="B346" s="2">
         <v>140000</v>
       </c>
       <c r="C346" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D346" s="2">
         <v>190000</v>
@@ -47167,14 +47426,14 @@
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A347" s="14" t="s">
+      <c r="A347" t="s">
         <v>353</v>
       </c>
       <c r="B347" s="2">
         <v>140000</v>
       </c>
       <c r="C347" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D347" s="2">
         <v>190000</v>
@@ -47193,14 +47452,14 @@
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A348" s="14" t="s">
+      <c r="A348" t="s">
         <v>354</v>
       </c>
       <c r="B348" s="2">
         <v>140000</v>
       </c>
       <c r="C348" s="2">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D348" s="2">
         <v>190000</v>
@@ -47219,7 +47478,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A349" s="14" t="s">
+      <c r="A349" t="s">
         <v>355</v>
       </c>
       <c r="B349" s="5">
@@ -47245,7 +47504,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A350" s="14" t="s">
+      <c r="A350" t="s">
         <v>356</v>
       </c>
       <c r="B350" s="5">

--- a/백업_기준가격.xlsx
+++ b/백업_기준가격.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\hotel-code\hotel-cmscontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2859FA-C28F-4AAC-8768-42007C4602B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C87811F-61D0-4A5F-B448-131F0CEEA29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,30 @@
     <author>HP</author>
   </authors>
   <commentList>
+    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{9B4AC422-D985-4E8C-A514-271DF535ED8D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/28 50&gt;45</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B29" authorId="0" shapeId="0" xr:uid="{7476F89E-2BFD-4030-9326-F0667A2D8B1C}">
       <text>
         <r>
@@ -98,7 +122,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> &gt; 80,000 &gt; 100,000</t>
+          <t xml:space="preserve"> &gt; 80,000 &gt; 100,000
+1/28 10&gt;11</t>
         </r>
       </text>
     </comment>
@@ -410,7 +435,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000</t>
+          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000
+1/28 10&gt;11</t>
         </r>
       </text>
     </comment>
@@ -535,7 +561,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 90,000 &gt; 12
-0,000</t>
+0,000
+1/28 12&gt;13</t>
         </r>
       </text>
     </comment>
@@ -664,7 +691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{AD5D6536-4F36-481E-BD0E-F5AEA02B4219}">
+    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{8EF8128A-2DDE-495F-9F95-9FBE83CED4E8}">
       <text>
         <r>
           <rPr>
@@ -722,7 +749,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000</t>
+          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000
+1/28 10&gt;11</t>
         </r>
       </text>
     </comment>
@@ -847,7 +875,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 90,000 &gt; 12
-0,000</t>
+0,000
+1/28 12&gt;14</t>
         </r>
       </text>
     </comment>
@@ -976,7 +1005,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{E984BDE6-FDED-4830-B35B-35C0271A5EB8}">
+    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{18254671-B0EE-4774-A377-BA040AAD5709}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/28 35&gt;30</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{C485FE38-0073-4C45-837C-5CBFE5A673E6}">
       <text>
         <r>
           <rPr>
@@ -1034,7 +1087,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000</t>
+          <t xml:space="preserve"> &gt; 70,000 &gt; 100,000
+1/28 10&gt;11</t>
         </r>
       </text>
     </comment>
@@ -1159,7 +1213,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 90,000 &gt; 12
-0,000</t>
+0,000
+1/28 12&gt;14</t>
         </r>
       </text>
     </comment>
@@ -1288,6 +1343,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{857694F0-05C6-4A55-87F2-7C185FACDD09}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/28 35&gt;30</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B33" authorId="0" shapeId="0" xr:uid="{4BA80A7A-EBC6-404F-8853-84B401FE5C32}">
       <text>
         <r>
@@ -1600,6 +1679,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="G33" authorId="0" shapeId="0" xr:uid="{F6B26A40-E070-440E-8F01-9E98948ABFFB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/28 35&gt;30</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B34" authorId="0" shapeId="0" xr:uid="{4C233DE7-AAEC-4D92-9C63-1B2CB36CF8C5}">
       <text>
         <r>
@@ -3519,6 +3622,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="F55" authorId="0" shapeId="0" xr:uid="{7602C7EF-7D9A-44FB-996B-19618D14B8CD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/28 32&gt;38</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E56" authorId="0" shapeId="0" xr:uid="{0E743CC6-13F5-488C-A4D0-67D7B502AA7C}">
       <text>
         <r>
@@ -11356,7 +11483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0" xr:uid="{3FD5ED08-F70D-4A6C-94D8-3276A8E5B196}">
+    <comment ref="B129" authorId="0" shapeId="0" xr:uid="{4B67F1D3-5A5C-41A2-81B6-78C292B8416A}">
       <text>
         <r>
           <rPr>
@@ -11367,6 +11494,21 @@
             <scheme val="minor"/>
           </rPr>
           <t>HP:
+1월 14일 120,000 &gt; 140,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C129" authorId="0" shapeId="0" xr:uid="{3FD5ED08-F70D-4A6C-94D8-3276A8E5B196}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
 1월 14일 130,000 &gt; 160,000</t>
         </r>
       </text>
@@ -11512,7 +11654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0" xr:uid="{7B759017-AEF8-4B2E-9E14-1A029F32B0FE}">
+    <comment ref="B130" authorId="0" shapeId="0" xr:uid="{250D976D-E07A-4D3F-9B10-3DD2BAD4B508}">
       <text>
         <r>
           <rPr>
@@ -11523,6 +11665,21 @@
             <scheme val="minor"/>
           </rPr>
           <t>HP:
+1월 14일 120,000 &gt; 140,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0" xr:uid="{7B759017-AEF8-4B2E-9E14-1A029F32B0FE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
 1월 14일 130,000 &gt; 160,000</t>
         </r>
       </text>
@@ -11668,6 +11825,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="B131" authorId="0" shapeId="0" xr:uid="{C4C03D65-C35A-4C58-AA57-9E49E2589B8C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
+1월 14일 120,000 &gt; 140,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C131" authorId="0" shapeId="0" xr:uid="{8B6301B8-4113-4E21-A588-7DC6ACA94A27}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
+1월 14일 130,000 &gt; 160,000</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D131" authorId="0" shapeId="0" xr:uid="{14135724-E78D-4A9B-92FC-FA6ECA0B9AA7}">
       <text>
         <r>
@@ -12119,7 +12306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D133" authorId="0" shapeId="0" xr:uid="{C0359836-7161-40A1-B45E-72801A534D68}">
+    <comment ref="B133" authorId="0" shapeId="0" xr:uid="{88848C8F-D331-4D62-AAA4-5B790429FC34}">
       <text>
         <r>
           <rPr>
@@ -12177,11 +12364,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 200,000 &gt; 240,000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E133" authorId="0" shapeId="0" xr:uid="{5BF87FF8-17CC-484B-AB3C-41DB05649427}">
+          <t xml:space="preserve"> 150,000 &gt; 170,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D133" authorId="0" shapeId="0" xr:uid="{C0359836-7161-40A1-B45E-72801A534D68}">
       <text>
         <r>
           <rPr>
@@ -12239,11 +12426,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 210,000 &gt; 250,000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F133" authorId="0" shapeId="0" xr:uid="{9A9EDA65-F320-4B82-9C0E-632DC847829E}">
+          <t xml:space="preserve"> 200,000 &gt; 240,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E133" authorId="0" shapeId="0" xr:uid="{5BF87FF8-17CC-484B-AB3C-41DB05649427}">
       <text>
         <r>
           <rPr>
@@ -12282,7 +12469,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>14</t>
+          <t xml:space="preserve"> 14</t>
         </r>
         <r>
           <rPr>
@@ -12301,6 +12488,68 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve"> 210,000 &gt; 250,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F133" authorId="0" shapeId="0" xr:uid="{9A9EDA65-F320-4B82-9C0E-632DC847829E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>월</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>14</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>일</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve"> 220,000 &gt; 30
 0,000</t>
         </r>
@@ -12321,6 +12570,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="C134" authorId="0" shapeId="0" xr:uid="{CB3BFE71-CF95-4468-AF6C-E6BB8EAB5B91}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
+1월 14일 130,000 &gt; 160,000</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D134" authorId="0" shapeId="0" xr:uid="{2221A03C-3676-4115-B2DC-C74715779B85}">
       <text>
         <r>
@@ -12476,7 +12740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C135" authorId="0" shapeId="0" xr:uid="{5A9C62E6-5C6A-4A8B-A339-645E14E3DB20}">
+    <comment ref="C135" authorId="0" shapeId="0" xr:uid="{906BCCED-E40F-463B-B3B4-36758E752500}">
       <text>
         <r>
           <rPr>
@@ -12646,6 +12910,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="C136" authorId="0" shapeId="0" xr:uid="{0840C428-66AC-4EC8-85F8-F984F4FDA72B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HP:
+1월 14일 130,000 &gt; 160,000</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D136" authorId="0" shapeId="0" xr:uid="{B5E8414C-F7A4-4478-BE62-E2C148427523}">
       <text>
         <r>
@@ -13250,7 +13529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B140" authorId="0" shapeId="0" xr:uid="{F22CF9D4-3EDF-47DA-9A86-D5CE0777C140}">
+    <comment ref="F139" authorId="0" shapeId="0" xr:uid="{6B9ECBD9-8E69-48FE-8C06-D23B7495439E}">
       <text>
         <r>
           <rPr>
@@ -13289,7 +13568,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 14</t>
+          <t>14</t>
         </r>
         <r>
           <rPr>
@@ -13308,11 +13587,12 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 150,000 &gt; 170,000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{2BBBBA4F-F07D-4096-A6D3-D85E8A9FBCE6}">
+          <t xml:space="preserve"> 250,000 &gt; 30
+0,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0" xr:uid="{F22CF9D4-3EDF-47DA-9A86-D5CE0777C140}">
       <text>
         <r>
           <rPr>
@@ -13370,11 +13650,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> 220,000 &gt; 240,000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F140" authorId="0" shapeId="0" xr:uid="{F9FAA510-445F-48F3-A706-3DB8F6496B96}">
+          <t xml:space="preserve"> 150,000 &gt; 170,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{2BBBBA4F-F07D-4096-A6D3-D85E8A9FBCE6}">
       <text>
         <r>
           <rPr>
@@ -13413,7 +13693,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>14</t>
+          <t xml:space="preserve"> 14</t>
         </r>
         <r>
           <rPr>
@@ -13432,6 +13712,68 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve"> 220,000 &gt; 240,000</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F140" authorId="0" shapeId="0" xr:uid="{F9FAA510-445F-48F3-A706-3DB8F6496B96}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>월</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>14</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>일</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve"> 250,000 &gt; 30
 0,000</t>
         </r>
@@ -14734,6 +15076,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="C148" authorId="0" shapeId="0" xr:uid="{F7EBE22D-56B2-4ABC-A722-A62C6BDBC96B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/15 12&gt;15
+1/18 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D148" authorId="0" shapeId="0" xr:uid="{5CAC00FE-11E0-4ACC-AB98-FA620235B719}">
       <text>
         <r>
@@ -14871,6 +15238,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="C149" authorId="0" shapeId="0" xr:uid="{030F657D-BB0F-4DAE-A1AD-022C5EC97C34}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/15 12&gt;15
+1/18 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D149" authorId="0" shapeId="0" xr:uid="{8774C1D8-D9F8-4162-84ED-79A39E59AC6E}">
       <text>
         <r>
@@ -16090,6 +16482,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{4F073B97-F44E-43E8-B398-C758E256253A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/15 12&gt;15
+1/18 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D157" authorId="0" shapeId="0" xr:uid="{6A1021C6-F7D6-4CF3-83BF-27E4EE7F8CD0}">
       <text>
         <r>
@@ -16266,6 +16683,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="C158" authorId="0" shapeId="0" xr:uid="{3FF9DD23-DC11-4599-B16F-1DEE329C57D6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/15 12&gt;15
+1/18 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D158" authorId="0" shapeId="0" xr:uid="{8D92F032-FBB4-48D6-8527-04F84E1ADE9F}">
       <text>
         <r>
@@ -17494,6 +17936,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C167" authorId="0" shapeId="0" xr:uid="{1A32CD4C-B48F-4C02-B80F-E4814BF43ADE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D167" authorId="0" shapeId="0" xr:uid="{9A6B651B-159D-4285-A2C0-A252E522B590}">
       <text>
         <r>
@@ -17590,6 +18056,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{1D89C900-A79D-4AE3-AB0D-013AF7E34178}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D168" authorId="0" shapeId="0" xr:uid="{BF1BB2BE-A0A9-477F-97B4-ED93A7A10113}">
       <text>
         <r>
@@ -17683,6 +18173,30 @@
           </rPr>
           <t xml:space="preserve">
 1/16 11 &gt;14</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C169" authorId="0" shapeId="0" xr:uid="{C745C082-34C6-48E8-9434-F3D41CD827F1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
         </r>
       </text>
     </comment>
@@ -18028,6 +18542,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C172" authorId="0" shapeId="0" xr:uid="{1F5781EA-0C33-4B58-973B-C7C9C1437FF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D172" authorId="0" shapeId="0" xr:uid="{CB2033A0-719B-462F-A900-3BB193ED55A2}">
       <text>
         <r>
@@ -18126,6 +18664,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C173" authorId="0" shapeId="0" xr:uid="{5C428A08-AF51-48B9-91F6-15DF49AB4370}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D173" authorId="0" shapeId="0" xr:uid="{5DC44D73-022C-4E6A-BACE-C3DA1C4D2201}">
       <text>
         <r>
@@ -18224,6 +18786,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{76AF1D22-7437-4F69-87AF-213B73A4469D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D174" authorId="0" shapeId="0" xr:uid="{F8539826-CE5F-4F77-8FFE-67526735529F}">
       <text>
         <r>
@@ -18562,6 +19148,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C177" authorId="0" shapeId="0" xr:uid="{6BF8EB78-24D5-41C1-926D-0121E4978A37}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D177" authorId="0" shapeId="0" xr:uid="{56F51DBF-9B68-4F2E-AA9A-4BDFF7A854F1}">
       <text>
         <r>
@@ -18660,6 +19270,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C178" authorId="0" shapeId="0" xr:uid="{33B3B179-2F69-4737-9C92-23AA2690AAD7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D178" authorId="0" shapeId="0" xr:uid="{A9116C2D-B265-4EE2-96EA-1BB676600636}">
       <text>
         <r>
@@ -19583,6 +20217,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C186" authorId="0" shapeId="0" xr:uid="{CEF1D635-A2F2-479F-9B75-2A685E95E4BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D186" authorId="0" shapeId="0" xr:uid="{B80DD79A-8D13-4D20-B4A0-620023A2CB78}">
       <text>
         <r>
@@ -19681,6 +20339,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C187" authorId="0" shapeId="0" xr:uid="{62EA21A5-8468-44A8-8BAA-75C578030F2B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D187" authorId="0" shapeId="0" xr:uid="{74AB1898-322A-4384-99EC-C17806FDB25F}">
       <text>
         <r>
@@ -20629,6 +21311,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C195" authorId="0" shapeId="0" xr:uid="{16E4ED7E-60C3-4019-90AD-5F20845786FF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D195" authorId="0" shapeId="0" xr:uid="{768065C0-01C5-49FF-8352-0E3A99F1EA84}">
       <text>
         <r>
@@ -21333,6 +22039,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C201" authorId="0" shapeId="0" xr:uid="{70A8110E-2EDC-4466-884D-4F8FBEE6060F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D201" authorId="0" shapeId="0" xr:uid="{E7CB7CB3-497C-4F11-B036-FEA155CF0863}">
       <text>
         <r>
@@ -21431,6 +22161,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C202" authorId="0" shapeId="0" xr:uid="{D40971BE-DBF1-455A-A354-44E9D0D654D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D202" authorId="0" shapeId="0" xr:uid="{CA53305A-679B-4B50-8C0F-FDCC53B29F97}">
       <text>
         <r>
@@ -21524,6 +22278,30 @@
           </rPr>
           <t xml:space="preserve">
 1/16 14&gt;16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C203" authorId="0" shapeId="0" xr:uid="{BDEB6ECB-FA52-434F-B6D3-0E7EBA99A768}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
         </r>
       </text>
     </comment>
@@ -22233,6 +23011,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C209" authorId="0" shapeId="0" xr:uid="{0D349487-847B-4BB7-AE23-65A695E60DC4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D209" authorId="0" shapeId="0" xr:uid="{8670B601-AAFB-480E-915E-7879FCC16FAE}">
       <text>
         <r>
@@ -22326,6 +23128,30 @@
           </rPr>
           <t xml:space="preserve">
 1/16 14&gt;16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C210" authorId="0" shapeId="0" xr:uid="{A747FF40-7923-4FEB-B5E1-59C5BA758B40}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
         </r>
       </text>
     </comment>
@@ -22547,6 +23373,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C212" authorId="0" shapeId="0" xr:uid="{A5D1A3C3-92A8-46FD-B711-85A6ACC96DA9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D212" authorId="0" shapeId="0" xr:uid="{A036629C-9A2B-4F63-971B-936AA1D1567E}">
       <text>
         <r>
@@ -23495,6 +24345,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C220" authorId="0" shapeId="0" xr:uid="{D8C9342B-C7BC-4EFA-86FC-4E4E2301FB76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D220" authorId="0" shapeId="0" xr:uid="{8A5869E1-450E-4681-83F2-9FAB2593711D}">
       <text>
         <r>
@@ -24687,6 +25561,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C230" authorId="0" shapeId="0" xr:uid="{C25D5D6A-4D56-46DC-80C4-54FAD0FC9B54}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D230" authorId="0" shapeId="0" xr:uid="{0609ADF2-F4CE-487E-BD5F-77447BCDB2F4}">
       <text>
         <r>
@@ -25269,6 +26167,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C235" authorId="0" shapeId="0" xr:uid="{FD22E0B9-9311-45FF-8640-CBE12F3CA53B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D235" authorId="0" shapeId="0" xr:uid="{082DE7CC-F88A-4722-9911-432A7CB2400F}">
       <text>
         <r>
@@ -25367,6 +26289,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C236" authorId="0" shapeId="0" xr:uid="{039FEEE3-E6C5-4AFA-B036-2A7A3816E633}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 12&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D236" authorId="0" shapeId="0" xr:uid="{72899839-7054-4EE9-A3B0-7045A0518ED0}">
       <text>
         <r>
@@ -25465,6 +26411,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C237" authorId="0" shapeId="0" xr:uid="{E9C66995-6E89-4E9D-9BD4-67FFE693A854}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D237" authorId="0" shapeId="0" xr:uid="{ED3FC4EE-B6CC-43FF-BF05-95308E502258}">
       <text>
         <r>
@@ -25654,6 +26624,54 @@
           </rPr>
           <t xml:space="preserve">
 1/15 22&gt;30</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B239" authorId="0" shapeId="0" xr:uid="{ED8076D4-C545-43A6-B00F-5599D0896C9E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 11 &gt;14</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C239" authorId="0" shapeId="0" xr:uid="{87D38179-748E-4A16-9B08-E78F56604E59}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
         </r>
       </text>
     </comment>
@@ -25755,6 +26773,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C240" authorId="0" shapeId="0" xr:uid="{509C1B03-04E9-42B7-BE99-28F7C548981B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D240" authorId="0" shapeId="0" xr:uid="{D227DE8B-2D01-442B-8373-04C00FA61EC4}">
       <text>
         <r>
@@ -25853,6 +26895,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C241" authorId="0" shapeId="0" xr:uid="{ADD930F4-2EB3-42E9-A579-FC2C9FC9A16F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D241" authorId="0" shapeId="0" xr:uid="{6A968967-3C7A-4390-B2C1-E42B329636AB}">
       <text>
         <r>
@@ -25951,6 +27017,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C242" authorId="0" shapeId="0" xr:uid="{B6F79728-5226-43D2-A490-5970049A12C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D242" authorId="0" shapeId="0" xr:uid="{FE2D53E1-EB6D-4CFD-83B3-FFFA522BC3C5}">
       <text>
         <r>
@@ -26049,6 +27139,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C243" authorId="0" shapeId="0" xr:uid="{B079AF02-BDF3-4DC9-86B0-C487B98B0848}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D243" authorId="0" shapeId="0" xr:uid="{D2986B53-7115-4462-AC62-39C2D2EC4F10}">
       <text>
         <r>
@@ -26147,6 +27261,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C244" authorId="0" shapeId="0" xr:uid="{95247C55-24CD-468B-B0F2-A8346098F120}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D244" authorId="0" shapeId="0" xr:uid="{539591DE-2DCA-45B8-9687-290E8F179AD5}">
       <text>
         <r>
@@ -26240,6 +27378,30 @@
           </rPr>
           <t xml:space="preserve">
 1/16 14&gt;16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C245" authorId="0" shapeId="0" xr:uid="{0331263B-73DC-4EFD-B5C5-437636CAE7E4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/16 15&gt;17</t>
         </r>
       </text>
     </comment>
@@ -26729,6 +27891,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C250" authorId="0" shapeId="0" xr:uid="{38854F34-F018-472B-AB5D-0BB96E728243}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E250" authorId="0" shapeId="0" xr:uid="{EC287B5D-F533-4DD8-8E94-8AD373675E78}">
       <text>
         <r>
@@ -26750,6 +27936,30 @@
           </rPr>
           <t xml:space="preserve">
 1/14 15&gt;21</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C251" authorId="0" shapeId="0" xr:uid="{3102218F-8ABD-4A6C-879F-B76EF0132446}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/15 15&gt;17</t>
         </r>
       </text>
     </comment>
@@ -27667,6 +28877,30 @@
           <t xml:space="preserve">
 1/14 12&gt;14
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C263" authorId="0" shapeId="0" xr:uid="{716ECCD2-138C-4E10-A250-E0C2C87C84AB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1/14 14&gt;15</t>
         </r>
       </text>
     </comment>
@@ -36907,7 +38141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t>날짜</t>
   </si>
@@ -37979,14 +39213,33 @@
   <si>
     <t>2027-01-09</t>
   </si>
+  <si>
+    <t xml:space="preserve">아고다 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수수료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로모션</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ctrip</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>부킹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -38102,7 +39355,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -38114,10 +39367,23 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -38898,11 +40164,11 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2">
-        <v>90000</v>
+        <v>110000</v>
       </c>
       <c r="C19" s="2">
         <v>100000</v>
@@ -38911,26 +40177,26 @@
         <v>90000</v>
       </c>
       <c r="E19" s="2">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="F19" s="2">
-        <v>240000</v>
+        <v>150000</v>
       </c>
       <c r="G19" s="2">
         <v>300000</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="6">
         <v>450000</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="4">
-        <v>100000</v>
-      </c>
-      <c r="C20" s="4">
+        <v>110000</v>
+      </c>
+      <c r="C20" s="7">
         <v>120000</v>
       </c>
       <c r="D20" s="4">
@@ -38945,18 +40211,18 @@
       <c r="G20" s="4">
         <v>400000</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="7">
         <v>600000</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="7">
         <v>120000</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="7">
         <v>130000</v>
       </c>
       <c r="D21" s="4">
@@ -38966,61 +40232,61 @@
         <v>180000</v>
       </c>
       <c r="F21" s="4">
-        <v>330000</v>
+        <v>300000</v>
       </c>
       <c r="G21" s="4">
         <v>400000</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="7">
         <v>600000</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="6">
         <v>100000</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="6">
         <v>90000</v>
       </c>
-      <c r="D22" s="2">
-        <v>90000</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E22" s="6">
         <v>110000</v>
       </c>
       <c r="F22" s="2">
-        <v>240000</v>
-      </c>
-      <c r="G22" s="2">
+        <v>200000</v>
+      </c>
+      <c r="G22" s="6">
         <v>350000</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="6">
         <v>400000</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="6">
         <v>100000</v>
       </c>
       <c r="C23" s="2">
         <v>100000</v>
       </c>
       <c r="D23" s="2">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="E23" s="2">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="F23" s="2">
-        <v>130000</v>
-      </c>
-      <c r="G23" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G23" s="6">
         <v>350000</v>
       </c>
       <c r="H23" s="2">
@@ -39028,117 +40294,117 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="15" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="2">
+        <v>110000</v>
+      </c>
+      <c r="C24" s="6">
         <v>90000</v>
       </c>
-      <c r="C24" s="2">
-        <v>90000</v>
-      </c>
       <c r="D24" s="2">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="E24" s="2">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="F24" s="2">
-        <v>240000</v>
-      </c>
-      <c r="G24" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G24" s="6">
         <v>350000</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="6">
         <v>400000</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="2">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="C25" s="2">
         <v>90000</v>
       </c>
       <c r="D25" s="2">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="E25" s="2">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="F25" s="2">
-        <v>120000</v>
-      </c>
-      <c r="G25" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G25" s="6">
         <v>350000</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="6">
         <v>400000</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="15" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="2">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="C26" s="2">
         <v>100000</v>
       </c>
       <c r="D26" s="2">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="E26" s="2">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="F26" s="2">
-        <v>120000</v>
+        <v>300000</v>
       </c>
       <c r="G26" s="2">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="H26" s="2">
         <v>250000</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="4">
         <v>110000</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="7">
         <v>120000</v>
       </c>
       <c r="D27" s="4">
         <v>160000</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="7">
         <v>170000</v>
       </c>
       <c r="F27" s="4">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="G27" s="4">
-        <v>500000</v>
-      </c>
-      <c r="H27" s="4">
+        <v>450000</v>
+      </c>
+      <c r="H27" s="7">
         <v>650000</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="4">
         <v>120000</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="7">
         <v>130000</v>
       </c>
       <c r="D28" s="4">
@@ -39148,26 +40414,26 @@
         <v>190000</v>
       </c>
       <c r="F28" s="4">
-        <v>210000</v>
-      </c>
-      <c r="G28" s="4">
+        <v>300000</v>
+      </c>
+      <c r="G28" s="7">
         <v>550000</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="7">
         <v>700000</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="2">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="C29" s="2">
         <v>110000</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="6">
         <v>120000</v>
       </c>
       <c r="E29" s="2">
@@ -39176,25 +40442,25 @@
       <c r="F29" s="2">
         <v>160000</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="6">
         <v>350000</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="6">
         <v>500000</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="2">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="C30" s="2">
         <v>110000</v>
       </c>
       <c r="D30" s="2">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="E30" s="2">
         <v>140000</v>
@@ -39202,25 +40468,25 @@
       <c r="F30" s="2">
         <v>160000</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="6">
         <v>350000</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="6">
         <v>300000</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="2">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="C31" s="2">
         <v>110000</v>
       </c>
       <c r="D31" s="2">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="E31" s="2">
         <v>140000</v>
@@ -39229,24 +40495,24 @@
         <v>160000</v>
       </c>
       <c r="G31" s="2">
-        <v>350000</v>
-      </c>
-      <c r="H31" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H31" s="6">
         <v>300000</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="15" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="2">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="C32" s="2">
         <v>110000</v>
       </c>
       <c r="D32" s="2">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="E32" s="2">
         <v>140000</v>
@@ -39255,14 +40521,14 @@
         <v>160000</v>
       </c>
       <c r="G32" s="2">
-        <v>350000</v>
-      </c>
-      <c r="H32" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H32" s="6">
         <v>450000</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="15" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="2">
@@ -39272,7 +40538,7 @@
         <v>110000</v>
       </c>
       <c r="D33" s="2">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="E33" s="2">
         <v>140000</v>
@@ -39281,7 +40547,7 @@
         <v>160000</v>
       </c>
       <c r="G33" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="H33" s="2">
         <v>450000</v>
@@ -39356,7 +40622,7 @@
         <v>160000</v>
       </c>
       <c r="F36" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="G36" s="2">
         <v>450000</v>
@@ -39544,7 +40810,7 @@
         <v>400000</v>
       </c>
       <c r="H43" s="2">
-        <v>400000</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -39850,7 +41116,7 @@
         <v>270000</v>
       </c>
       <c r="F55" s="4">
-        <v>320000</v>
+        <v>380000</v>
       </c>
       <c r="G55" s="4">
         <v>600000</v>
@@ -40146,7 +41412,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B67" s="2">
@@ -40172,7 +41438,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="15" t="s">
         <v>74</v>
       </c>
       <c r="B68" s="2">
@@ -40198,7 +41464,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="16" t="s">
         <v>75</v>
       </c>
       <c r="B69" s="7">
@@ -40224,7 +41490,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="16" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="7">
@@ -40250,7 +41516,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="15" t="s">
         <v>77</v>
       </c>
       <c r="B71" s="2">
@@ -40276,7 +41542,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="15" t="s">
         <v>78</v>
       </c>
       <c r="B72" s="6">
@@ -40302,7 +41568,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B73" s="2">
@@ -40328,7 +41594,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="15" t="s">
         <v>80</v>
       </c>
       <c r="B74" s="6">
@@ -40354,7 +41620,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="15" t="s">
         <v>81</v>
       </c>
       <c r="B75" s="6">
@@ -40380,7 +41646,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="16" t="s">
         <v>82</v>
       </c>
       <c r="B76" s="7">
@@ -40406,7 +41672,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="16" t="s">
         <v>83</v>
       </c>
       <c r="B77" s="7">
@@ -40432,7 +41698,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="15" t="s">
         <v>84</v>
       </c>
       <c r="B78" s="6">
@@ -40458,7 +41724,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="15" t="s">
         <v>85</v>
       </c>
       <c r="B79" s="6">
@@ -40484,7 +41750,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="15" t="s">
         <v>86</v>
       </c>
       <c r="B80" s="2">
@@ -40510,7 +41776,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="15" t="s">
         <v>87</v>
       </c>
       <c r="B81" s="6">
@@ -40536,7 +41802,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="15" t="s">
         <v>88</v>
       </c>
       <c r="B82" s="2">
@@ -40562,7 +41828,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="16" t="s">
         <v>89</v>
       </c>
       <c r="B83" s="5">
@@ -41137,7 +42403,7 @@
       <c r="A105" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B105" s="12">
+      <c r="B105" s="4">
         <v>180000</v>
       </c>
       <c r="C105" s="7">
@@ -41531,7 +42797,7 @@
         <v>140000</v>
       </c>
       <c r="C120" s="6">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D120" s="2">
         <v>180000</v>
@@ -41557,7 +42823,7 @@
         <v>140000</v>
       </c>
       <c r="C121" s="6">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D121" s="2">
         <v>180000</v>
@@ -41635,7 +42901,7 @@
         <v>140000</v>
       </c>
       <c r="C124" s="6">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D124" s="2">
         <v>180000</v>
@@ -41661,7 +42927,7 @@
         <v>150000</v>
       </c>
       <c r="C125" s="7">
-        <v>150000</v>
+        <v>190000</v>
       </c>
       <c r="D125" s="4">
         <v>240000</v>
@@ -41687,7 +42953,7 @@
         <v>150000</v>
       </c>
       <c r="C126" s="7">
-        <v>150000</v>
+        <v>190000</v>
       </c>
       <c r="D126" s="4">
         <v>240000</v>
@@ -41732,28 +42998,28 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="17">
         <v>140000</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="17">
         <v>160000</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="17">
         <v>180000</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="17">
         <v>180000</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="17">
         <v>230000</v>
       </c>
-      <c r="G128" s="2">
+      <c r="G128" s="17">
         <v>450000</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="17">
         <v>600000</v>
       </c>
     </row>
@@ -41761,8 +43027,8 @@
       <c r="A129" t="s">
         <v>135</v>
       </c>
-      <c r="B129" s="6">
-        <v>120000</v>
+      <c r="B129" s="2">
+        <v>140000</v>
       </c>
       <c r="C129" s="2">
         <v>160000</v>
@@ -41787,8 +43053,8 @@
       <c r="A130" t="s">
         <v>136</v>
       </c>
-      <c r="B130" s="6">
-        <v>120000</v>
+      <c r="B130" s="2">
+        <v>140000</v>
       </c>
       <c r="C130" s="2">
         <v>160000</v>
@@ -41813,11 +43079,11 @@
       <c r="A131" t="s">
         <v>137</v>
       </c>
-      <c r="B131" s="6">
-        <v>120000</v>
-      </c>
-      <c r="C131" s="6">
-        <v>130000</v>
+      <c r="B131" s="2">
+        <v>140000</v>
+      </c>
+      <c r="C131" s="2">
+        <v>160000</v>
       </c>
       <c r="D131" s="2">
         <v>180000</v>
@@ -41865,22 +43131,22 @@
       <c r="A133" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B133" s="7">
-        <v>150000</v>
-      </c>
-      <c r="C133" s="7">
-        <v>150000</v>
-      </c>
-      <c r="D133" s="4">
+      <c r="B133" s="4">
+        <v>170000</v>
+      </c>
+      <c r="C133" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D133" s="18">
         <v>240000</v>
       </c>
-      <c r="E133" s="4">
+      <c r="E133" s="18">
         <v>250000</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="18">
         <v>300000</v>
       </c>
-      <c r="G133" s="4">
+      <c r="G133" s="18">
         <v>700000</v>
       </c>
       <c r="H133" s="4">
@@ -41891,22 +43157,22 @@
       <c r="A134" t="s">
         <v>140</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="19">
         <v>140000</v>
       </c>
-      <c r="C134" s="6">
-        <v>130000</v>
-      </c>
-      <c r="D134" s="2">
+      <c r="C134" s="19">
+        <v>160000</v>
+      </c>
+      <c r="D134" s="19">
         <v>180000</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="19">
         <v>200000</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="19">
         <v>230000</v>
       </c>
-      <c r="G134" s="2">
+      <c r="G134" s="19">
         <v>450000</v>
       </c>
       <c r="H134" s="2">
@@ -41917,22 +43183,22 @@
       <c r="A135" t="s">
         <v>141</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="19">
         <v>140000</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="19">
         <v>160000</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="19">
         <v>180000</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="19">
         <v>200000</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="19">
         <v>230000</v>
       </c>
-      <c r="G135" s="2">
+      <c r="G135" s="19">
         <v>450000</v>
       </c>
       <c r="H135" s="2">
@@ -41943,22 +43209,22 @@
       <c r="A136" t="s">
         <v>142</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="19">
         <v>140000</v>
       </c>
-      <c r="C136" s="6">
-        <v>120000</v>
-      </c>
-      <c r="D136" s="2">
+      <c r="C136" s="19">
+        <v>160000</v>
+      </c>
+      <c r="D136" s="19">
         <v>180000</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="19">
         <v>200000</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="19">
         <v>230000</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G136" s="19">
         <v>450000</v>
       </c>
       <c r="H136" s="2">
@@ -41969,22 +43235,22 @@
       <c r="A137" t="s">
         <v>143</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="19">
         <v>140000</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="19">
         <v>160000</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="19">
         <v>180000</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="19">
         <v>200000</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="19">
         <v>230000</v>
       </c>
-      <c r="G137" s="2">
+      <c r="G137" s="19">
         <v>450000</v>
       </c>
       <c r="H137" s="2">
@@ -41995,22 +43261,22 @@
       <c r="A138" t="s">
         <v>144</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="19">
         <v>140000</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="19">
         <v>160000</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="19">
         <v>180000</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="19">
         <v>200000</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="19">
         <v>230000</v>
       </c>
-      <c r="G138" s="2">
+      <c r="G138" s="19">
         <v>450000</v>
       </c>
       <c r="H138" s="2">
@@ -42021,22 +43287,22 @@
       <c r="A139" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="18">
         <v>170000</v>
       </c>
-      <c r="C139" s="7">
-        <v>160000</v>
-      </c>
-      <c r="D139" s="4">
+      <c r="C139" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D139" s="18">
         <v>240000</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E139" s="18">
         <v>250000</v>
       </c>
-      <c r="F139" s="7">
-        <v>250000</v>
-      </c>
-      <c r="G139" s="4">
+      <c r="F139" s="18">
+        <v>300000</v>
+      </c>
+      <c r="G139" s="18">
         <v>650000</v>
       </c>
       <c r="H139" s="4">
@@ -42047,22 +43313,22 @@
       <c r="A140" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="18">
         <v>170000</v>
       </c>
-      <c r="C140" s="7">
-        <v>160000</v>
-      </c>
-      <c r="D140" s="4">
+      <c r="C140" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D140" s="18">
         <v>240000</v>
       </c>
-      <c r="E140" s="7">
+      <c r="E140" s="18">
         <v>250000</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="18">
         <v>300000</v>
       </c>
-      <c r="G140" s="4">
+      <c r="G140" s="18">
         <v>700000</v>
       </c>
       <c r="H140" s="4">
@@ -42073,22 +43339,22 @@
       <c r="A141" t="s">
         <v>147</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="19">
         <v>140000</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141" s="19">
         <v>160000</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="19">
         <v>180000</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="19">
         <v>210000</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="19">
         <v>230000</v>
       </c>
-      <c r="G141" s="2">
+      <c r="G141" s="19">
         <v>450000</v>
       </c>
       <c r="H141" s="2">
@@ -42099,22 +43365,22 @@
       <c r="A142" t="s">
         <v>148</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="19">
         <v>140000</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142" s="19">
         <v>160000</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="19">
         <v>180000</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="19">
         <v>210000</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="19">
         <v>230000</v>
       </c>
-      <c r="G142" s="2">
+      <c r="G142" s="19">
         <v>450000</v>
       </c>
       <c r="H142" s="2">
@@ -42125,22 +43391,22 @@
       <c r="A143" t="s">
         <v>149</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="19">
         <v>140000</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="19">
         <v>160000</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="19">
         <v>190000</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="19">
         <v>210000</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="19">
         <v>240000</v>
       </c>
-      <c r="G143" s="2">
+      <c r="G143" s="19">
         <v>450000</v>
       </c>
       <c r="H143" s="2">
@@ -42151,22 +43417,22 @@
       <c r="A144" t="s">
         <v>150</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="19">
         <v>140000</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144" s="19">
         <v>160000</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="19">
         <v>190000</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="19">
         <v>210000</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="19">
         <v>240000</v>
       </c>
-      <c r="G144" s="2">
+      <c r="G144" s="19">
         <v>450000</v>
       </c>
       <c r="H144" s="2">
@@ -42177,22 +43443,22 @@
       <c r="A145" t="s">
         <v>151</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="19">
         <v>140000</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145" s="19">
         <v>160000</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="19">
         <v>190000</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="19">
         <v>210000</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="19">
         <v>240000</v>
       </c>
-      <c r="G145" s="2">
+      <c r="G145" s="19">
         <v>450000</v>
       </c>
       <c r="H145" s="2">
@@ -42203,22 +43469,22 @@
       <c r="A146" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="18">
         <v>180000</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="18">
         <v>190000</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146" s="18">
         <v>240000</v>
       </c>
-      <c r="E146" s="4">
+      <c r="E146" s="18">
         <v>250000</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="18">
         <v>300000</v>
       </c>
-      <c r="G146" s="4">
+      <c r="G146" s="18">
         <v>600000</v>
       </c>
       <c r="H146" s="4">
@@ -42229,22 +43495,22 @@
       <c r="A147" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="18">
         <v>180000</v>
       </c>
-      <c r="C147" s="7">
-        <v>140000</v>
-      </c>
-      <c r="D147" s="4">
+      <c r="C147" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D147" s="18">
         <v>240000</v>
       </c>
-      <c r="E147" s="4">
+      <c r="E147" s="18">
         <v>250000</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="18">
         <v>300000</v>
       </c>
-      <c r="G147" s="4">
+      <c r="G147" s="18">
         <v>700000</v>
       </c>
       <c r="H147" s="4">
@@ -42255,22 +43521,22 @@
       <c r="A148" t="s">
         <v>154</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="19">
         <v>160000</v>
       </c>
-      <c r="C148" s="6">
-        <v>120000</v>
-      </c>
-      <c r="D148" s="2">
+      <c r="C148" s="19">
+        <v>170000</v>
+      </c>
+      <c r="D148" s="19">
         <v>190000</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="19">
         <v>210000</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="19">
         <v>240000</v>
       </c>
-      <c r="G148" s="2">
+      <c r="G148" s="19">
         <v>450000</v>
       </c>
       <c r="H148" s="2">
@@ -42281,22 +43547,22 @@
       <c r="A149" t="s">
         <v>155</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="19">
         <v>160000</v>
       </c>
-      <c r="C149" s="6">
-        <v>120000</v>
-      </c>
-      <c r="D149" s="2">
+      <c r="C149" s="19">
+        <v>170000</v>
+      </c>
+      <c r="D149" s="19">
         <v>190000</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="19">
         <v>210000</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="19">
         <v>240000</v>
       </c>
-      <c r="G149" s="2">
+      <c r="G149" s="19">
         <v>450000</v>
       </c>
       <c r="H149" s="2">
@@ -42307,22 +43573,22 @@
       <c r="A150" t="s">
         <v>156</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="19">
         <v>160000</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="19">
         <v>170000</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="19">
         <v>190000</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="19">
         <v>210000</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="19">
         <v>240000</v>
       </c>
-      <c r="G150" s="2">
+      <c r="G150" s="19">
         <v>450000</v>
       </c>
       <c r="H150" s="2">
@@ -42333,22 +43599,22 @@
       <c r="A151" t="s">
         <v>157</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="19">
         <v>160000</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="19">
         <v>170000</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="19">
         <v>190000</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="19">
         <v>210000</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="19">
         <v>240000</v>
       </c>
-      <c r="G151" s="2">
+      <c r="G151" s="19">
         <v>450000</v>
       </c>
       <c r="H151" s="2">
@@ -42359,22 +43625,22 @@
       <c r="A152" t="s">
         <v>158</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="19">
         <v>160000</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="19">
         <v>170000</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="19">
         <v>190000</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="19">
         <v>210000</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="19">
         <v>240000</v>
       </c>
-      <c r="G152" s="2">
+      <c r="G152" s="19">
         <v>450000</v>
       </c>
       <c r="H152" s="2">
@@ -42385,22 +43651,22 @@
       <c r="A153" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="18">
         <v>180000</v>
       </c>
-      <c r="C153" s="7">
-        <v>140000</v>
-      </c>
-      <c r="D153" s="4">
+      <c r="C153" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D153" s="18">
         <v>240000</v>
       </c>
-      <c r="E153" s="4">
+      <c r="E153" s="18">
         <v>250000</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="18">
         <v>300000</v>
       </c>
-      <c r="G153" s="4">
+      <c r="G153" s="18">
         <v>600000</v>
       </c>
       <c r="H153" s="4">
@@ -42411,22 +43677,22 @@
       <c r="A154" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="18">
         <v>180000</v>
       </c>
-      <c r="C154" s="7">
-        <v>140000</v>
-      </c>
-      <c r="D154" s="4">
+      <c r="C154" s="18">
+        <v>190000</v>
+      </c>
+      <c r="D154" s="18">
         <v>240000</v>
       </c>
-      <c r="E154" s="4">
+      <c r="E154" s="18">
         <v>250000</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="18">
         <v>300000</v>
       </c>
-      <c r="G154" s="4">
+      <c r="G154" s="18">
         <v>700000</v>
       </c>
       <c r="H154" s="4">
@@ -42437,22 +43703,22 @@
       <c r="A155" t="s">
         <v>161</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="19">
         <v>160000</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="19">
         <v>170000</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="19">
         <v>190000</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="19">
         <v>210000</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="19">
         <v>240000</v>
       </c>
-      <c r="G155" s="2">
+      <c r="G155" s="19">
         <v>450000</v>
       </c>
       <c r="H155" s="2">
@@ -42492,8 +43758,8 @@
       <c r="B157" s="2">
         <v>160000</v>
       </c>
-      <c r="C157" s="6">
-        <v>120000</v>
+      <c r="C157" s="2">
+        <v>170000</v>
       </c>
       <c r="D157" s="2">
         <v>190000</v>
@@ -42518,8 +43784,8 @@
       <c r="B158" s="2">
         <v>160000</v>
       </c>
-      <c r="C158" s="6">
-        <v>120000</v>
+      <c r="C158" s="2">
+        <v>170000</v>
       </c>
       <c r="D158" s="2">
         <v>190000</v>
@@ -42752,8 +44018,8 @@
       <c r="B167" s="4">
         <v>160000</v>
       </c>
-      <c r="C167" s="7">
-        <v>150000</v>
+      <c r="C167" s="4">
+        <v>170000</v>
       </c>
       <c r="D167" s="4">
         <v>240000</v>
@@ -42778,8 +44044,8 @@
       <c r="B168" s="4">
         <v>160000</v>
       </c>
-      <c r="C168" s="7">
-        <v>160000</v>
+      <c r="C168" s="4">
+        <v>170000</v>
       </c>
       <c r="D168" s="4">
         <v>240000</v>
@@ -42804,8 +44070,8 @@
       <c r="B169" s="2">
         <v>140000</v>
       </c>
-      <c r="C169" s="6">
-        <v>130000</v>
+      <c r="C169" s="2">
+        <v>150000</v>
       </c>
       <c r="D169" s="2">
         <v>190000</v>
@@ -42882,8 +44148,8 @@
       <c r="B172" s="2">
         <v>140000</v>
       </c>
-      <c r="C172" s="6">
-        <v>130000</v>
+      <c r="C172" s="2">
+        <v>150000</v>
       </c>
       <c r="D172" s="2">
         <v>190000</v>
@@ -42908,8 +44174,8 @@
       <c r="B173" s="2">
         <v>140000</v>
       </c>
-      <c r="C173" s="6">
-        <v>130000</v>
+      <c r="C173" s="2">
+        <v>150000</v>
       </c>
       <c r="D173" s="2">
         <v>190000</v>
@@ -42934,8 +44200,8 @@
       <c r="B174" s="4">
         <v>160000</v>
       </c>
-      <c r="C174" s="7">
-        <v>150000</v>
+      <c r="C174" s="4">
+        <v>170000</v>
       </c>
       <c r="D174" s="4">
         <v>240000</v>
@@ -43012,8 +44278,8 @@
       <c r="B177" s="2">
         <v>140000</v>
       </c>
-      <c r="C177" s="6">
-        <v>120000</v>
+      <c r="C177" s="2">
+        <v>150000</v>
       </c>
       <c r="D177" s="2">
         <v>190000</v>
@@ -43038,8 +44304,8 @@
       <c r="B178" s="2">
         <v>140000</v>
       </c>
-      <c r="C178" s="6">
-        <v>130000</v>
+      <c r="C178" s="2">
+        <v>150000</v>
       </c>
       <c r="D178" s="2">
         <v>190000</v>
@@ -43246,8 +44512,8 @@
       <c r="B186" s="2">
         <v>140000</v>
       </c>
-      <c r="C186" s="6">
-        <v>130000</v>
+      <c r="C186" s="2">
+        <v>150000</v>
       </c>
       <c r="D186" s="2">
         <v>190000</v>
@@ -43272,8 +44538,8 @@
       <c r="B187" s="2">
         <v>140000</v>
       </c>
-      <c r="C187" s="6">
-        <v>130000</v>
+      <c r="C187" s="2">
+        <v>150000</v>
       </c>
       <c r="D187" s="2">
         <v>190000</v>
@@ -43480,8 +44746,8 @@
       <c r="B195" s="4">
         <v>160000</v>
       </c>
-      <c r="C195" s="7">
-        <v>150000</v>
+      <c r="C195" s="4">
+        <v>170000</v>
       </c>
       <c r="D195" s="4">
         <v>240000</v>
@@ -43636,8 +44902,8 @@
       <c r="B201" s="2">
         <v>140000</v>
       </c>
-      <c r="C201" s="6">
-        <v>130000</v>
+      <c r="C201" s="2">
+        <v>150000</v>
       </c>
       <c r="D201" s="2">
         <v>190000</v>
@@ -43662,8 +44928,8 @@
       <c r="B202" s="4">
         <v>160000</v>
       </c>
-      <c r="C202" s="7">
-        <v>150000</v>
+      <c r="C202" s="4">
+        <v>170000</v>
       </c>
       <c r="D202" s="4">
         <v>240000</v>
@@ -43688,8 +44954,8 @@
       <c r="B203" s="4">
         <v>160000</v>
       </c>
-      <c r="C203" s="7">
-        <v>150000</v>
+      <c r="C203" s="4">
+        <v>170000</v>
       </c>
       <c r="D203" s="4">
         <v>240000</v>
@@ -43844,8 +45110,8 @@
       <c r="B209" s="4">
         <v>160000</v>
       </c>
-      <c r="C209" s="7">
-        <v>140000</v>
+      <c r="C209" s="4">
+        <v>170000</v>
       </c>
       <c r="D209" s="4">
         <v>240000</v>
@@ -43870,8 +45136,8 @@
       <c r="B210" s="4">
         <v>160000</v>
       </c>
-      <c r="C210" s="7">
-        <v>140000</v>
+      <c r="C210" s="4">
+        <v>170000</v>
       </c>
       <c r="D210" s="4">
         <v>240000</v>
@@ -43922,8 +45188,8 @@
       <c r="B212" s="2">
         <v>140000</v>
       </c>
-      <c r="C212" s="6">
-        <v>120000</v>
+      <c r="C212" s="2">
+        <v>150000</v>
       </c>
       <c r="D212" s="2">
         <v>190000</v>
@@ -44130,8 +45396,8 @@
       <c r="B220" s="2">
         <v>140000</v>
       </c>
-      <c r="C220" s="6">
-        <v>120000</v>
+      <c r="C220" s="2">
+        <v>150000</v>
       </c>
       <c r="D220" s="2">
         <v>190000</v>
@@ -44390,8 +45656,8 @@
       <c r="B230" s="4">
         <v>160000</v>
       </c>
-      <c r="C230" s="7">
-        <v>140000</v>
+      <c r="C230" s="4">
+        <v>170000</v>
       </c>
       <c r="D230" s="4">
         <v>240000</v>
@@ -44520,8 +45786,8 @@
       <c r="B235" s="2">
         <v>140000</v>
       </c>
-      <c r="C235" s="6">
-        <v>120000</v>
+      <c r="C235" s="2">
+        <v>150000</v>
       </c>
       <c r="D235" s="2">
         <v>190000</v>
@@ -44546,8 +45812,8 @@
       <c r="B236" s="2">
         <v>140000</v>
       </c>
-      <c r="C236" s="6">
-        <v>120000</v>
+      <c r="C236" s="2">
+        <v>150000</v>
       </c>
       <c r="D236" s="2">
         <v>190000</v>
@@ -44572,8 +45838,8 @@
       <c r="B237" s="4">
         <v>160000</v>
       </c>
-      <c r="C237" s="7">
-        <v>150000</v>
+      <c r="C237" s="4">
+        <v>170000</v>
       </c>
       <c r="D237" s="4">
         <v>240000</v>
@@ -44621,11 +45887,11 @@
       <c r="A239" t="s">
         <v>245</v>
       </c>
-      <c r="B239" s="6">
-        <v>120000</v>
-      </c>
-      <c r="C239" s="6">
-        <v>130000</v>
+      <c r="B239" s="2">
+        <v>140000</v>
+      </c>
+      <c r="C239" s="2">
+        <v>150000</v>
       </c>
       <c r="D239" s="2">
         <v>190000</v>
@@ -44650,8 +45916,8 @@
       <c r="B240" s="2">
         <v>140000</v>
       </c>
-      <c r="C240" s="6">
-        <v>130000</v>
+      <c r="C240" s="2">
+        <v>150000</v>
       </c>
       <c r="D240" s="2">
         <v>190000</v>
@@ -44676,8 +45942,8 @@
       <c r="B241" s="2">
         <v>140000</v>
       </c>
-      <c r="C241" s="6">
-        <v>120000</v>
+      <c r="C241" s="2">
+        <v>150000</v>
       </c>
       <c r="D241" s="2">
         <v>190000</v>
@@ -44702,8 +45968,8 @@
       <c r="B242" s="2">
         <v>140000</v>
       </c>
-      <c r="C242" s="6">
-        <v>120000</v>
+      <c r="C242" s="2">
+        <v>150000</v>
       </c>
       <c r="D242" s="2">
         <v>190000</v>
@@ -44728,8 +45994,8 @@
       <c r="B243" s="2">
         <v>140000</v>
       </c>
-      <c r="C243" s="6">
-        <v>120000</v>
+      <c r="C243" s="2">
+        <v>150000</v>
       </c>
       <c r="D243" s="2">
         <v>190000</v>
@@ -44754,8 +46020,8 @@
       <c r="B244" s="4">
         <v>160000</v>
       </c>
-      <c r="C244" s="7">
-        <v>140000</v>
+      <c r="C244" s="4">
+        <v>170000</v>
       </c>
       <c r="D244" s="4">
         <v>240000</v>
@@ -44780,8 +46046,8 @@
       <c r="B245" s="4">
         <v>160000</v>
       </c>
-      <c r="C245" s="7">
-        <v>150000</v>
+      <c r="C245" s="4">
+        <v>170000</v>
       </c>
       <c r="D245" s="4">
         <v>240000</v>
@@ -44910,8 +46176,8 @@
       <c r="B250" s="2">
         <v>140000</v>
       </c>
-      <c r="C250" s="6">
-        <v>140000</v>
+      <c r="C250" s="2">
+        <v>150000</v>
       </c>
       <c r="D250" s="2">
         <v>190000</v>
@@ -44936,8 +46202,8 @@
       <c r="B251" s="4">
         <v>160000</v>
       </c>
-      <c r="C251" s="7">
-        <v>140000</v>
+      <c r="C251" s="4">
+        <v>170000</v>
       </c>
       <c r="D251" s="4">
         <v>240000</v>
@@ -45248,8 +46514,8 @@
       <c r="B263" s="2">
         <v>140000</v>
       </c>
-      <c r="C263" s="6">
-        <v>130000</v>
+      <c r="C263" s="2">
+        <v>150000</v>
       </c>
       <c r="D263" s="2">
         <v>190000</v>
@@ -46932,7 +48198,7 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A328" s="3" t="s">
+      <c r="A328" s="16" t="s">
         <v>334</v>
       </c>
       <c r="B328" s="5">
@@ -46958,7 +48224,7 @@
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A329" s="3" t="s">
+      <c r="A329" s="16" t="s">
         <v>335</v>
       </c>
       <c r="B329" s="5">
@@ -46984,7 +48250,7 @@
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A330" s="10" t="s">
+      <c r="A330" s="15" t="s">
         <v>336</v>
       </c>
       <c r="B330" s="2">
@@ -47010,7 +48276,7 @@
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A331" s="10" t="s">
+      <c r="A331" s="15" t="s">
         <v>337</v>
       </c>
       <c r="B331" s="2">
@@ -47036,7 +48302,7 @@
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A332" s="10" t="s">
+      <c r="A332" s="15" t="s">
         <v>338</v>
       </c>
       <c r="B332" s="2">
@@ -47062,7 +48328,7 @@
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A333" s="10" t="s">
+      <c r="A333" s="15" t="s">
         <v>339</v>
       </c>
       <c r="B333" s="2">
@@ -47088,7 +48354,7 @@
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A334" s="10" t="s">
+      <c r="A334" s="15" t="s">
         <v>340</v>
       </c>
       <c r="B334" s="2">
@@ -47114,7 +48380,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A335" s="11" t="s">
+      <c r="A335" s="16" t="s">
         <v>341</v>
       </c>
       <c r="B335" s="5">
@@ -47140,7 +48406,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A336" s="11" t="s">
+      <c r="A336" s="16" t="s">
         <v>342</v>
       </c>
       <c r="B336" s="5">
@@ -47166,7 +48432,7 @@
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A337" s="10" t="s">
+      <c r="A337" s="15" t="s">
         <v>343</v>
       </c>
       <c r="B337" s="2">
@@ -47192,7 +48458,7 @@
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A338" s="10" t="s">
+      <c r="A338" s="15" t="s">
         <v>344</v>
       </c>
       <c r="B338" s="2">
@@ -47218,7 +48484,7 @@
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A339" s="10" t="s">
+      <c r="A339" s="15" t="s">
         <v>345</v>
       </c>
       <c r="B339" s="2">
@@ -47244,7 +48510,7 @@
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A340" s="10" t="s">
+      <c r="A340" s="15" t="s">
         <v>346</v>
       </c>
       <c r="B340" s="2">
@@ -47270,7 +48536,7 @@
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A341" s="10" t="s">
+      <c r="A341" s="15" t="s">
         <v>347</v>
       </c>
       <c r="B341" s="2">
@@ -47296,7 +48562,7 @@
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A342" s="11" t="s">
+      <c r="A342" s="16" t="s">
         <v>348</v>
       </c>
       <c r="B342" s="5">
@@ -47322,7 +48588,7 @@
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A343" s="11" t="s">
+      <c r="A343" s="16" t="s">
         <v>349</v>
       </c>
       <c r="B343" s="5">
@@ -47348,7 +48614,7 @@
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
+      <c r="A344" s="15" t="s">
         <v>350</v>
       </c>
       <c r="B344" s="2">
@@ -47374,7 +48640,7 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
+      <c r="A345" s="15" t="s">
         <v>351</v>
       </c>
       <c r="B345" s="2">
@@ -47540,25 +48806,91 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020ECA8C-2A49-4B51-BF90-2B13424578B4}">
-  <dimension ref="B2:E2"/>
+  <dimension ref="B4:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="11"/>
+    <col min="4" max="4" width="11.875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="8">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="8">
+        <v>200000</v>
+      </c>
+      <c r="F5" s="13">
+        <f>E5*(1-(C5+D5))</f>
+        <v>162000</v>
+      </c>
+      <c r="I5" s="8">
+        <v>100000</v>
+      </c>
+      <c r="J5" s="14">
+        <v>200000</v>
+      </c>
+      <c r="K5" s="8">
         <v>300000</v>
       </c>
-      <c r="D2" s="9">
-        <f>B2/0.9</f>
-        <v>333333.33333333331</v>
-      </c>
-      <c r="E2" s="9">
-        <f>D2-D2*5%</f>
-        <v>316666.66666666663</v>
-      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="8">
+        <v>228000</v>
+      </c>
+      <c r="F6" s="13">
+        <f>E6*(1-(C6+D6))</f>
+        <v>161880</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I6" s="8">
+        <f>I5+I5*H6</f>
+        <v>114000</v>
+      </c>
+      <c r="J6" s="14">
+        <f>J5+J5*H6</f>
+        <v>228000</v>
+      </c>
+      <c r="K6" s="14">
+        <f>K5+K5*H6</f>
+        <v>342000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E7" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/백업_기준가격.xlsx
+++ b/백업_기준가격.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\hotel-code\hotel-cmscontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C87811F-61D0-4A5F-B448-131F0CEEA29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1B6EA8-D94E-4D93-A3C4-A524BB0B9CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">기준가격!$A$1:$H$346</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38141,7 +38142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="383">
   <si>
     <t>날짜</t>
   </si>
@@ -39233,6 +39234,69 @@
     <t>부킹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>2027-01-10</t>
+  </si>
+  <si>
+    <t>2027-01-11</t>
+  </si>
+  <si>
+    <t>2027-01-12</t>
+  </si>
+  <si>
+    <t>2027-01-13</t>
+  </si>
+  <si>
+    <t>2027-01-14</t>
+  </si>
+  <si>
+    <t>2027-01-15</t>
+  </si>
+  <si>
+    <t>2027-01-16</t>
+  </si>
+  <si>
+    <t>2027-01-17</t>
+  </si>
+  <si>
+    <t>2027-01-18</t>
+  </si>
+  <si>
+    <t>2027-01-19</t>
+  </si>
+  <si>
+    <t>2027-01-20</t>
+  </si>
+  <si>
+    <t>2027-01-21</t>
+  </si>
+  <si>
+    <t>2027-01-22</t>
+  </si>
+  <si>
+    <t>2027-01-23</t>
+  </si>
+  <si>
+    <t>2027-01-24</t>
+  </si>
+  <si>
+    <t>2027-01-25</t>
+  </si>
+  <si>
+    <t>2027-01-26</t>
+  </si>
+  <si>
+    <t>2027-01-27</t>
+  </si>
+  <si>
+    <t>2027-01-28</t>
+  </si>
+  <si>
+    <t>2027-01-29</t>
+  </si>
+  <si>
+    <t>2027-01-30</t>
+  </si>
 </sst>
 </file>
 
@@ -39241,7 +39305,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -39304,6 +39368,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -39355,19 +39441,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -39379,11 +39463,34 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -39687,16 +39794,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H350"/>
+  <dimension ref="A1:H555"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" style="9" customWidth="1"/>
     <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -39722,7 +39829,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2">
@@ -39748,7 +39855,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2">
@@ -39774,7 +39881,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2">
@@ -39800,7 +39907,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2">
@@ -39826,59 +39933,59 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>110000</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>130000</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>170000</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>180000</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>210000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>400000</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>500000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>120000</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>130000</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>180000</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>170000</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>220000</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>400000</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <v>500000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2">
@@ -39904,7 +40011,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2">
@@ -39930,7 +40037,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="2">
@@ -39956,7 +40063,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="2">
@@ -39982,7 +40089,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="2">
@@ -40008,59 +40115,59 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>120000</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>120000</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>170000</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>170000</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>200000</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>500000</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <v>550000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>120000</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>130000</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>180000</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>190000</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>180000</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>450000</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="3">
         <v>600000</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="2">
@@ -40086,7 +40193,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="2">
@@ -40112,7 +40219,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="2">
@@ -40138,7 +40245,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="2">
@@ -40164,7 +40271,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2">
@@ -40185,93 +40292,93 @@
       <c r="G19" s="2">
         <v>300000</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>450000</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>110000</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>120000</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>170000</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>170000</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>200000</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>400000</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>600000</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>120000</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>130000</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>190000</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>180000</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>300000</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>400000</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>600000</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>100000</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>90000</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>130000</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>110000</v>
       </c>
       <c r="F22" s="2">
         <v>200000</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>350000</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>400000</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>100000</v>
       </c>
       <c r="C23" s="2">
@@ -40286,7 +40393,7 @@
       <c r="F23" s="2">
         <v>150000</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>350000</v>
       </c>
       <c r="H23" s="2">
@@ -40294,13 +40401,13 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="2">
         <v>110000</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>90000</v>
       </c>
       <c r="D24" s="2">
@@ -40312,15 +40419,15 @@
       <c r="F24" s="2">
         <v>150000</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>350000</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>400000</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="2">
@@ -40338,15 +40445,15 @@
       <c r="F25" s="2">
         <v>150000</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>350000</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>400000</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="2">
@@ -40372,59 +40479,59 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>110000</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>120000</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>160000</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>170000</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="3">
         <v>200000</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="3">
         <v>450000</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>650000</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>120000</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>130000</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>180000</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3">
         <v>190000</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="3">
         <v>300000</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="6">
         <v>550000</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>700000</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="2">
@@ -40433,7 +40540,7 @@
       <c r="C29" s="2">
         <v>110000</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>120000</v>
       </c>
       <c r="E29" s="2">
@@ -40442,15 +40549,15 @@
       <c r="F29" s="2">
         <v>160000</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>350000</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>500000</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="2">
@@ -40468,15 +40575,15 @@
       <c r="F30" s="2">
         <v>160000</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>350000</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>300000</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="2">
@@ -40497,12 +40604,12 @@
       <c r="G31" s="2">
         <v>300000</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>300000</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="2">
@@ -40523,12 +40630,12 @@
       <c r="G32" s="2">
         <v>300000</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>450000</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="2">
@@ -40554,65 +40661,65 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>140000</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>150000</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>180000</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>180000</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="3">
         <v>180000</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="3">
         <v>500000</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="3">
         <v>600000</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>150000</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>150000</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>190000</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="3">
         <v>190000</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <v>360000</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="6">
         <v>550000</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="3">
         <v>650000</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="2">
         <v>140000</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>130000</v>
       </c>
       <c r="D36" s="2">
@@ -40632,7 +40739,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="2">
@@ -40658,7 +40765,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="2">
@@ -40684,13 +40791,13 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="2">
         <v>140000</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>140000</v>
       </c>
       <c r="D39" s="2">
@@ -40702,7 +40809,7 @@
       <c r="F39" s="2">
         <v>160000</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="5">
         <v>400000</v>
       </c>
       <c r="H39" s="2">
@@ -40710,13 +40817,13 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="2">
         <v>140000</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>130000</v>
       </c>
       <c r="D40" s="2">
@@ -40728,7 +40835,7 @@
       <c r="F40" s="2">
         <v>160000</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="5">
         <v>400000</v>
       </c>
       <c r="H40" s="2">
@@ -40736,59 +40843,59 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="3">
         <v>170000</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>150000</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>240000</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="6">
         <v>200000</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <v>380000</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="3">
         <v>400000</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="6">
         <v>700000</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>140000</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="3">
         <v>180000</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>190000</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="6">
         <v>210000</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="3">
         <v>380000</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="6">
         <v>600000</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="6">
         <v>750000</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="2">
@@ -40806,7 +40913,7 @@
       <c r="F43" s="2">
         <v>240000</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="5">
         <v>400000</v>
       </c>
       <c r="H43" s="2">
@@ -40814,7 +40921,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B44" s="2">
@@ -40832,15 +40939,15 @@
       <c r="F44" s="2">
         <v>300000</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>400000</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>550000</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="2">
@@ -40858,15 +40965,15 @@
       <c r="F45" s="2">
         <v>240000</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>400000</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>550000</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="2">
@@ -40884,15 +40991,15 @@
       <c r="F46" s="2">
         <v>240000</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>400000</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>550000</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B47" s="2">
@@ -40901,7 +41008,7 @@
       <c r="C47" s="2">
         <v>170000</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>210000</v>
       </c>
       <c r="E47" s="2">
@@ -40910,67 +41017,67 @@
       <c r="F47" s="2">
         <v>240000</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>400000</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>550000</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>180000</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="3">
         <v>190000</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>250000</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="3">
         <v>250000</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="3">
         <v>300000</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="6">
         <v>550000</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="6">
         <v>700000</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="6">
         <v>180000</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="6">
         <v>190000</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>250000</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="3">
         <v>250000</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="3">
         <v>300000</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="6">
         <v>600000</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="6">
         <v>750000</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="2">
@@ -40988,15 +41095,15 @@
       <c r="F50" s="2">
         <v>260000</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>450000</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B51" s="2">
@@ -41014,15 +41121,15 @@
       <c r="F51" s="2">
         <v>260000</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>450000</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="2">
@@ -41043,12 +41150,12 @@
       <c r="G52" s="2">
         <v>450000</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B53" s="2">
@@ -41074,13 +41181,13 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B54" s="2">
         <v>170000</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>170000</v>
       </c>
       <c r="D54" s="2">
@@ -41095,82 +41202,82 @@
       <c r="G54" s="2">
         <v>450000</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>150000</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="6">
         <v>160000</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>210000</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="6">
         <v>270000</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="3">
         <v>380000</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="3">
         <v>600000</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="6">
         <v>750000</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>150000</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>160000</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>240000</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="6">
         <v>270000</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="6">
         <v>380000</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="6">
         <v>700000</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="6">
         <v>850000</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B57" s="2">
         <v>170000</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>140000</v>
       </c>
       <c r="D57" s="2">
         <v>210000</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="5">
         <v>180000</v>
       </c>
       <c r="F57" s="2">
         <v>380000</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>450000</v>
       </c>
       <c r="H57" s="2">
@@ -41178,13 +41285,13 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="9" t="s">
         <v>64</v>
       </c>
       <c r="B58" s="2">
         <v>150000</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>140000</v>
       </c>
       <c r="D58" s="2">
@@ -41196,7 +41303,7 @@
       <c r="F58" s="2">
         <v>380000</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="5">
         <v>450000</v>
       </c>
       <c r="H58" s="2">
@@ -41204,7 +41311,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B59" s="2">
@@ -41230,7 +41337,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B60" s="2">
@@ -41242,7 +41349,7 @@
       <c r="D60" s="2">
         <v>210000</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="5">
         <v>200000</v>
       </c>
       <c r="F60" s="2">
@@ -41251,12 +41358,12 @@
       <c r="G60" s="2">
         <v>450000</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="9" t="s">
         <v>67</v>
       </c>
       <c r="B61" s="2">
@@ -41265,7 +41372,7 @@
       <c r="C61" s="2">
         <v>170000</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>170000</v>
       </c>
       <c r="E61" s="2">
@@ -41277,70 +41384,70 @@
       <c r="G61" s="2">
         <v>450000</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>180000</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="3">
         <v>180000</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>240000</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="6">
         <v>250000</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="3">
         <v>380000</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G62" s="3">
         <v>600000</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="6">
         <v>750000</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="6">
         <v>150000</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="6">
         <v>160000</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="3">
         <v>230000</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="6">
         <v>250000</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="6">
         <v>380000</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="6">
         <v>700000</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="6">
         <v>850000</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B64" s="2">
         <v>160000</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>140000</v>
       </c>
       <c r="D64" s="2">
@@ -41352,7 +41459,7 @@
       <c r="F64" s="2">
         <v>380000</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="5">
         <v>550000</v>
       </c>
       <c r="H64" s="2">
@@ -41360,7 +41467,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="9" t="s">
         <v>71</v>
       </c>
       <c r="B65" s="2">
@@ -41378,7 +41485,7 @@
       <c r="F65" s="2">
         <v>260000</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>550000</v>
       </c>
       <c r="H65" s="2">
@@ -41386,7 +41493,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B66" s="2">
@@ -41404,15 +41511,15 @@
       <c r="F66" s="2">
         <v>380000</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>550000</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B67" s="2">
@@ -41438,7 +41545,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B68" s="2">
@@ -41464,74 +41571,74 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="6">
         <v>150000</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="6">
         <v>160000</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="6">
         <v>240000</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="6">
         <v>240000</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="3">
         <v>300000</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69" s="3">
         <v>700000</v>
       </c>
-      <c r="H69" s="4">
+      <c r="H69" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="6">
         <v>150000</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="6">
         <v>160000</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>220000</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="6">
         <v>240000</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="6">
         <v>380000</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="3">
         <v>750000</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="9" t="s">
         <v>77</v>
       </c>
       <c r="B71" s="2">
         <v>170000</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>140000</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="5">
         <v>180000</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="5">
         <v>180000</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="5">
         <v>350000</v>
       </c>
       <c r="G71" s="2">
@@ -41542,19 +41649,19 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B72" s="5">
         <v>130000</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>140000</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="5">
         <v>180000</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="5">
         <v>180000</v>
       </c>
       <c r="F72" s="2">
@@ -41568,7 +41675,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="9" t="s">
         <v>79</v>
       </c>
       <c r="B73" s="2">
@@ -41580,7 +41687,7 @@
       <c r="D73" s="2">
         <v>210000</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="5">
         <v>180000</v>
       </c>
       <c r="F73" s="2">
@@ -41594,13 +41701,13 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="6">
+      <c r="B74" s="5">
         <v>130000</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>140000</v>
       </c>
       <c r="D74" s="2">
@@ -41615,93 +41722,93 @@
       <c r="G74" s="2">
         <v>550000</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H74" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75" s="5">
         <v>130000</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>140000</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="5">
         <v>180000</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="5">
         <v>180000</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="5">
         <v>210000</v>
       </c>
       <c r="G75" s="2">
         <v>550000</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H75" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="6">
         <v>150000</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="6">
         <v>160000</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>260000</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E76" s="6">
         <v>240000</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="6">
         <v>270000</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="6">
         <v>700000</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="6">
         <v>850000</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="6">
         <v>150000</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="3">
         <v>160000</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="3">
         <v>260000</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E77" s="6">
         <v>260000</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="6">
         <v>270000</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="6">
         <v>750000</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H77" s="6">
         <v>900000</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="6">
+      <c r="B78" s="5">
         <v>160000</v>
       </c>
       <c r="C78" s="2">
@@ -41713,21 +41820,21 @@
       <c r="E78" s="2">
         <v>230000</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="5">
         <v>210000</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="5">
         <v>550000</v>
       </c>
-      <c r="H78" s="6">
+      <c r="H78" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="5">
         <v>160000</v>
       </c>
       <c r="C79" s="2">
@@ -41742,21 +41849,21 @@
       <c r="F79" s="2">
         <v>260000</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="5">
         <v>550000</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H79" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B80" s="2">
         <v>170000</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>140000</v>
       </c>
       <c r="D80" s="2">
@@ -41768,7 +41875,7 @@
       <c r="F80" s="2">
         <v>260000</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G80" s="5">
         <v>550000</v>
       </c>
       <c r="H80" s="2">
@@ -41776,10 +41883,10 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="5">
         <v>150000</v>
       </c>
       <c r="C81" s="2">
@@ -41802,7 +41909,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="15" t="s">
+      <c r="A82" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B82" s="2">
@@ -41820,7 +41927,7 @@
       <c r="F82" s="2">
         <v>260000</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="5">
         <v>550000</v>
       </c>
       <c r="H82" s="2">
@@ -41828,65 +41935,65 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83" s="4">
         <v>180000</v>
       </c>
-      <c r="C83" s="5">
+      <c r="C83" s="4">
         <v>190000</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="3">
         <v>260000</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="3">
         <v>270000</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="3">
         <v>320000</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="6">
         <v>700000</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="6">
         <v>850000</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B84" s="4">
         <v>180000</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="6">
         <v>150000</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>260000</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="3">
         <v>270000</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="3">
         <v>380000</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="6">
         <v>750000</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="6">
         <v>900000</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="5">
         <v>160000</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>150000</v>
       </c>
       <c r="D85" s="2">
@@ -41898,21 +42005,21 @@
       <c r="F85" s="2">
         <v>350000</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G85" s="5">
         <v>550000</v>
       </c>
-      <c r="H85" s="6">
+      <c r="H85" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="9" t="s">
         <v>92</v>
       </c>
       <c r="B86" s="2">
         <v>160000</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>140000</v>
       </c>
       <c r="D86" s="2">
@@ -41924,21 +42031,21 @@
       <c r="F86" s="2">
         <v>260000</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="5">
         <v>550000</v>
       </c>
-      <c r="H86" s="6">
+      <c r="H86" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="9" t="s">
         <v>93</v>
       </c>
       <c r="B87" s="2">
         <v>160000</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>140000</v>
       </c>
       <c r="D87" s="2">
@@ -41953,12 +42060,12 @@
       <c r="G87" s="2">
         <v>550000</v>
       </c>
-      <c r="H87" s="6">
+      <c r="H87" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B88" s="2">
@@ -41967,7 +42074,7 @@
       <c r="C88" s="2">
         <v>190000</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="5">
         <v>170000</v>
       </c>
       <c r="E88" s="2">
@@ -41979,12 +42086,12 @@
       <c r="G88" s="2">
         <v>550000</v>
       </c>
-      <c r="H88" s="6">
+      <c r="H88" s="5">
         <v>700000</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="9" t="s">
         <v>95</v>
       </c>
       <c r="B89" s="2">
@@ -41993,10 +42100,10 @@
       <c r="C89" s="2">
         <v>190000</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="5">
         <v>170000</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="5">
         <v>180000</v>
       </c>
       <c r="F89" s="2">
@@ -42010,65 +42117,65 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90" s="4">
         <v>180000</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="3">
         <v>210000</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>220000</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="6">
         <v>240000</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="3">
         <v>320000</v>
       </c>
-      <c r="G90" s="4">
+      <c r="G90" s="3">
         <v>700000</v>
       </c>
-      <c r="H90" s="4">
+      <c r="H90" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91" s="4">
         <v>180000</v>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="6">
         <v>160000</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="3">
         <v>260000</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E91" s="6">
         <v>240000</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="3">
         <v>320000</v>
       </c>
-      <c r="G91" s="4">
+      <c r="G91" s="3">
         <v>800000</v>
       </c>
-      <c r="H91" s="4">
+      <c r="H91" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B92" s="2">
         <v>160000</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>140000</v>
       </c>
       <c r="D92" s="2">
@@ -42077,7 +42184,7 @@
       <c r="E92" s="2">
         <v>230000</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="5">
         <v>350000</v>
       </c>
       <c r="G92" s="2">
@@ -42088,13 +42195,13 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B93" s="2">
         <v>160000</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>140000</v>
       </c>
       <c r="D93" s="2">
@@ -42103,7 +42210,7 @@
       <c r="E93" s="2">
         <v>230000</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="5">
         <v>350000</v>
       </c>
       <c r="G93" s="2">
@@ -42114,13 +42221,13 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B94" s="2">
         <v>160000</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>140000</v>
       </c>
       <c r="D94" s="2">
@@ -42140,7 +42247,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="9" t="s">
         <v>101</v>
       </c>
       <c r="B95" s="2">
@@ -42166,7 +42273,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="9" t="s">
         <v>102</v>
       </c>
       <c r="B96" s="2">
@@ -42178,7 +42285,7 @@
       <c r="D96" s="2">
         <v>210000</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="5">
         <v>180000</v>
       </c>
       <c r="F96" s="2">
@@ -42192,74 +42299,74 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="3">
         <v>180000</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="6">
         <v>160000</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="3">
         <v>260000</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E97" s="3">
         <v>270000</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="3">
         <v>400000</v>
       </c>
-      <c r="G97" s="4">
+      <c r="G97" s="3">
         <v>650000</v>
       </c>
-      <c r="H97" s="4">
+      <c r="H97" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="3">
         <v>180000</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="6">
         <v>160000</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>260000</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="6">
         <v>240000</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F98" s="6">
         <v>380000</v>
       </c>
-      <c r="G98" s="4">
+      <c r="G98" s="3">
         <v>700000</v>
       </c>
-      <c r="H98" s="4">
+      <c r="H98" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="9" t="s">
         <v>105</v>
       </c>
       <c r="B99" s="2">
         <v>160000</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>140000</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="5">
         <v>180000</v>
       </c>
       <c r="E99" s="2">
         <v>230000</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="5">
         <v>350000</v>
       </c>
       <c r="G99" s="2">
@@ -42270,19 +42377,19 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B100" s="5">
         <v>120000</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>140000</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="5">
         <v>170000</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="5">
         <v>190000</v>
       </c>
       <c r="F100" s="2">
@@ -42296,7 +42403,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B101" s="2">
@@ -42322,13 +42429,13 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="9" t="s">
         <v>108</v>
       </c>
       <c r="B102" s="2">
         <v>160000</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>140000</v>
       </c>
       <c r="D102" s="2">
@@ -42348,13 +42455,13 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="9" t="s">
         <v>109</v>
       </c>
       <c r="B103" s="2">
         <v>160000</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>140000</v>
       </c>
       <c r="D103" s="2">
@@ -42374,59 +42481,59 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="3">
         <v>180000</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="6">
         <v>160000</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="3">
         <v>240000</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="3">
         <v>260000</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="3">
         <v>300000</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="3">
         <v>650000</v>
       </c>
-      <c r="H104" s="4">
+      <c r="H104" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="3">
         <v>180000</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="6">
         <v>160000</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="3">
         <v>240000</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="3">
         <v>260000</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="3">
         <v>300000</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="3">
         <v>700000</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B106" s="2">
@@ -42452,13 +42559,13 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="9" t="s">
         <v>113</v>
       </c>
       <c r="B107" s="2">
         <v>160000</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>130000</v>
       </c>
       <c r="D107" s="2">
@@ -42478,7 +42585,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="9" t="s">
         <v>114</v>
       </c>
       <c r="B108" s="2">
@@ -42504,7 +42611,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="9" t="s">
         <v>115</v>
       </c>
       <c r="B109" s="2">
@@ -42530,7 +42637,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="9" t="s">
         <v>116</v>
       </c>
       <c r="B110" s="2">
@@ -42556,71 +42663,71 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="3">
         <v>150000</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="3">
         <v>170000</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="3">
         <v>240000</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E111" s="6">
         <v>250000</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="3">
         <v>300000</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="3">
         <v>650000</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H111" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="6">
         <v>140000</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="6">
         <v>150000</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="3">
         <v>240000</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="3">
         <v>260000</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="3">
         <v>300000</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="3">
         <v>700000</v>
       </c>
-      <c r="H112" s="4">
+      <c r="H112" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="9" t="s">
         <v>119</v>
       </c>
       <c r="B113" s="2">
         <v>140000</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>120000</v>
       </c>
       <c r="D113" s="2">
         <v>180000</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="5">
         <v>160000</v>
       </c>
       <c r="F113" s="2">
@@ -42634,7 +42741,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="9" t="s">
         <v>120</v>
       </c>
       <c r="B114" s="2">
@@ -42660,7 +42767,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="9" t="s">
         <v>121</v>
       </c>
       <c r="B115" s="2">
@@ -42686,7 +42793,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B116" s="2">
@@ -42712,7 +42819,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="9" t="s">
         <v>123</v>
       </c>
       <c r="B117" s="2">
@@ -42724,7 +42831,7 @@
       <c r="D117" s="2">
         <v>180000</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="5">
         <v>140000</v>
       </c>
       <c r="F117" s="2">
@@ -42738,65 +42845,65 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="3">
         <v>180000</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="3">
         <v>190000</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118" s="3">
         <v>240000</v>
       </c>
-      <c r="E118" s="7">
+      <c r="E118" s="6">
         <v>210000</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="3">
         <v>300000</v>
       </c>
-      <c r="G118" s="4">
+      <c r="G118" s="3">
         <v>650000</v>
       </c>
-      <c r="H118" s="4">
+      <c r="H118" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="6">
         <v>140000</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="6">
         <v>150000</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="3">
         <v>240000</v>
       </c>
-      <c r="E119" s="7">
+      <c r="E119" s="6">
         <v>200000</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="3">
         <v>300000</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="3">
         <v>700000</v>
       </c>
-      <c r="H119" s="4">
+      <c r="H119" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="9" t="s">
         <v>126</v>
       </c>
       <c r="B120" s="2">
         <v>140000</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>160000</v>
       </c>
       <c r="D120" s="2">
@@ -42816,13 +42923,13 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="9" t="s">
         <v>127</v>
       </c>
       <c r="B121" s="2">
         <v>140000</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>160000</v>
       </c>
       <c r="D121" s="2">
@@ -42842,7 +42949,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="9" t="s">
         <v>128</v>
       </c>
       <c r="B122" s="2">
@@ -42868,7 +42975,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="9" t="s">
         <v>129</v>
       </c>
       <c r="B123" s="2">
@@ -42894,13 +43001,13 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="9" t="s">
         <v>130</v>
       </c>
       <c r="B124" s="2">
         <v>140000</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>160000</v>
       </c>
       <c r="D124" s="2">
@@ -42920,59 +43027,59 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="3">
         <v>150000</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="6">
         <v>190000</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125" s="3">
         <v>240000</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E125" s="3">
         <v>250000</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="3">
         <v>300000</v>
       </c>
-      <c r="G125" s="4">
+      <c r="G125" s="3">
         <v>650000</v>
       </c>
-      <c r="H125" s="4">
+      <c r="H125" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="6">
         <v>150000</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="6">
         <v>190000</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126" s="3">
         <v>240000</v>
       </c>
-      <c r="E126" s="4">
+      <c r="E126" s="3">
         <v>250000</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="3">
         <v>300000</v>
       </c>
-      <c r="G126" s="4">
+      <c r="G126" s="3">
         <v>700000</v>
       </c>
-      <c r="H126" s="4">
+      <c r="H126" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="9" t="s">
         <v>133</v>
       </c>
       <c r="B127" s="2">
@@ -42998,33 +43105,33 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="9" t="s">
+      <c r="A128" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B128" s="17">
+      <c r="B128" s="13">
         <v>140000</v>
       </c>
-      <c r="C128" s="17">
+      <c r="C128" s="13">
         <v>160000</v>
       </c>
-      <c r="D128" s="17">
+      <c r="D128" s="13">
         <v>180000</v>
       </c>
-      <c r="E128" s="17">
+      <c r="E128" s="13">
         <v>180000</v>
       </c>
-      <c r="F128" s="17">
+      <c r="F128" s="13">
         <v>230000</v>
       </c>
-      <c r="G128" s="17">
+      <c r="G128" s="13">
         <v>450000</v>
       </c>
-      <c r="H128" s="17">
+      <c r="H128" s="13">
         <v>600000</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="9" t="s">
         <v>135</v>
       </c>
       <c r="B129" s="2">
@@ -43050,7 +43157,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B130" s="2">
@@ -43076,7 +43183,7 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131" s="9" t="s">
         <v>137</v>
       </c>
       <c r="B131" s="2">
@@ -43102,77 +43209,77 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="3">
         <v>170000</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132" s="3">
         <v>190000</v>
       </c>
-      <c r="D132" s="4">
+      <c r="D132" s="3">
         <v>240000</v>
       </c>
-      <c r="E132" s="4">
+      <c r="E132" s="3">
         <v>250000</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="3">
         <v>300000</v>
       </c>
-      <c r="G132" s="4">
+      <c r="G132" s="3">
         <v>600000</v>
       </c>
-      <c r="H132" s="4">
+      <c r="H132" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="3">
         <v>170000</v>
       </c>
-      <c r="C133" s="18">
+      <c r="C133" s="3">
         <v>190000</v>
       </c>
-      <c r="D133" s="18">
+      <c r="D133" s="3">
         <v>240000</v>
       </c>
-      <c r="E133" s="18">
+      <c r="E133" s="3">
         <v>250000</v>
       </c>
-      <c r="F133" s="18">
+      <c r="F133" s="3">
         <v>300000</v>
       </c>
-      <c r="G133" s="18">
+      <c r="G133" s="3">
         <v>700000</v>
       </c>
-      <c r="H133" s="4">
+      <c r="H133" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B134" s="19">
+      <c r="B134" s="2">
         <v>140000</v>
       </c>
-      <c r="C134" s="19">
+      <c r="C134" s="2">
         <v>160000</v>
       </c>
-      <c r="D134" s="19">
+      <c r="D134" s="2">
         <v>180000</v>
       </c>
-      <c r="E134" s="19">
+      <c r="E134" s="2">
         <v>200000</v>
       </c>
-      <c r="F134" s="19">
+      <c r="F134" s="2">
         <v>230000</v>
       </c>
-      <c r="G134" s="19">
+      <c r="G134" s="2">
         <v>450000</v>
       </c>
       <c r="H134" s="2">
@@ -43180,25 +43287,25 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B135" s="19">
+      <c r="B135" s="2">
         <v>140000</v>
       </c>
-      <c r="C135" s="19">
+      <c r="C135" s="2">
         <v>160000</v>
       </c>
-      <c r="D135" s="19">
+      <c r="D135" s="2">
         <v>180000</v>
       </c>
-      <c r="E135" s="19">
+      <c r="E135" s="2">
         <v>200000</v>
       </c>
-      <c r="F135" s="19">
+      <c r="F135" s="2">
         <v>230000</v>
       </c>
-      <c r="G135" s="19">
+      <c r="G135" s="2">
         <v>450000</v>
       </c>
       <c r="H135" s="2">
@@ -43206,25 +43313,25 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B136" s="19">
+      <c r="B136" s="2">
         <v>140000</v>
       </c>
-      <c r="C136" s="19">
+      <c r="C136" s="2">
         <v>160000</v>
       </c>
-      <c r="D136" s="19">
+      <c r="D136" s="2">
         <v>180000</v>
       </c>
-      <c r="E136" s="19">
+      <c r="E136" s="2">
         <v>200000</v>
       </c>
-      <c r="F136" s="19">
+      <c r="F136" s="2">
         <v>230000</v>
       </c>
-      <c r="G136" s="19">
+      <c r="G136" s="2">
         <v>450000</v>
       </c>
       <c r="H136" s="2">
@@ -43232,25 +43339,25 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B137" s="19">
+      <c r="B137" s="2">
         <v>140000</v>
       </c>
-      <c r="C137" s="19">
+      <c r="C137" s="2">
         <v>160000</v>
       </c>
-      <c r="D137" s="19">
+      <c r="D137" s="2">
         <v>180000</v>
       </c>
-      <c r="E137" s="19">
+      <c r="E137" s="2">
         <v>200000</v>
       </c>
-      <c r="F137" s="19">
+      <c r="F137" s="2">
         <v>230000</v>
       </c>
-      <c r="G137" s="19">
+      <c r="G137" s="2">
         <v>450000</v>
       </c>
       <c r="H137" s="2">
@@ -43258,25 +43365,25 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B138" s="19">
+      <c r="B138" s="2">
         <v>140000</v>
       </c>
-      <c r="C138" s="19">
+      <c r="C138" s="2">
         <v>160000</v>
       </c>
-      <c r="D138" s="19">
+      <c r="D138" s="2">
         <v>180000</v>
       </c>
-      <c r="E138" s="19">
+      <c r="E138" s="2">
         <v>200000</v>
       </c>
-      <c r="F138" s="19">
+      <c r="F138" s="2">
         <v>230000</v>
       </c>
-      <c r="G138" s="19">
+      <c r="G138" s="2">
         <v>450000</v>
       </c>
       <c r="H138" s="2">
@@ -43284,77 +43391,77 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B139" s="18">
+      <c r="B139" s="3">
         <v>170000</v>
       </c>
-      <c r="C139" s="18">
+      <c r="C139" s="3">
         <v>190000</v>
       </c>
-      <c r="D139" s="18">
+      <c r="D139" s="3">
         <v>240000</v>
       </c>
-      <c r="E139" s="18">
+      <c r="E139" s="3">
         <v>250000</v>
       </c>
-      <c r="F139" s="18">
+      <c r="F139" s="3">
         <v>300000</v>
       </c>
-      <c r="G139" s="18">
+      <c r="G139" s="3">
         <v>650000</v>
       </c>
-      <c r="H139" s="4">
+      <c r="H139" s="3">
         <v>800000</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B140" s="18">
+      <c r="B140" s="3">
         <v>170000</v>
       </c>
-      <c r="C140" s="18">
+      <c r="C140" s="3">
         <v>190000</v>
       </c>
-      <c r="D140" s="18">
+      <c r="D140" s="3">
         <v>240000</v>
       </c>
-      <c r="E140" s="18">
+      <c r="E140" s="3">
         <v>250000</v>
       </c>
-      <c r="F140" s="18">
+      <c r="F140" s="3">
         <v>300000</v>
       </c>
-      <c r="G140" s="18">
+      <c r="G140" s="3">
         <v>700000</v>
       </c>
-      <c r="H140" s="4">
+      <c r="H140" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B141" s="19">
+      <c r="B141" s="2">
         <v>140000</v>
       </c>
-      <c r="C141" s="19">
+      <c r="C141" s="2">
         <v>160000</v>
       </c>
-      <c r="D141" s="19">
+      <c r="D141" s="2">
         <v>180000</v>
       </c>
-      <c r="E141" s="19">
+      <c r="E141" s="2">
         <v>210000</v>
       </c>
-      <c r="F141" s="19">
+      <c r="F141" s="2">
         <v>230000</v>
       </c>
-      <c r="G141" s="19">
+      <c r="G141" s="2">
         <v>450000</v>
       </c>
       <c r="H141" s="2">
@@ -43362,25 +43469,25 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="A142" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B142" s="19">
+      <c r="B142" s="2">
         <v>140000</v>
       </c>
-      <c r="C142" s="19">
+      <c r="C142" s="2">
         <v>160000</v>
       </c>
-      <c r="D142" s="19">
+      <c r="D142" s="2">
         <v>180000</v>
       </c>
-      <c r="E142" s="19">
+      <c r="E142" s="2">
         <v>210000</v>
       </c>
-      <c r="F142" s="19">
+      <c r="F142" s="2">
         <v>230000</v>
       </c>
-      <c r="G142" s="19">
+      <c r="G142" s="2">
         <v>450000</v>
       </c>
       <c r="H142" s="2">
@@ -43388,25 +43495,25 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="A143" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B143" s="19">
+      <c r="B143" s="2">
         <v>140000</v>
       </c>
-      <c r="C143" s="19">
+      <c r="C143" s="2">
         <v>160000</v>
       </c>
-      <c r="D143" s="19">
+      <c r="D143" s="2">
         <v>190000</v>
       </c>
-      <c r="E143" s="19">
+      <c r="E143" s="2">
         <v>210000</v>
       </c>
-      <c r="F143" s="19">
+      <c r="F143" s="2">
         <v>240000</v>
       </c>
-      <c r="G143" s="19">
+      <c r="G143" s="2">
         <v>450000</v>
       </c>
       <c r="H143" s="2">
@@ -43414,25 +43521,25 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="A144" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B144" s="19">
+      <c r="B144" s="2">
         <v>140000</v>
       </c>
-      <c r="C144" s="19">
+      <c r="C144" s="2">
         <v>160000</v>
       </c>
-      <c r="D144" s="19">
+      <c r="D144" s="2">
         <v>190000</v>
       </c>
-      <c r="E144" s="19">
+      <c r="E144" s="2">
         <v>210000</v>
       </c>
-      <c r="F144" s="19">
+      <c r="F144" s="2">
         <v>240000</v>
       </c>
-      <c r="G144" s="19">
+      <c r="G144" s="2">
         <v>450000</v>
       </c>
       <c r="H144" s="2">
@@ -43440,25 +43547,25 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="A145" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B145" s="19">
+      <c r="B145" s="2">
         <v>140000</v>
       </c>
-      <c r="C145" s="19">
+      <c r="C145" s="2">
         <v>160000</v>
       </c>
-      <c r="D145" s="19">
+      <c r="D145" s="2">
         <v>190000</v>
       </c>
-      <c r="E145" s="19">
+      <c r="E145" s="2">
         <v>210000</v>
       </c>
-      <c r="F145" s="19">
+      <c r="F145" s="2">
         <v>240000</v>
       </c>
-      <c r="G145" s="19">
+      <c r="G145" s="2">
         <v>450000</v>
       </c>
       <c r="H145" s="2">
@@ -43466,77 +43573,77 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+      <c r="A146" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B146" s="18">
+      <c r="B146" s="3">
         <v>180000</v>
       </c>
-      <c r="C146" s="18">
+      <c r="C146" s="3">
         <v>190000</v>
       </c>
-      <c r="D146" s="18">
+      <c r="D146" s="3">
         <v>240000</v>
       </c>
-      <c r="E146" s="18">
+      <c r="E146" s="3">
         <v>250000</v>
       </c>
-      <c r="F146" s="18">
+      <c r="F146" s="3">
         <v>300000</v>
       </c>
-      <c r="G146" s="18">
+      <c r="G146" s="3">
         <v>600000</v>
       </c>
-      <c r="H146" s="4">
+      <c r="H146" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="A147" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B147" s="18">
+      <c r="B147" s="3">
         <v>180000</v>
       </c>
-      <c r="C147" s="18">
+      <c r="C147" s="3">
         <v>190000</v>
       </c>
-      <c r="D147" s="18">
+      <c r="D147" s="3">
         <v>240000</v>
       </c>
-      <c r="E147" s="18">
+      <c r="E147" s="3">
         <v>250000</v>
       </c>
-      <c r="F147" s="18">
+      <c r="F147" s="3">
         <v>300000</v>
       </c>
-      <c r="G147" s="18">
+      <c r="G147" s="3">
         <v>700000</v>
       </c>
-      <c r="H147" s="4">
+      <c r="H147" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="A148" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B148" s="19">
+      <c r="B148" s="2">
         <v>160000</v>
       </c>
-      <c r="C148" s="19">
+      <c r="C148" s="2">
         <v>170000</v>
       </c>
-      <c r="D148" s="19">
+      <c r="D148" s="2">
         <v>190000</v>
       </c>
-      <c r="E148" s="19">
+      <c r="E148" s="2">
         <v>210000</v>
       </c>
-      <c r="F148" s="19">
+      <c r="F148" s="2">
         <v>240000</v>
       </c>
-      <c r="G148" s="19">
+      <c r="G148" s="2">
         <v>450000</v>
       </c>
       <c r="H148" s="2">
@@ -43544,25 +43651,25 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+      <c r="A149" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B149" s="19">
+      <c r="B149" s="2">
         <v>160000</v>
       </c>
-      <c r="C149" s="19">
+      <c r="C149" s="2">
         <v>170000</v>
       </c>
-      <c r="D149" s="19">
+      <c r="D149" s="2">
         <v>190000</v>
       </c>
-      <c r="E149" s="19">
+      <c r="E149" s="2">
         <v>210000</v>
       </c>
-      <c r="F149" s="19">
+      <c r="F149" s="2">
         <v>240000</v>
       </c>
-      <c r="G149" s="19">
+      <c r="G149" s="2">
         <v>450000</v>
       </c>
       <c r="H149" s="2">
@@ -43570,25 +43677,25 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="A150" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B150" s="19">
+      <c r="B150" s="2">
         <v>160000</v>
       </c>
-      <c r="C150" s="19">
+      <c r="C150" s="2">
         <v>170000</v>
       </c>
-      <c r="D150" s="19">
+      <c r="D150" s="2">
         <v>190000</v>
       </c>
-      <c r="E150" s="19">
+      <c r="E150" s="2">
         <v>210000</v>
       </c>
-      <c r="F150" s="19">
+      <c r="F150" s="2">
         <v>240000</v>
       </c>
-      <c r="G150" s="19">
+      <c r="G150" s="2">
         <v>450000</v>
       </c>
       <c r="H150" s="2">
@@ -43596,25 +43703,25 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="A151" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B151" s="19">
+      <c r="B151" s="2">
         <v>160000</v>
       </c>
-      <c r="C151" s="19">
+      <c r="C151" s="2">
         <v>170000</v>
       </c>
-      <c r="D151" s="19">
+      <c r="D151" s="2">
         <v>190000</v>
       </c>
-      <c r="E151" s="19">
+      <c r="E151" s="2">
         <v>210000</v>
       </c>
-      <c r="F151" s="19">
+      <c r="F151" s="2">
         <v>240000</v>
       </c>
-      <c r="G151" s="19">
+      <c r="G151" s="2">
         <v>450000</v>
       </c>
       <c r="H151" s="2">
@@ -43622,25 +43729,25 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="A152" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B152" s="19">
+      <c r="B152" s="2">
         <v>160000</v>
       </c>
-      <c r="C152" s="19">
+      <c r="C152" s="2">
         <v>170000</v>
       </c>
-      <c r="D152" s="19">
+      <c r="D152" s="2">
         <v>190000</v>
       </c>
-      <c r="E152" s="19">
+      <c r="E152" s="2">
         <v>210000</v>
       </c>
-      <c r="F152" s="19">
+      <c r="F152" s="2">
         <v>240000</v>
       </c>
-      <c r="G152" s="19">
+      <c r="G152" s="2">
         <v>450000</v>
       </c>
       <c r="H152" s="2">
@@ -43648,77 +43755,77 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B153" s="18">
+      <c r="B153" s="3">
         <v>180000</v>
       </c>
-      <c r="C153" s="18">
+      <c r="C153" s="3">
         <v>190000</v>
       </c>
-      <c r="D153" s="18">
+      <c r="D153" s="3">
         <v>240000</v>
       </c>
-      <c r="E153" s="18">
+      <c r="E153" s="3">
         <v>250000</v>
       </c>
-      <c r="F153" s="18">
+      <c r="F153" s="3">
         <v>300000</v>
       </c>
-      <c r="G153" s="18">
+      <c r="G153" s="3">
         <v>600000</v>
       </c>
-      <c r="H153" s="4">
+      <c r="H153" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+      <c r="A154" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B154" s="18">
+      <c r="B154" s="3">
         <v>180000</v>
       </c>
-      <c r="C154" s="18">
+      <c r="C154" s="3">
         <v>190000</v>
       </c>
-      <c r="D154" s="18">
+      <c r="D154" s="3">
         <v>240000</v>
       </c>
-      <c r="E154" s="18">
+      <c r="E154" s="3">
         <v>250000</v>
       </c>
-      <c r="F154" s="18">
+      <c r="F154" s="3">
         <v>300000</v>
       </c>
-      <c r="G154" s="18">
+      <c r="G154" s="3">
         <v>700000</v>
       </c>
-      <c r="H154" s="4">
+      <c r="H154" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="A155" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B155" s="19">
+      <c r="B155" s="2">
         <v>160000</v>
       </c>
-      <c r="C155" s="19">
+      <c r="C155" s="2">
         <v>170000</v>
       </c>
-      <c r="D155" s="19">
+      <c r="D155" s="2">
         <v>190000</v>
       </c>
-      <c r="E155" s="19">
+      <c r="E155" s="2">
         <v>210000</v>
       </c>
-      <c r="F155" s="19">
+      <c r="F155" s="2">
         <v>240000</v>
       </c>
-      <c r="G155" s="19">
+      <c r="G155" s="2">
         <v>450000</v>
       </c>
       <c r="H155" s="2">
@@ -43726,7 +43833,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156" s="9" t="s">
         <v>162</v>
       </c>
       <c r="B156" s="2">
@@ -43752,7 +43859,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="A157" s="9" t="s">
         <v>163</v>
       </c>
       <c r="B157" s="2">
@@ -43778,7 +43885,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="A158" s="9" t="s">
         <v>164</v>
       </c>
       <c r="B158" s="2">
@@ -43804,7 +43911,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="A159" s="9" t="s">
         <v>165</v>
       </c>
       <c r="B159" s="2">
@@ -43830,59 +43937,59 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+      <c r="A160" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="3">
         <v>180000</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160" s="3">
         <v>190000</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160" s="3">
         <v>240000</v>
       </c>
-      <c r="E160" s="4">
+      <c r="E160" s="3">
         <v>250000</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="3">
         <v>300000</v>
       </c>
-      <c r="G160" s="4">
+      <c r="G160" s="3">
         <v>600000</v>
       </c>
-      <c r="H160" s="4">
+      <c r="H160" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="A161" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="3">
         <v>160000</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161" s="3">
         <v>170000</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161" s="3">
         <v>240000</v>
       </c>
-      <c r="E161" s="4">
+      <c r="E161" s="3">
         <v>250000</v>
       </c>
-      <c r="F161" s="4">
+      <c r="F161" s="3">
         <v>300000</v>
       </c>
-      <c r="G161" s="4">
+      <c r="G161" s="3">
         <v>700000</v>
       </c>
-      <c r="H161" s="4">
+      <c r="H161" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+      <c r="A162" s="9" t="s">
         <v>168</v>
       </c>
       <c r="B162" s="2">
@@ -43903,12 +44010,12 @@
       <c r="G162" s="2">
         <v>450000</v>
       </c>
-      <c r="H162" s="6">
+      <c r="H162" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+      <c r="A163" s="9" t="s">
         <v>169</v>
       </c>
       <c r="B163" s="2">
@@ -43929,12 +44036,12 @@
       <c r="G163" s="2">
         <v>450000</v>
       </c>
-      <c r="H163" s="6">
+      <c r="H163" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+      <c r="A164" s="9" t="s">
         <v>170</v>
       </c>
       <c r="B164" s="2">
@@ -43960,7 +44067,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+      <c r="A165" s="9" t="s">
         <v>171</v>
       </c>
       <c r="B165" s="2">
@@ -43986,7 +44093,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="A166" s="9" t="s">
         <v>172</v>
       </c>
       <c r="B166" s="2">
@@ -44012,59 +44119,59 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="A167" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="3">
         <v>160000</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167" s="3">
         <v>170000</v>
       </c>
-      <c r="D167" s="4">
+      <c r="D167" s="3">
         <v>240000</v>
       </c>
-      <c r="E167" s="4">
+      <c r="E167" s="3">
         <v>250000</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="3">
         <v>300000</v>
       </c>
-      <c r="G167" s="4">
+      <c r="G167" s="3">
         <v>600000</v>
       </c>
-      <c r="H167" s="4">
+      <c r="H167" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="A168" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="3">
         <v>160000</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168" s="3">
         <v>170000</v>
       </c>
-      <c r="D168" s="4">
+      <c r="D168" s="3">
         <v>240000</v>
       </c>
-      <c r="E168" s="4">
+      <c r="E168" s="3">
         <v>250000</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="3">
         <v>300000</v>
       </c>
-      <c r="G168" s="4">
+      <c r="G168" s="3">
         <v>700000</v>
       </c>
-      <c r="H168" s="4">
+      <c r="H168" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="A169" s="9" t="s">
         <v>175</v>
       </c>
       <c r="B169" s="2">
@@ -44090,7 +44197,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+      <c r="A170" s="9" t="s">
         <v>176</v>
       </c>
       <c r="B170" s="2">
@@ -44116,7 +44223,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+      <c r="A171" s="9" t="s">
         <v>177</v>
       </c>
       <c r="B171" s="2">
@@ -44142,7 +44249,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+      <c r="A172" s="9" t="s">
         <v>178</v>
       </c>
       <c r="B172" s="2">
@@ -44168,7 +44275,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+      <c r="A173" s="9" t="s">
         <v>179</v>
       </c>
       <c r="B173" s="2">
@@ -44194,59 +44301,59 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
+      <c r="A174" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="3">
         <v>160000</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174" s="3">
         <v>170000</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D174" s="3">
         <v>240000</v>
       </c>
-      <c r="E174" s="4">
+      <c r="E174" s="3">
         <v>250000</v>
       </c>
-      <c r="F174" s="4">
+      <c r="F174" s="3">
         <v>300000</v>
       </c>
-      <c r="G174" s="4">
+      <c r="G174" s="3">
         <v>600000</v>
       </c>
-      <c r="H174" s="4">
+      <c r="H174" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
+      <c r="A175" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="3">
         <v>160000</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175" s="3">
         <v>170000</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175" s="3">
         <v>240000</v>
       </c>
-      <c r="E175" s="4">
+      <c r="E175" s="3">
         <v>250000</v>
       </c>
-      <c r="F175" s="4">
+      <c r="F175" s="3">
         <v>300000</v>
       </c>
-      <c r="G175" s="4">
+      <c r="G175" s="3">
         <v>700000</v>
       </c>
-      <c r="H175" s="4">
+      <c r="H175" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="A176" s="9" t="s">
         <v>182</v>
       </c>
       <c r="B176" s="2">
@@ -44272,7 +44379,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+      <c r="A177" s="9" t="s">
         <v>183</v>
       </c>
       <c r="B177" s="2">
@@ -44298,7 +44405,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+      <c r="A178" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B178" s="2">
@@ -44324,7 +44431,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
+      <c r="A179" s="9" t="s">
         <v>185</v>
       </c>
       <c r="B179" s="2">
@@ -44350,7 +44457,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
+      <c r="A180" s="9" t="s">
         <v>186</v>
       </c>
       <c r="B180" s="2">
@@ -44376,59 +44483,59 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="3">
         <v>160000</v>
       </c>
-      <c r="C181" s="4">
+      <c r="C181" s="3">
         <v>170000</v>
       </c>
-      <c r="D181" s="4">
+      <c r="D181" s="3">
         <v>240000</v>
       </c>
-      <c r="E181" s="4">
+      <c r="E181" s="3">
         <v>250000</v>
       </c>
-      <c r="F181" s="4">
+      <c r="F181" s="3">
         <v>300000</v>
       </c>
-      <c r="G181" s="4">
+      <c r="G181" s="3">
         <v>600000</v>
       </c>
-      <c r="H181" s="4">
+      <c r="H181" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
+      <c r="A182" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="3">
         <v>160000</v>
       </c>
-      <c r="C182" s="4">
+      <c r="C182" s="3">
         <v>170000</v>
       </c>
-      <c r="D182" s="4">
+      <c r="D182" s="3">
         <v>240000</v>
       </c>
-      <c r="E182" s="4">
+      <c r="E182" s="3">
         <v>250000</v>
       </c>
-      <c r="F182" s="4">
+      <c r="F182" s="3">
         <v>300000</v>
       </c>
-      <c r="G182" s="4">
+      <c r="G182" s="3">
         <v>700000</v>
       </c>
-      <c r="H182" s="4">
+      <c r="H182" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
+      <c r="A183" s="9" t="s">
         <v>189</v>
       </c>
       <c r="B183" s="2">
@@ -44454,7 +44561,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+      <c r="A184" s="9" t="s">
         <v>190</v>
       </c>
       <c r="B184" s="2">
@@ -44480,7 +44587,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
+      <c r="A185" s="9" t="s">
         <v>191</v>
       </c>
       <c r="B185" s="2">
@@ -44506,7 +44613,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+      <c r="A186" s="9" t="s">
         <v>192</v>
       </c>
       <c r="B186" s="2">
@@ -44532,7 +44639,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
+      <c r="A187" s="9" t="s">
         <v>193</v>
       </c>
       <c r="B187" s="2">
@@ -44558,59 +44665,59 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
+      <c r="A188" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="3">
         <v>160000</v>
       </c>
-      <c r="C188" s="4">
+      <c r="C188" s="3">
         <v>170000</v>
       </c>
-      <c r="D188" s="4">
+      <c r="D188" s="3">
         <v>240000</v>
       </c>
-      <c r="E188" s="4">
+      <c r="E188" s="3">
         <v>250000</v>
       </c>
-      <c r="F188" s="4">
+      <c r="F188" s="3">
         <v>300000</v>
       </c>
-      <c r="G188" s="4">
+      <c r="G188" s="3">
         <v>600000</v>
       </c>
-      <c r="H188" s="4">
+      <c r="H188" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
+      <c r="A189" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="3">
         <v>160000</v>
       </c>
-      <c r="C189" s="4">
+      <c r="C189" s="3">
         <v>170000</v>
       </c>
-      <c r="D189" s="4">
+      <c r="D189" s="3">
         <v>240000</v>
       </c>
-      <c r="E189" s="4">
+      <c r="E189" s="3">
         <v>250000</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="3">
         <v>300000</v>
       </c>
-      <c r="G189" s="4">
+      <c r="G189" s="3">
         <v>700000</v>
       </c>
-      <c r="H189" s="4">
+      <c r="H189" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
+      <c r="A190" s="9" t="s">
         <v>196</v>
       </c>
       <c r="B190" s="2">
@@ -44636,7 +44743,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
+      <c r="A191" s="9" t="s">
         <v>197</v>
       </c>
       <c r="B191" s="2">
@@ -44662,7 +44769,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
+      <c r="A192" s="9" t="s">
         <v>198</v>
       </c>
       <c r="B192" s="2">
@@ -44688,7 +44795,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
+      <c r="A193" s="9" t="s">
         <v>199</v>
       </c>
       <c r="B193" s="2">
@@ -44709,12 +44816,12 @@
       <c r="G193" s="2">
         <v>450000</v>
       </c>
-      <c r="H193" s="6">
+      <c r="H193" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+      <c r="A194" s="9" t="s">
         <v>200</v>
       </c>
       <c r="B194" s="2">
@@ -44735,64 +44842,64 @@
       <c r="G194" s="2">
         <v>450000</v>
       </c>
-      <c r="H194" s="6">
+      <c r="H194" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
+      <c r="A195" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="3">
         <v>160000</v>
       </c>
-      <c r="C195" s="4">
+      <c r="C195" s="3">
         <v>170000</v>
       </c>
-      <c r="D195" s="4">
+      <c r="D195" s="3">
         <v>240000</v>
       </c>
-      <c r="E195" s="4">
+      <c r="E195" s="3">
         <v>250000</v>
       </c>
-      <c r="F195" s="4">
+      <c r="F195" s="3">
         <v>300000</v>
       </c>
-      <c r="G195" s="4">
+      <c r="G195" s="3">
         <v>600000</v>
       </c>
-      <c r="H195" s="7">
+      <c r="H195" s="6">
         <v>750000</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A196" s="3" t="s">
+      <c r="A196" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="3">
         <v>160000</v>
       </c>
-      <c r="C196" s="4">
+      <c r="C196" s="3">
         <v>170000</v>
       </c>
-      <c r="D196" s="4">
+      <c r="D196" s="3">
         <v>240000</v>
       </c>
-      <c r="E196" s="4">
+      <c r="E196" s="3">
         <v>250000</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="3">
         <v>300000</v>
       </c>
-      <c r="G196" s="4">
+      <c r="G196" s="3">
         <v>700000</v>
       </c>
-      <c r="H196" s="7">
+      <c r="H196" s="6">
         <v>850000</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
+      <c r="A197" s="9" t="s">
         <v>203</v>
       </c>
       <c r="B197" s="2">
@@ -44813,12 +44920,12 @@
       <c r="G197" s="2">
         <v>450000</v>
       </c>
-      <c r="H197" s="6">
+      <c r="H197" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
+      <c r="A198" s="9" t="s">
         <v>204</v>
       </c>
       <c r="B198" s="2">
@@ -44839,12 +44946,12 @@
       <c r="G198" s="2">
         <v>450000</v>
       </c>
-      <c r="H198" s="6">
+      <c r="H198" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
+      <c r="A199" s="9" t="s">
         <v>205</v>
       </c>
       <c r="B199" s="2">
@@ -44865,12 +44972,12 @@
       <c r="G199" s="2">
         <v>450000</v>
       </c>
-      <c r="H199" s="6">
+      <c r="H199" s="5">
         <v>600000</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
+      <c r="A200" s="9" t="s">
         <v>206</v>
       </c>
       <c r="B200" s="2">
@@ -44896,7 +45003,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
+      <c r="A201" s="9" t="s">
         <v>207</v>
       </c>
       <c r="B201" s="2">
@@ -44922,59 +45029,59 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A202" s="3" t="s">
+      <c r="A202" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="3">
         <v>160000</v>
       </c>
-      <c r="C202" s="4">
+      <c r="C202" s="3">
         <v>170000</v>
       </c>
-      <c r="D202" s="4">
+      <c r="D202" s="3">
         <v>240000</v>
       </c>
-      <c r="E202" s="4">
+      <c r="E202" s="3">
         <v>250000</v>
       </c>
-      <c r="F202" s="4">
+      <c r="F202" s="3">
         <v>300000</v>
       </c>
-      <c r="G202" s="4">
+      <c r="G202" s="3">
         <v>600000</v>
       </c>
-      <c r="H202" s="4">
+      <c r="H202" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="3" t="s">
+      <c r="A203" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="3">
         <v>160000</v>
       </c>
-      <c r="C203" s="4">
+      <c r="C203" s="3">
         <v>170000</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D203" s="3">
         <v>240000</v>
       </c>
-      <c r="E203" s="4">
+      <c r="E203" s="3">
         <v>250000</v>
       </c>
-      <c r="F203" s="4">
+      <c r="F203" s="3">
         <v>300000</v>
       </c>
-      <c r="G203" s="4">
+      <c r="G203" s="3">
         <v>700000</v>
       </c>
-      <c r="H203" s="4">
+      <c r="H203" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
+      <c r="A204" s="9" t="s">
         <v>210</v>
       </c>
       <c r="B204" s="2">
@@ -45000,7 +45107,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
+      <c r="A205" s="9" t="s">
         <v>211</v>
       </c>
       <c r="B205" s="2">
@@ -45026,7 +45133,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
+      <c r="A206" s="9" t="s">
         <v>212</v>
       </c>
       <c r="B206" s="2">
@@ -45052,7 +45159,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
+      <c r="A207" s="9" t="s">
         <v>213</v>
       </c>
       <c r="B207" s="2">
@@ -45078,7 +45185,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
+      <c r="A208" s="9" t="s">
         <v>214</v>
       </c>
       <c r="B208" s="2">
@@ -45104,59 +45211,59 @@
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A209" s="3" t="s">
+      <c r="A209" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="3">
         <v>160000</v>
       </c>
-      <c r="C209" s="4">
+      <c r="C209" s="3">
         <v>170000</v>
       </c>
-      <c r="D209" s="4">
+      <c r="D209" s="3">
         <v>240000</v>
       </c>
-      <c r="E209" s="4">
+      <c r="E209" s="3">
         <v>250000</v>
       </c>
-      <c r="F209" s="4">
+      <c r="F209" s="3">
         <v>300000</v>
       </c>
-      <c r="G209" s="4">
+      <c r="G209" s="3">
         <v>600000</v>
       </c>
-      <c r="H209" s="4">
+      <c r="H209" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A210" s="3" t="s">
+      <c r="A210" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="3">
         <v>160000</v>
       </c>
-      <c r="C210" s="4">
+      <c r="C210" s="3">
         <v>170000</v>
       </c>
-      <c r="D210" s="4">
+      <c r="D210" s="3">
         <v>240000</v>
       </c>
-      <c r="E210" s="4">
+      <c r="E210" s="3">
         <v>250000</v>
       </c>
-      <c r="F210" s="4">
+      <c r="F210" s="3">
         <v>300000</v>
       </c>
-      <c r="G210" s="4">
+      <c r="G210" s="3">
         <v>700000</v>
       </c>
-      <c r="H210" s="4">
+      <c r="H210" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+      <c r="A211" s="9" t="s">
         <v>217</v>
       </c>
       <c r="B211" s="2">
@@ -45182,7 +45289,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
+      <c r="A212" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B212" s="2">
@@ -45208,7 +45315,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
+      <c r="A213" s="9" t="s">
         <v>219</v>
       </c>
       <c r="B213" s="2">
@@ -45234,7 +45341,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
+      <c r="A214" s="9" t="s">
         <v>220</v>
       </c>
       <c r="B214" s="2">
@@ -45260,7 +45367,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
+      <c r="A215" s="9" t="s">
         <v>221</v>
       </c>
       <c r="B215" s="2">
@@ -45286,59 +45393,59 @@
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A216" s="3" t="s">
+      <c r="A216" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="3">
         <v>160000</v>
       </c>
-      <c r="C216" s="4">
+      <c r="C216" s="3">
         <v>170000</v>
       </c>
-      <c r="D216" s="4">
+      <c r="D216" s="3">
         <v>240000</v>
       </c>
-      <c r="E216" s="4">
+      <c r="E216" s="3">
         <v>250000</v>
       </c>
-      <c r="F216" s="4">
+      <c r="F216" s="3">
         <v>300000</v>
       </c>
-      <c r="G216" s="4">
+      <c r="G216" s="3">
         <v>600000</v>
       </c>
-      <c r="H216" s="4">
+      <c r="H216" s="3">
         <v>750000</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A217" s="3" t="s">
+      <c r="A217" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="3">
         <v>160000</v>
       </c>
-      <c r="C217" s="4">
+      <c r="C217" s="3">
         <v>170000</v>
       </c>
-      <c r="D217" s="4">
+      <c r="D217" s="3">
         <v>240000</v>
       </c>
-      <c r="E217" s="4">
+      <c r="E217" s="3">
         <v>250000</v>
       </c>
-      <c r="F217" s="4">
+      <c r="F217" s="3">
         <v>300000</v>
       </c>
-      <c r="G217" s="4">
+      <c r="G217" s="3">
         <v>700000</v>
       </c>
-      <c r="H217" s="4">
+      <c r="H217" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
+      <c r="A218" s="9" t="s">
         <v>224</v>
       </c>
       <c r="B218" s="2">
@@ -45364,7 +45471,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
+      <c r="A219" s="9" t="s">
         <v>225</v>
       </c>
       <c r="B219" s="2">
@@ -45390,7 +45497,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
+      <c r="A220" s="9" t="s">
         <v>226</v>
       </c>
       <c r="B220" s="2">
@@ -45416,7 +45523,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
+      <c r="A221" s="9" t="s">
         <v>227</v>
       </c>
       <c r="B221" s="2">
@@ -45442,7 +45549,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
+      <c r="A222" s="9" t="s">
         <v>228</v>
       </c>
       <c r="B222" s="2">
@@ -45468,59 +45575,59 @@
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A223" s="3" t="s">
+      <c r="A223" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="3">
         <v>160000</v>
       </c>
-      <c r="C223" s="4">
+      <c r="C223" s="3">
         <v>170000</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D223" s="3">
         <v>240000</v>
       </c>
-      <c r="E223" s="4">
+      <c r="E223" s="3">
         <v>250000</v>
       </c>
-      <c r="F223" s="4">
+      <c r="F223" s="3">
         <v>300000</v>
       </c>
-      <c r="G223" s="4">
+      <c r="G223" s="3">
         <v>700000</v>
       </c>
-      <c r="H223" s="4">
+      <c r="H223" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A224" s="3" t="s">
+      <c r="A224" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="3">
         <v>160000</v>
       </c>
-      <c r="C224" s="4">
+      <c r="C224" s="3">
         <v>170000</v>
       </c>
-      <c r="D224" s="4">
+      <c r="D224" s="3">
         <v>240000</v>
       </c>
-      <c r="E224" s="4">
+      <c r="E224" s="3">
         <v>250000</v>
       </c>
-      <c r="F224" s="4">
+      <c r="F224" s="3">
         <v>300000</v>
       </c>
-      <c r="G224" s="4">
+      <c r="G224" s="3">
         <v>750000</v>
       </c>
-      <c r="H224" s="4">
+      <c r="H224" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
+      <c r="A225" s="9" t="s">
         <v>231</v>
       </c>
       <c r="B225" s="2">
@@ -45546,7 +45653,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
+      <c r="A226" s="9" t="s">
         <v>232</v>
       </c>
       <c r="B226" s="2">
@@ -45572,7 +45679,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
+      <c r="A227" s="9" t="s">
         <v>233</v>
       </c>
       <c r="B227" s="2">
@@ -45598,7 +45705,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
+      <c r="A228" s="9" t="s">
         <v>234</v>
       </c>
       <c r="B228" s="2">
@@ -45624,7 +45731,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
+      <c r="A229" s="9" t="s">
         <v>235</v>
       </c>
       <c r="B229" s="2">
@@ -45650,59 +45757,59 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="3">
         <v>160000</v>
       </c>
-      <c r="C230" s="4">
+      <c r="C230" s="3">
         <v>170000</v>
       </c>
-      <c r="D230" s="4">
+      <c r="D230" s="3">
         <v>240000</v>
       </c>
-      <c r="E230" s="4">
+      <c r="E230" s="3">
         <v>250000</v>
       </c>
-      <c r="F230" s="4">
+      <c r="F230" s="3">
         <v>300000</v>
       </c>
-      <c r="G230" s="4">
+      <c r="G230" s="3">
         <v>700000</v>
       </c>
-      <c r="H230" s="4">
+      <c r="H230" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
+      <c r="A231" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="3">
         <v>160000</v>
       </c>
-      <c r="C231" s="4">
+      <c r="C231" s="3">
         <v>170000</v>
       </c>
-      <c r="D231" s="4">
+      <c r="D231" s="3">
         <v>240000</v>
       </c>
-      <c r="E231" s="4">
+      <c r="E231" s="3">
         <v>250000</v>
       </c>
-      <c r="F231" s="4">
+      <c r="F231" s="3">
         <v>300000</v>
       </c>
-      <c r="G231" s="4">
+      <c r="G231" s="3">
         <v>750000</v>
       </c>
-      <c r="H231" s="4">
+      <c r="H231" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
+      <c r="A232" s="9" t="s">
         <v>238</v>
       </c>
       <c r="B232" s="2">
@@ -45728,7 +45835,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
+      <c r="A233" s="9" t="s">
         <v>239</v>
       </c>
       <c r="B233" s="2">
@@ -45754,7 +45861,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
+      <c r="A234" s="9" t="s">
         <v>240</v>
       </c>
       <c r="B234" s="2">
@@ -45780,7 +45887,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
+      <c r="A235" s="9" t="s">
         <v>241</v>
       </c>
       <c r="B235" s="2">
@@ -45806,7 +45913,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
+      <c r="A236" s="9" t="s">
         <v>242</v>
       </c>
       <c r="B236" s="2">
@@ -45832,59 +45939,59 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
+      <c r="A237" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="3">
         <v>160000</v>
       </c>
-      <c r="C237" s="4">
+      <c r="C237" s="3">
         <v>170000</v>
       </c>
-      <c r="D237" s="4">
+      <c r="D237" s="3">
         <v>240000</v>
       </c>
-      <c r="E237" s="4">
+      <c r="E237" s="3">
         <v>250000</v>
       </c>
-      <c r="F237" s="4">
+      <c r="F237" s="3">
         <v>300000</v>
       </c>
-      <c r="G237" s="4">
+      <c r="G237" s="3">
         <v>700000</v>
       </c>
-      <c r="H237" s="4">
+      <c r="H237" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A238" s="3" t="s">
+      <c r="A238" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="3">
         <v>160000</v>
       </c>
-      <c r="C238" s="4">
+      <c r="C238" s="3">
         <v>170000</v>
       </c>
-      <c r="D238" s="4">
+      <c r="D238" s="3">
         <v>240000</v>
       </c>
-      <c r="E238" s="4">
+      <c r="E238" s="3">
         <v>250000</v>
       </c>
-      <c r="F238" s="4">
+      <c r="F238" s="3">
         <v>300000</v>
       </c>
-      <c r="G238" s="4">
+      <c r="G238" s="3">
         <v>750000</v>
       </c>
-      <c r="H238" s="4">
+      <c r="H238" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
+      <c r="A239" s="9" t="s">
         <v>245</v>
       </c>
       <c r="B239" s="2">
@@ -45910,7 +46017,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
+      <c r="A240" s="9" t="s">
         <v>246</v>
       </c>
       <c r="B240" s="2">
@@ -45928,7 +46035,7 @@
       <c r="F240" s="2">
         <v>240000</v>
       </c>
-      <c r="G240" s="6">
+      <c r="G240" s="5">
         <v>500000</v>
       </c>
       <c r="H240" s="2">
@@ -45936,7 +46043,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
+      <c r="A241" s="9" t="s">
         <v>247</v>
       </c>
       <c r="B241" s="2">
@@ -45954,7 +46061,7 @@
       <c r="F241" s="2">
         <v>240000</v>
       </c>
-      <c r="G241" s="6">
+      <c r="G241" s="5">
         <v>500000</v>
       </c>
       <c r="H241" s="2">
@@ -45962,7 +46069,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
+      <c r="A242" s="9" t="s">
         <v>248</v>
       </c>
       <c r="B242" s="2">
@@ -45988,7 +46095,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
+      <c r="A243" s="9" t="s">
         <v>249</v>
       </c>
       <c r="B243" s="2">
@@ -46014,59 +46121,59 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
+      <c r="A244" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="3">
         <v>160000</v>
       </c>
-      <c r="C244" s="4">
+      <c r="C244" s="3">
         <v>170000</v>
       </c>
-      <c r="D244" s="4">
+      <c r="D244" s="3">
         <v>240000</v>
       </c>
-      <c r="E244" s="4">
+      <c r="E244" s="3">
         <v>250000</v>
       </c>
-      <c r="F244" s="4">
+      <c r="F244" s="3">
         <v>300000</v>
       </c>
-      <c r="G244" s="4">
+      <c r="G244" s="3">
         <v>700000</v>
       </c>
-      <c r="H244" s="4">
+      <c r="H244" s="3">
         <v>850000</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A245" s="3" t="s">
+      <c r="A245" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="3">
         <v>160000</v>
       </c>
-      <c r="C245" s="4">
+      <c r="C245" s="3">
         <v>170000</v>
       </c>
-      <c r="D245" s="4">
+      <c r="D245" s="3">
         <v>240000</v>
       </c>
-      <c r="E245" s="4">
+      <c r="E245" s="3">
         <v>250000</v>
       </c>
-      <c r="F245" s="4">
+      <c r="F245" s="3">
         <v>300000</v>
       </c>
-      <c r="G245" s="4">
+      <c r="G245" s="3">
         <v>750000</v>
       </c>
-      <c r="H245" s="4">
+      <c r="H245" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
+      <c r="A246" s="9" t="s">
         <v>252</v>
       </c>
       <c r="B246" s="2">
@@ -46092,7 +46199,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
+      <c r="A247" s="9" t="s">
         <v>253</v>
       </c>
       <c r="B247" s="2">
@@ -46118,7 +46225,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
+      <c r="A248" s="9" t="s">
         <v>254</v>
       </c>
       <c r="B248" s="2">
@@ -46144,7 +46251,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
+      <c r="A249" s="9" t="s">
         <v>255</v>
       </c>
       <c r="B249" s="2">
@@ -46170,7 +46277,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
+      <c r="A250" s="9" t="s">
         <v>256</v>
       </c>
       <c r="B250" s="2">
@@ -46196,59 +46303,59 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="3" t="s">
+      <c r="A251" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="3">
         <v>160000</v>
       </c>
-      <c r="C251" s="4">
+      <c r="C251" s="3">
         <v>170000</v>
       </c>
-      <c r="D251" s="4">
+      <c r="D251" s="3">
         <v>240000</v>
       </c>
-      <c r="E251" s="4">
+      <c r="E251" s="3">
         <v>250000</v>
       </c>
-      <c r="F251" s="4">
+      <c r="F251" s="3">
         <v>300000</v>
       </c>
-      <c r="G251" s="4">
+      <c r="G251" s="3">
         <v>750000</v>
       </c>
-      <c r="H251" s="4">
+      <c r="H251" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="3" t="s">
+      <c r="A252" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="3">
         <v>160000</v>
       </c>
-      <c r="C252" s="4">
+      <c r="C252" s="3">
         <v>170000</v>
       </c>
-      <c r="D252" s="4">
+      <c r="D252" s="3">
         <v>240000</v>
       </c>
-      <c r="E252" s="4">
+      <c r="E252" s="3">
         <v>250000</v>
       </c>
-      <c r="F252" s="4">
+      <c r="F252" s="3">
         <v>300000</v>
       </c>
-      <c r="G252" s="4">
+      <c r="G252" s="3">
         <v>800000</v>
       </c>
-      <c r="H252" s="4">
+      <c r="H252" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
+      <c r="A253" s="9" t="s">
         <v>259</v>
       </c>
       <c r="B253" s="2">
@@ -46274,7 +46381,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
+      <c r="A254" s="9" t="s">
         <v>260</v>
       </c>
       <c r="B254" s="2">
@@ -46300,7 +46407,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
+      <c r="A255" s="9" t="s">
         <v>261</v>
       </c>
       <c r="B255" s="2">
@@ -46326,7 +46433,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
+      <c r="A256" s="9" t="s">
         <v>262</v>
       </c>
       <c r="B256" s="2">
@@ -46352,7 +46459,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
+      <c r="A257" s="9" t="s">
         <v>263</v>
       </c>
       <c r="B257" s="2">
@@ -46378,59 +46485,59 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="3" t="s">
+      <c r="A258" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="3">
         <v>160000</v>
       </c>
-      <c r="C258" s="4">
+      <c r="C258" s="3">
         <v>170000</v>
       </c>
-      <c r="D258" s="4">
+      <c r="D258" s="3">
         <v>240000</v>
       </c>
-      <c r="E258" s="4">
+      <c r="E258" s="3">
         <v>250000</v>
       </c>
-      <c r="F258" s="4">
+      <c r="F258" s="3">
         <v>300000</v>
       </c>
-      <c r="G258" s="4">
+      <c r="G258" s="3">
         <v>750000</v>
       </c>
-      <c r="H258" s="4">
+      <c r="H258" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="3" t="s">
+      <c r="A259" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="B259" s="4">
+      <c r="B259" s="3">
         <v>160000</v>
       </c>
-      <c r="C259" s="4">
+      <c r="C259" s="3">
         <v>170000</v>
       </c>
-      <c r="D259" s="4">
+      <c r="D259" s="3">
         <v>240000</v>
       </c>
-      <c r="E259" s="4">
+      <c r="E259" s="3">
         <v>250000</v>
       </c>
-      <c r="F259" s="4">
+      <c r="F259" s="3">
         <v>300000</v>
       </c>
-      <c r="G259" s="4">
+      <c r="G259" s="3">
         <v>800000</v>
       </c>
-      <c r="H259" s="4">
+      <c r="H259" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
+      <c r="A260" s="9" t="s">
         <v>266</v>
       </c>
       <c r="B260" s="2">
@@ -46456,7 +46563,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
+      <c r="A261" s="9" t="s">
         <v>267</v>
       </c>
       <c r="B261" s="2">
@@ -46482,7 +46589,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
+      <c r="A262" s="9" t="s">
         <v>268</v>
       </c>
       <c r="B262" s="2">
@@ -46508,7 +46615,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
+      <c r="A263" s="9" t="s">
         <v>269</v>
       </c>
       <c r="B263" s="2">
@@ -46534,7 +46641,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
+      <c r="A264" s="9" t="s">
         <v>270</v>
       </c>
       <c r="B264" s="2">
@@ -46560,59 +46667,59 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="3" t="s">
+      <c r="A265" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B265" s="4">
+      <c r="B265" s="3">
         <v>160000</v>
       </c>
-      <c r="C265" s="4">
+      <c r="C265" s="3">
         <v>170000</v>
       </c>
-      <c r="D265" s="4">
+      <c r="D265" s="3">
         <v>240000</v>
       </c>
-      <c r="E265" s="4">
+      <c r="E265" s="3">
         <v>250000</v>
       </c>
-      <c r="F265" s="4">
+      <c r="F265" s="3">
         <v>300000</v>
       </c>
-      <c r="G265" s="4">
+      <c r="G265" s="3">
         <v>750000</v>
       </c>
-      <c r="H265" s="4">
+      <c r="H265" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="3" t="s">
+      <c r="A266" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="B266" s="4">
+      <c r="B266" s="3">
         <v>160000</v>
       </c>
-      <c r="C266" s="4">
+      <c r="C266" s="3">
         <v>170000</v>
       </c>
-      <c r="D266" s="4">
+      <c r="D266" s="3">
         <v>240000</v>
       </c>
-      <c r="E266" s="4">
+      <c r="E266" s="3">
         <v>250000</v>
       </c>
-      <c r="F266" s="4">
+      <c r="F266" s="3">
         <v>300000</v>
       </c>
-      <c r="G266" s="4">
+      <c r="G266" s="3">
         <v>800000</v>
       </c>
-      <c r="H266" s="4">
+      <c r="H266" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
+      <c r="A267" s="9" t="s">
         <v>273</v>
       </c>
       <c r="B267" s="2">
@@ -46638,7 +46745,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
+      <c r="A268" s="9" t="s">
         <v>274</v>
       </c>
       <c r="B268" s="2">
@@ -46664,7 +46771,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
+      <c r="A269" s="9" t="s">
         <v>275</v>
       </c>
       <c r="B269" s="2">
@@ -46690,7 +46797,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
+      <c r="A270" s="9" t="s">
         <v>276</v>
       </c>
       <c r="B270" s="2">
@@ -46716,7 +46823,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
+      <c r="A271" s="9" t="s">
         <v>277</v>
       </c>
       <c r="B271" s="2">
@@ -46742,59 +46849,59 @@
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A272" s="3" t="s">
+      <c r="A272" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="3">
         <v>160000</v>
       </c>
-      <c r="C272" s="4">
+      <c r="C272" s="3">
         <v>170000</v>
       </c>
-      <c r="D272" s="4">
+      <c r="D272" s="3">
         <v>240000</v>
       </c>
-      <c r="E272" s="4">
+      <c r="E272" s="3">
         <v>250000</v>
       </c>
-      <c r="F272" s="4">
+      <c r="F272" s="3">
         <v>300000</v>
       </c>
-      <c r="G272" s="4">
+      <c r="G272" s="3">
         <v>750000</v>
       </c>
-      <c r="H272" s="4">
+      <c r="H272" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A273" s="3" t="s">
+      <c r="A273" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B273" s="4">
+      <c r="B273" s="3">
         <v>160000</v>
       </c>
-      <c r="C273" s="4">
+      <c r="C273" s="3">
         <v>170000</v>
       </c>
-      <c r="D273" s="4">
+      <c r="D273" s="3">
         <v>240000</v>
       </c>
-      <c r="E273" s="4">
+      <c r="E273" s="3">
         <v>250000</v>
       </c>
-      <c r="F273" s="4">
+      <c r="F273" s="3">
         <v>300000</v>
       </c>
-      <c r="G273" s="4">
+      <c r="G273" s="3">
         <v>800000</v>
       </c>
-      <c r="H273" s="4">
+      <c r="H273" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
+      <c r="A274" s="9" t="s">
         <v>280</v>
       </c>
       <c r="B274" s="2">
@@ -46820,7 +46927,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
+      <c r="A275" s="9" t="s">
         <v>281</v>
       </c>
       <c r="B275" s="2">
@@ -46846,7 +46953,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
+      <c r="A276" s="9" t="s">
         <v>282</v>
       </c>
       <c r="B276" s="2">
@@ -46872,7 +46979,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
+      <c r="A277" s="9" t="s">
         <v>283</v>
       </c>
       <c r="B277" s="2">
@@ -46898,7 +47005,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
+      <c r="A278" s="9" t="s">
         <v>284</v>
       </c>
       <c r="B278" s="2">
@@ -46924,59 +47031,59 @@
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A279" s="3" t="s">
+      <c r="A279" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="B279" s="4">
+      <c r="B279" s="3">
         <v>160000</v>
       </c>
-      <c r="C279" s="4">
+      <c r="C279" s="3">
         <v>170000</v>
       </c>
-      <c r="D279" s="4">
+      <c r="D279" s="3">
         <v>240000</v>
       </c>
-      <c r="E279" s="4">
+      <c r="E279" s="3">
         <v>250000</v>
       </c>
-      <c r="F279" s="4">
+      <c r="F279" s="3">
         <v>300000</v>
       </c>
-      <c r="G279" s="4">
+      <c r="G279" s="3">
         <v>750000</v>
       </c>
-      <c r="H279" s="4">
+      <c r="H279" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A280" s="3" t="s">
+      <c r="A280" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="3">
         <v>160000</v>
       </c>
-      <c r="C280" s="4">
+      <c r="C280" s="3">
         <v>170000</v>
       </c>
-      <c r="D280" s="4">
+      <c r="D280" s="3">
         <v>240000</v>
       </c>
-      <c r="E280" s="4">
+      <c r="E280" s="3">
         <v>250000</v>
       </c>
-      <c r="F280" s="4">
+      <c r="F280" s="3">
         <v>300000</v>
       </c>
-      <c r="G280" s="4">
+      <c r="G280" s="3">
         <v>800000</v>
       </c>
-      <c r="H280" s="4">
+      <c r="H280" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
+      <c r="A281" s="9" t="s">
         <v>287</v>
       </c>
       <c r="B281" s="2">
@@ -47002,7 +47109,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
+      <c r="A282" s="9" t="s">
         <v>288</v>
       </c>
       <c r="B282" s="2">
@@ -47028,7 +47135,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
+      <c r="A283" s="9" t="s">
         <v>289</v>
       </c>
       <c r="B283" s="2">
@@ -47054,7 +47161,7 @@
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
+      <c r="A284" s="9" t="s">
         <v>290</v>
       </c>
       <c r="B284" s="2">
@@ -47080,7 +47187,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
+      <c r="A285" s="9" t="s">
         <v>291</v>
       </c>
       <c r="B285" s="2">
@@ -47106,59 +47213,59 @@
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A286" s="3" t="s">
+      <c r="A286" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="3">
         <v>160000</v>
       </c>
-      <c r="C286" s="4">
+      <c r="C286" s="3">
         <v>170000</v>
       </c>
-      <c r="D286" s="4">
+      <c r="D286" s="3">
         <v>240000</v>
       </c>
-      <c r="E286" s="4">
+      <c r="E286" s="3">
         <v>250000</v>
       </c>
-      <c r="F286" s="4">
+      <c r="F286" s="3">
         <v>300000</v>
       </c>
-      <c r="G286" s="4">
+      <c r="G286" s="3">
         <v>750000</v>
       </c>
-      <c r="H286" s="4">
+      <c r="H286" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A287" s="3" t="s">
+      <c r="A287" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B287" s="4">
+      <c r="B287" s="3">
         <v>160000</v>
       </c>
-      <c r="C287" s="4">
+      <c r="C287" s="3">
         <v>170000</v>
       </c>
-      <c r="D287" s="4">
+      <c r="D287" s="3">
         <v>240000</v>
       </c>
-      <c r="E287" s="4">
+      <c r="E287" s="3">
         <v>250000</v>
       </c>
-      <c r="F287" s="4">
+      <c r="F287" s="3">
         <v>300000</v>
       </c>
-      <c r="G287" s="4">
+      <c r="G287" s="3">
         <v>800000</v>
       </c>
-      <c r="H287" s="4">
+      <c r="H287" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
+      <c r="A288" s="9" t="s">
         <v>294</v>
       </c>
       <c r="B288" s="2">
@@ -47184,7 +47291,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
+      <c r="A289" s="9" t="s">
         <v>295</v>
       </c>
       <c r="B289" s="2">
@@ -47210,7 +47317,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
+      <c r="A290" s="9" t="s">
         <v>296</v>
       </c>
       <c r="B290" s="2">
@@ -47236,7 +47343,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
+      <c r="A291" s="9" t="s">
         <v>297</v>
       </c>
       <c r="B291" s="2">
@@ -47262,7 +47369,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
+      <c r="A292" s="9" t="s">
         <v>298</v>
       </c>
       <c r="B292" s="2">
@@ -47288,59 +47395,59 @@
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A293" s="3" t="s">
+      <c r="A293" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="B293" s="4">
+      <c r="B293" s="3">
         <v>160000</v>
       </c>
-      <c r="C293" s="4">
+      <c r="C293" s="3">
         <v>170000</v>
       </c>
-      <c r="D293" s="4">
+      <c r="D293" s="3">
         <v>240000</v>
       </c>
-      <c r="E293" s="4">
+      <c r="E293" s="3">
         <v>250000</v>
       </c>
-      <c r="F293" s="4">
+      <c r="F293" s="3">
         <v>300000</v>
       </c>
-      <c r="G293" s="4">
+      <c r="G293" s="3">
         <v>750000</v>
       </c>
-      <c r="H293" s="4">
+      <c r="H293" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A294" s="3" t="s">
+      <c r="A294" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="B294" s="4">
+      <c r="B294" s="3">
         <v>160000</v>
       </c>
-      <c r="C294" s="4">
+      <c r="C294" s="3">
         <v>170000</v>
       </c>
-      <c r="D294" s="4">
+      <c r="D294" s="3">
         <v>240000</v>
       </c>
-      <c r="E294" s="4">
+      <c r="E294" s="3">
         <v>250000</v>
       </c>
-      <c r="F294" s="4">
+      <c r="F294" s="3">
         <v>300000</v>
       </c>
-      <c r="G294" s="4">
+      <c r="G294" s="3">
         <v>800000</v>
       </c>
-      <c r="H294" s="4">
+      <c r="H294" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
+      <c r="A295" s="9" t="s">
         <v>301</v>
       </c>
       <c r="B295" s="2">
@@ -47366,7 +47473,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
+      <c r="A296" s="9" t="s">
         <v>302</v>
       </c>
       <c r="B296" s="2">
@@ -47392,7 +47499,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
+      <c r="A297" s="9" t="s">
         <v>303</v>
       </c>
       <c r="B297" s="2">
@@ -47418,7 +47525,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
+      <c r="A298" s="9" t="s">
         <v>304</v>
       </c>
       <c r="B298" s="2">
@@ -47444,7 +47551,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
+      <c r="A299" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B299" s="2">
@@ -47470,59 +47577,59 @@
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A300" s="3" t="s">
+      <c r="A300" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="B300" s="4">
+      <c r="B300" s="3">
         <v>160000</v>
       </c>
-      <c r="C300" s="4">
+      <c r="C300" s="3">
         <v>170000</v>
       </c>
-      <c r="D300" s="4">
+      <c r="D300" s="3">
         <v>240000</v>
       </c>
-      <c r="E300" s="4">
+      <c r="E300" s="3">
         <v>250000</v>
       </c>
-      <c r="F300" s="4">
+      <c r="F300" s="3">
         <v>300000</v>
       </c>
-      <c r="G300" s="4">
+      <c r="G300" s="3">
         <v>750000</v>
       </c>
-      <c r="H300" s="4">
+      <c r="H300" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A301" s="3" t="s">
+      <c r="A301" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="3">
         <v>160000</v>
       </c>
-      <c r="C301" s="4">
+      <c r="C301" s="3">
         <v>170000</v>
       </c>
-      <c r="D301" s="4">
+      <c r="D301" s="3">
         <v>240000</v>
       </c>
-      <c r="E301" s="4">
+      <c r="E301" s="3">
         <v>250000</v>
       </c>
-      <c r="F301" s="4">
+      <c r="F301" s="3">
         <v>300000</v>
       </c>
-      <c r="G301" s="4">
+      <c r="G301" s="3">
         <v>800000</v>
       </c>
-      <c r="H301" s="4">
+      <c r="H301" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
+      <c r="A302" s="9" t="s">
         <v>308</v>
       </c>
       <c r="B302" s="2">
@@ -47548,7 +47655,7 @@
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
+      <c r="A303" s="9" t="s">
         <v>309</v>
       </c>
       <c r="B303" s="2">
@@ -47574,7 +47681,7 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
+      <c r="A304" s="9" t="s">
         <v>310</v>
       </c>
       <c r="B304" s="2">
@@ -47600,7 +47707,7 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
+      <c r="A305" s="9" t="s">
         <v>311</v>
       </c>
       <c r="B305" s="2">
@@ -47626,7 +47733,7 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
+      <c r="A306" s="9" t="s">
         <v>312</v>
       </c>
       <c r="B306" s="2">
@@ -47652,59 +47759,59 @@
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A307" s="3" t="s">
+      <c r="A307" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="3">
         <v>160000</v>
       </c>
-      <c r="C307" s="4">
+      <c r="C307" s="3">
         <v>170000</v>
       </c>
-      <c r="D307" s="4">
+      <c r="D307" s="3">
         <v>240000</v>
       </c>
-      <c r="E307" s="4">
+      <c r="E307" s="3">
         <v>250000</v>
       </c>
-      <c r="F307" s="4">
+      <c r="F307" s="3">
         <v>210000</v>
       </c>
-      <c r="G307" s="4">
+      <c r="G307" s="3">
         <v>750000</v>
       </c>
-      <c r="H307" s="4">
+      <c r="H307" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A308" s="3" t="s">
+      <c r="A308" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="3">
         <v>160000</v>
       </c>
-      <c r="C308" s="4">
+      <c r="C308" s="3">
         <v>170000</v>
       </c>
-      <c r="D308" s="4">
+      <c r="D308" s="3">
         <v>240000</v>
       </c>
-      <c r="E308" s="4">
+      <c r="E308" s="3">
         <v>250000</v>
       </c>
-      <c r="F308" s="4">
+      <c r="F308" s="3">
         <v>300000</v>
       </c>
-      <c r="G308" s="4">
+      <c r="G308" s="3">
         <v>800000</v>
       </c>
-      <c r="H308" s="4">
+      <c r="H308" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
+      <c r="A309" s="9" t="s">
         <v>315</v>
       </c>
       <c r="B309" s="2">
@@ -47730,7 +47837,7 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
+      <c r="A310" s="9" t="s">
         <v>316</v>
       </c>
       <c r="B310" s="2">
@@ -47756,7 +47863,7 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
+      <c r="A311" s="9" t="s">
         <v>317</v>
       </c>
       <c r="B311" s="2">
@@ -47782,7 +47889,7 @@
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
+      <c r="A312" s="9" t="s">
         <v>318</v>
       </c>
       <c r="B312" s="2">
@@ -47808,7 +47915,7 @@
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
+      <c r="A313" s="9" t="s">
         <v>319</v>
       </c>
       <c r="B313" s="2">
@@ -47834,59 +47941,59 @@
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A314" s="3" t="s">
+      <c r="A314" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="3">
         <v>160000</v>
       </c>
-      <c r="C314" s="4">
+      <c r="C314" s="3">
         <v>170000</v>
       </c>
-      <c r="D314" s="4">
+      <c r="D314" s="3">
         <v>240000</v>
       </c>
-      <c r="E314" s="4">
+      <c r="E314" s="3">
         <v>250000</v>
       </c>
-      <c r="F314" s="4">
+      <c r="F314" s="3">
         <v>300000</v>
       </c>
-      <c r="G314" s="4">
+      <c r="G314" s="3">
         <v>750000</v>
       </c>
-      <c r="H314" s="4">
+      <c r="H314" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A315" s="3" t="s">
+      <c r="A315" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="3">
         <v>160000</v>
       </c>
-      <c r="C315" s="4">
+      <c r="C315" s="3">
         <v>170000</v>
       </c>
-      <c r="D315" s="4">
+      <c r="D315" s="3">
         <v>240000</v>
       </c>
-      <c r="E315" s="4">
+      <c r="E315" s="3">
         <v>250000</v>
       </c>
-      <c r="F315" s="4">
+      <c r="F315" s="3">
         <v>300000</v>
       </c>
-      <c r="G315" s="4">
+      <c r="G315" s="3">
         <v>800000</v>
       </c>
-      <c r="H315" s="4">
+      <c r="H315" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
+      <c r="A316" s="9" t="s">
         <v>322</v>
       </c>
       <c r="B316" s="2">
@@ -47912,7 +48019,7 @@
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
+      <c r="A317" s="9" t="s">
         <v>323</v>
       </c>
       <c r="B317" s="2">
@@ -47938,7 +48045,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
+      <c r="A318" s="9" t="s">
         <v>324</v>
       </c>
       <c r="B318" s="2">
@@ -47964,7 +48071,7 @@
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
+      <c r="A319" s="9" t="s">
         <v>325</v>
       </c>
       <c r="B319" s="2">
@@ -47990,7 +48097,7 @@
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
+      <c r="A320" s="9" t="s">
         <v>326</v>
       </c>
       <c r="B320" s="2">
@@ -48016,59 +48123,59 @@
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A321" s="3" t="s">
+      <c r="A321" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="3">
         <v>160000</v>
       </c>
-      <c r="C321" s="4">
+      <c r="C321" s="3">
         <v>170000</v>
       </c>
-      <c r="D321" s="4">
+      <c r="D321" s="3">
         <v>240000</v>
       </c>
-      <c r="E321" s="4">
+      <c r="E321" s="3">
         <v>250000</v>
       </c>
-      <c r="F321" s="4">
+      <c r="F321" s="3">
         <v>300000</v>
       </c>
-      <c r="G321" s="4">
+      <c r="G321" s="3">
         <v>750000</v>
       </c>
-      <c r="H321" s="4">
+      <c r="H321" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A322" s="3" t="s">
+      <c r="A322" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="3">
         <v>160000</v>
       </c>
-      <c r="C322" s="4">
+      <c r="C322" s="3">
         <v>170000</v>
       </c>
-      <c r="D322" s="4">
+      <c r="D322" s="3">
         <v>240000</v>
       </c>
-      <c r="E322" s="4">
+      <c r="E322" s="3">
         <v>250000</v>
       </c>
-      <c r="F322" s="4">
+      <c r="F322" s="3">
         <v>300000</v>
       </c>
-      <c r="G322" s="4">
+      <c r="G322" s="3">
         <v>800000</v>
       </c>
-      <c r="H322" s="4">
+      <c r="H322" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
+      <c r="A323" s="9" t="s">
         <v>329</v>
       </c>
       <c r="B323" s="2">
@@ -48094,7 +48201,7 @@
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
+      <c r="A324" s="9" t="s">
         <v>330</v>
       </c>
       <c r="B324" s="2">
@@ -48120,7 +48227,7 @@
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
+      <c r="A325" s="9" t="s">
         <v>331</v>
       </c>
       <c r="B325" s="2">
@@ -48146,7 +48253,7 @@
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
+      <c r="A326" s="9" t="s">
         <v>332</v>
       </c>
       <c r="B326" s="2">
@@ -48172,7 +48279,7 @@
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
+      <c r="A327" s="9" t="s">
         <v>333</v>
       </c>
       <c r="B327" s="2">
@@ -48198,59 +48305,59 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A328" s="16" t="s">
+      <c r="A328" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="B328" s="5">
+      <c r="B328" s="4">
         <v>160000</v>
       </c>
-      <c r="C328" s="4">
+      <c r="C328" s="3">
         <v>170000</v>
       </c>
-      <c r="D328" s="4">
+      <c r="D328" s="3">
         <v>240000</v>
       </c>
-      <c r="E328" s="5">
+      <c r="E328" s="4">
         <v>250000</v>
       </c>
-      <c r="F328" s="5">
+      <c r="F328" s="4">
         <v>300000</v>
       </c>
-      <c r="G328" s="4">
+      <c r="G328" s="3">
         <v>750000</v>
       </c>
-      <c r="H328" s="4">
+      <c r="H328" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A329" s="16" t="s">
+      <c r="A329" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="B329" s="5">
+      <c r="B329" s="4">
         <v>160000</v>
       </c>
-      <c r="C329" s="4">
+      <c r="C329" s="3">
         <v>170000</v>
       </c>
-      <c r="D329" s="4">
+      <c r="D329" s="3">
         <v>240000</v>
       </c>
-      <c r="E329" s="5">
+      <c r="E329" s="4">
         <v>250000</v>
       </c>
-      <c r="F329" s="5">
+      <c r="F329" s="4">
         <v>300000</v>
       </c>
-      <c r="G329" s="4">
+      <c r="G329" s="3">
         <v>800000</v>
       </c>
-      <c r="H329" s="4">
+      <c r="H329" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A330" s="15" t="s">
+      <c r="A330" s="9" t="s">
         <v>336</v>
       </c>
       <c r="B330" s="2">
@@ -48276,7 +48383,7 @@
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A331" s="15" t="s">
+      <c r="A331" s="9" t="s">
         <v>337</v>
       </c>
       <c r="B331" s="2">
@@ -48302,7 +48409,7 @@
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A332" s="15" t="s">
+      <c r="A332" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B332" s="2">
@@ -48328,7 +48435,7 @@
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A333" s="15" t="s">
+      <c r="A333" s="9" t="s">
         <v>339</v>
       </c>
       <c r="B333" s="2">
@@ -48354,7 +48461,7 @@
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A334" s="15" t="s">
+      <c r="A334" s="9" t="s">
         <v>340</v>
       </c>
       <c r="B334" s="2">
@@ -48380,59 +48487,59 @@
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A335" s="16" t="s">
+      <c r="A335" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B335" s="5">
+      <c r="B335" s="4">
         <v>220000</v>
       </c>
-      <c r="C335" s="4">
+      <c r="C335" s="3">
         <v>240000</v>
       </c>
-      <c r="D335" s="4">
+      <c r="D335" s="3">
         <v>280000</v>
       </c>
-      <c r="E335" s="5">
+      <c r="E335" s="4">
         <v>290000</v>
       </c>
-      <c r="F335" s="5">
+      <c r="F335" s="4">
         <v>400000</v>
       </c>
-      <c r="G335" s="4">
+      <c r="G335" s="3">
         <v>950000</v>
       </c>
-      <c r="H335" s="4">
+      <c r="H335" s="3">
         <v>1100000</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A336" s="16" t="s">
+      <c r="A336" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="B336" s="5">
+      <c r="B336" s="4">
         <v>220000</v>
       </c>
-      <c r="C336" s="4">
+      <c r="C336" s="3">
         <v>240000</v>
       </c>
-      <c r="D336" s="4">
+      <c r="D336" s="3">
         <v>280000</v>
       </c>
-      <c r="E336" s="5">
+      <c r="E336" s="4">
         <v>290000</v>
       </c>
-      <c r="F336" s="5">
+      <c r="F336" s="4">
         <v>400000</v>
       </c>
-      <c r="G336" s="4">
+      <c r="G336" s="3">
         <v>950000</v>
       </c>
-      <c r="H336" s="4">
+      <c r="H336" s="3">
         <v>1100000</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A337" s="15" t="s">
+      <c r="A337" s="9" t="s">
         <v>343</v>
       </c>
       <c r="B337" s="2">
@@ -48458,7 +48565,7 @@
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A338" s="15" t="s">
+      <c r="A338" s="9" t="s">
         <v>344</v>
       </c>
       <c r="B338" s="2">
@@ -48484,7 +48591,7 @@
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A339" s="15" t="s">
+      <c r="A339" s="9" t="s">
         <v>345</v>
       </c>
       <c r="B339" s="2">
@@ -48510,7 +48617,7 @@
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A340" s="15" t="s">
+      <c r="A340" s="9" t="s">
         <v>346</v>
       </c>
       <c r="B340" s="2">
@@ -48536,7 +48643,7 @@
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A341" s="15" t="s">
+      <c r="A341" s="9" t="s">
         <v>347</v>
       </c>
       <c r="B341" s="2">
@@ -48562,59 +48669,59 @@
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A342" s="16" t="s">
+      <c r="A342" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="B342" s="5">
+      <c r="B342" s="4">
         <v>220000</v>
       </c>
-      <c r="C342" s="4">
+      <c r="C342" s="3">
         <v>240000</v>
       </c>
-      <c r="D342" s="4">
+      <c r="D342" s="3">
         <v>280000</v>
       </c>
-      <c r="E342" s="5">
+      <c r="E342" s="4">
         <v>290000</v>
       </c>
-      <c r="F342" s="5">
+      <c r="F342" s="4">
         <v>400000</v>
       </c>
-      <c r="G342" s="4">
+      <c r="G342" s="3">
         <v>950000</v>
       </c>
-      <c r="H342" s="4">
+      <c r="H342" s="3">
         <v>1100000</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A343" s="16" t="s">
+      <c r="A343" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="B343" s="5">
+      <c r="B343" s="4">
         <v>220000</v>
       </c>
-      <c r="C343" s="4">
+      <c r="C343" s="3">
         <v>240000</v>
       </c>
-      <c r="D343" s="4">
+      <c r="D343" s="3">
         <v>280000</v>
       </c>
-      <c r="E343" s="5">
+      <c r="E343" s="4">
         <v>290000</v>
       </c>
-      <c r="F343" s="5">
+      <c r="F343" s="4">
         <v>400000</v>
       </c>
-      <c r="G343" s="4">
+      <c r="G343" s="3">
         <v>950000</v>
       </c>
-      <c r="H343" s="4">
+      <c r="H343" s="3">
         <v>1100000</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A344" s="15" t="s">
+      <c r="A344" s="9" t="s">
         <v>350</v>
       </c>
       <c r="B344" s="2">
@@ -48640,7 +48747,7 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A345" s="15" t="s">
+      <c r="A345" s="9" t="s">
         <v>351</v>
       </c>
       <c r="B345" s="2">
@@ -48666,7 +48773,7 @@
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
+      <c r="A346" s="9" t="s">
         <v>352</v>
       </c>
       <c r="B346" s="2">
@@ -48692,7 +48799,7 @@
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
+      <c r="A347" s="9" t="s">
         <v>353</v>
       </c>
       <c r="B347" s="2">
@@ -48718,7 +48825,7 @@
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
+      <c r="A348" s="9" t="s">
         <v>354</v>
       </c>
       <c r="B348" s="2">
@@ -48744,56 +48851,2005 @@
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
+      <c r="A349" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B349" s="5">
+      <c r="B349" s="4">
         <v>160000</v>
       </c>
-      <c r="C349" s="4">
+      <c r="C349" s="3">
         <v>170000</v>
       </c>
-      <c r="D349" s="4">
+      <c r="D349" s="3">
         <v>240000</v>
       </c>
-      <c r="E349" s="5">
+      <c r="E349" s="4">
         <v>250000</v>
       </c>
-      <c r="F349" s="5">
+      <c r="F349" s="4">
         <v>300000</v>
       </c>
-      <c r="G349" s="4">
+      <c r="G349" s="3">
         <v>750000</v>
       </c>
-      <c r="H349" s="4">
+      <c r="H349" s="3">
         <v>900000</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
+      <c r="A350" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="B350" s="5">
+      <c r="B350" s="4">
         <v>160000</v>
       </c>
-      <c r="C350" s="4">
+      <c r="C350" s="3">
         <v>170000</v>
       </c>
-      <c r="D350" s="4">
+      <c r="D350" s="3">
         <v>240000</v>
       </c>
-      <c r="E350" s="5">
+      <c r="E350" s="4">
         <v>250000</v>
       </c>
-      <c r="F350" s="5">
+      <c r="F350" s="4">
         <v>300000</v>
       </c>
-      <c r="G350" s="4">
+      <c r="G350" s="3">
         <v>800000</v>
       </c>
-      <c r="H350" s="4">
+      <c r="H350" s="3">
         <v>950000</v>
       </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A351" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B351" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C351" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D351" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E351" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F351" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G351" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H351" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A352" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B352" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C352" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D352" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E352" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F352" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G352" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H352" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A353" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B353" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C353" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D353" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E353" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F353" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G353" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H353" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A354" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B354" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C354" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D354" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E354" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F354" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G354" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H354" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A355" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B355" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C355" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D355" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E355" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F355" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G355" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H355" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A356" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B356" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C356" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D356" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E356" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F356" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G356" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H356" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A357" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B357" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C357" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D357" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E357" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F357" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G357" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H357" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A358" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B358" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C358" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D358" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E358" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F358" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G358" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H358" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A359" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B359" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C359" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D359" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E359" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F359" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G359" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H359" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A360" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B360" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C360" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D360" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E360" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F360" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G360" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H360" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A361" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B361" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C361" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D361" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E361" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F361" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G361" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H361" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A362" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B362" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C362" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D362" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E362" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F362" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G362" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H362" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A363" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B363" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C363" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D363" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E363" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F363" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G363" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H363" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A364" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B364" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C364" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D364" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E364" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F364" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G364" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H364" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A365" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B365" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C365" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D365" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E365" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F365" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G365" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H365" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A366" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B366" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C366" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D366" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E366" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F366" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G366" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H366" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A367" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B367" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C367" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D367" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E367" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F367" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G367" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H367" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A368" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B368" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C368" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D368" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E368" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F368" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G368" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H368" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A369" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B369" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C369" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D369" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E369" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F369" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G369" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H369" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A370" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B370" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C370" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D370" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E370" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F370" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G370" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H370" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A371" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B371" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C371" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D371" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E371" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F371" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G371" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H371" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A372" s="22">
+        <v>46418</v>
+      </c>
+      <c r="B372" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C372" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D372" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E372" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F372" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G372" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H372" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A373" s="20">
+        <v>46419</v>
+      </c>
+      <c r="B373" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C373" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D373" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E373" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F373" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G373" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H373" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A374" s="20">
+        <v>46420</v>
+      </c>
+      <c r="B374" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C374" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D374" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E374" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F374" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G374" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H374" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A375" s="20">
+        <v>46421</v>
+      </c>
+      <c r="B375" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C375" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D375" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E375" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F375" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G375" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H375" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A376" s="20">
+        <v>46422</v>
+      </c>
+      <c r="B376" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C376" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D376" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E376" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F376" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G376" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H376" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A377" s="19">
+        <v>46423</v>
+      </c>
+      <c r="B377" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C377" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D377" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E377" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F377" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G377" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H377" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A378" s="19">
+        <v>46424</v>
+      </c>
+      <c r="B378" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C378" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D378" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E378" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F378" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G378" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H378" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A379" s="19">
+        <v>46425</v>
+      </c>
+      <c r="B379" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C379" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D379" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E379" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F379" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G379" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H379" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A380" s="19">
+        <v>46426</v>
+      </c>
+      <c r="B380" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C380" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D380" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E380" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F380" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G380" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H380" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A381" s="21">
+        <v>46427</v>
+      </c>
+      <c r="B381" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C381" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D381" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E381" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F381" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G381" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H381" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A382" s="20">
+        <v>46428</v>
+      </c>
+      <c r="B382" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C382" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D382" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E382" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F382" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G382" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H382" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A383" s="20">
+        <v>46429</v>
+      </c>
+      <c r="B383" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C383" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D383" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E383" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F383" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G383" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H383" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A384" s="19">
+        <v>46430</v>
+      </c>
+      <c r="B384" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C384" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D384" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E384" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F384" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G384" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H384" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A385" s="19">
+        <v>46431</v>
+      </c>
+      <c r="B385" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C385" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D385" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E385" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F385" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G385" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H385" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A386" s="21">
+        <v>46432</v>
+      </c>
+      <c r="B386" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C386" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D386" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E386" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F386" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G386" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H386" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A387" s="20">
+        <v>46433</v>
+      </c>
+      <c r="B387" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C387" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D387" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E387" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F387" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G387" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H387" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A388" s="20">
+        <v>46434</v>
+      </c>
+      <c r="B388" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C388" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D388" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E388" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F388" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G388" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H388" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A389" s="20">
+        <v>46435</v>
+      </c>
+      <c r="B389" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C389" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D389" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E389" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F389" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G389" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H389" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A390" s="20">
+        <v>46436</v>
+      </c>
+      <c r="B390" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C390" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D390" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E390" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F390" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G390" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H390" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A391" s="19">
+        <v>46437</v>
+      </c>
+      <c r="B391" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C391" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D391" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E391" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F391" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G391" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H391" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A392" s="19">
+        <v>46438</v>
+      </c>
+      <c r="B392" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C392" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D392" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E392" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F392" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G392" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H392" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A393" s="20">
+        <v>46439</v>
+      </c>
+      <c r="B393" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C393" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D393" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E393" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F393" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G393" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H393" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A394" s="20">
+        <v>46440</v>
+      </c>
+      <c r="B394" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C394" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D394" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E394" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F394" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G394" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H394" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A395" s="20">
+        <v>46441</v>
+      </c>
+      <c r="B395" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C395" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D395" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E395" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F395" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G395" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H395" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A396" s="20">
+        <v>46442</v>
+      </c>
+      <c r="B396" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C396" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D396" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E396" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F396" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G396" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H396" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A397" s="20">
+        <v>46443</v>
+      </c>
+      <c r="B397" s="2">
+        <v>80000</v>
+      </c>
+      <c r="C397" s="2">
+        <v>90000</v>
+      </c>
+      <c r="D397" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E397" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F397" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G397" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H397" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A398" s="19">
+        <v>46444</v>
+      </c>
+      <c r="B398" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C398" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D398" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E398" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F398" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G398" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H398" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A399" s="19">
+        <v>46445</v>
+      </c>
+      <c r="B399" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C399" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D399" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E399" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F399" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G399" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H399" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A400" s="19">
+        <v>46446</v>
+      </c>
+      <c r="B400" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C400" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D400" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E400" s="3">
+        <v>170000</v>
+      </c>
+      <c r="F400" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G400" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H400" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A401" s="20">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A402" s="20">
+        <v>46448</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A403" s="20">
+        <v>46449</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A404" s="20">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A405" s="19">
+        <v>46451</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A406" s="19">
+        <v>46452</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A407" s="21">
+        <v>46453</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A408" s="20">
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A409" s="20">
+        <v>46455</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A410" s="20">
+        <v>46456</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A411" s="20">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A412" s="19">
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A413" s="19">
+        <v>46459</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A414" s="21">
+        <v>46460</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A415" s="20">
+        <v>46461</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A416" s="20">
+        <v>46462</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A417" s="20">
+        <v>46463</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A418" s="20">
+        <v>46464</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A419" s="19">
+        <v>46465</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A420" s="19">
+        <v>46466</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A421" s="20">
+        <v>46467</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A422" s="20">
+        <v>46468</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A423" s="20">
+        <v>46469</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A424" s="20">
+        <v>46470</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A425" s="20">
+        <v>46471</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A426" s="19">
+        <v>46472</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A427" s="19">
+        <v>46473</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A428" s="20">
+        <v>46474</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A429" s="20">
+        <v>46475</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A430" s="20">
+        <v>46476</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A431" s="20">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A432" s="20">
+        <v>46478</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A433" s="19">
+        <v>46479</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A434" s="19">
+        <v>46480</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A435" s="20">
+        <v>46481</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A436" s="20">
+        <v>46482</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A437" s="20">
+        <v>46483</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A438" s="20">
+        <v>46484</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A439" s="20">
+        <v>46485</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A440" s="19">
+        <v>46486</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A441" s="19">
+        <v>46487</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A442" s="20">
+        <v>46488</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A443" s="20">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A444" s="20">
+        <v>46490</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A445" s="20">
+        <v>46491</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A446" s="20">
+        <v>46492</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A447" s="19">
+        <v>46493</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A448" s="19">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A449" s="20">
+        <v>46495</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A450" s="20">
+        <v>46496</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A451" s="20">
+        <v>46497</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A452" s="20">
+        <v>46498</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A453" s="20">
+        <v>46499</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A454" s="19">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A455" s="19">
+        <v>46501</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A456" s="20">
+        <v>46502</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A457" s="20">
+        <v>46503</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A458" s="20">
+        <v>46504</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A459" s="20">
+        <v>46505</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A460" s="20">
+        <v>46506</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A461" s="19">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A462" s="19">
+        <v>46508</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A463" s="19">
+        <v>46509</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A464" s="19">
+        <v>46510</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A465" s="19">
+        <v>46511</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A466" s="20">
+        <v>46512</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A467" s="20">
+        <v>46513</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A468" s="20">
+        <v>46514</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A469" s="20">
+        <v>46515</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A470" s="20">
+        <v>46516</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A471" s="20">
+        <v>46517</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A472" s="20">
+        <v>46518</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A473" s="19">
+        <v>46519</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A474" s="19">
+        <v>46520</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A475" s="19">
+        <v>46521</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A476" s="19">
+        <v>46522</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A477" s="20">
+        <v>46523</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A478" s="20">
+        <v>46524</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A479" s="20">
+        <v>46525</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A480" s="20">
+        <v>46526</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A481" s="20">
+        <v>46527</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A482" s="19">
+        <v>46528</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A483" s="19">
+        <v>46529</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A484" s="20">
+        <v>46530</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A485" s="20">
+        <v>46531</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A486" s="20">
+        <v>46532</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A487" s="20">
+        <v>46533</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A488" s="20">
+        <v>46534</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A489" s="19">
+        <v>46535</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A490" s="19">
+        <v>46536</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A491" s="20">
+        <v>46537</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A492" s="20">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A493" s="20"/>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A494" s="20"/>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A495" s="20"/>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A496" s="20"/>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A497" s="20"/>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A498" s="20"/>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A499" s="20"/>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A500" s="20"/>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A501" s="20"/>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A502" s="20"/>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A503" s="20"/>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A504" s="20"/>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A505" s="20"/>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A506" s="20"/>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A507" s="20"/>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A508" s="20"/>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A509" s="20"/>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A510" s="20"/>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A511" s="20"/>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A512" s="20"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A513" s="20"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A514" s="20"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A515" s="20"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A516" s="20"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A517" s="20"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A518" s="20"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A519" s="20"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A520" s="20"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A521" s="20"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A522" s="20"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A523" s="20"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A524" s="20"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A525" s="20"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A526" s="20"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A527" s="20"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A528" s="20"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A529" s="20"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A530" s="20"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A531" s="20"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A532" s="20"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A533" s="20"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A534" s="20"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A535" s="20"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A536" s="20"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A537" s="20"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A538" s="20"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A539" s="20"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A540" s="20"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A541" s="20"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A542" s="20"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A543" s="20"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A544" s="20"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A545" s="20"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A546" s="20"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A547" s="20"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A548" s="20"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A549" s="20"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A550" s="20"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A551" s="20"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A552" s="20"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A553" s="20"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A554" s="20"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A555" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H346" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -48809,88 +50865,88 @@
   <dimension ref="B4:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="11.875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="9"/>
+    <col min="4" max="4" width="11.875" style="9" customWidth="1"/>
     <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>0.1</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>0.09</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>200000</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <f>E5*(1-(C5+D5))</f>
         <v>162000</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>100000</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="12">
         <v>200000</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>300000</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>0.15</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>228000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <f>E6*(1-(C6+D6))</f>
         <v>161880</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5+I5*H6</f>
         <v>114000</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5+J5*H6</f>
         <v>228000</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <f>K5+K5*H6</f>
         <v>342000</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/백업_기준가격.xlsx
+++ b/백업_기준가격.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\hotel-code\hotel-cmscontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1B6EA8-D94E-4D93-A3C4-A524BB0B9CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89017A82-9D61-47A8-ACED-8EF54DCC5672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,9 @@
     <sheet name="가격" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">기준가격!$A$1:$H$346</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">기준가격!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39441,7 +39440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -39491,6 +39490,8 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -39794,15 +39795,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H555"/>
+  <dimension ref="A1:Q555"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" style="9" customWidth="1"/>
     <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="18" customWidth="1"/>
+    <col min="10" max="10" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -39827,8 +39834,29 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="J1">
+        <v>10</v>
+      </c>
+      <c r="K1">
+        <v>3</v>
+      </c>
+      <c r="L1">
+        <v>12</v>
+      </c>
+      <c r="M1">
+        <v>5</v>
+      </c>
+      <c r="N1">
+        <v>6</v>
+      </c>
+      <c r="O1">
+        <v>1</v>
+      </c>
+      <c r="P1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
@@ -39854,7 +39882,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -39880,7 +39908,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -39906,7 +39934,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -39932,7 +39960,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>12</v>
       </c>
@@ -39958,7 +39986,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
@@ -39984,7 +40012,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
@@ -40010,7 +40038,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -40036,7 +40064,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>16</v>
       </c>
@@ -40062,7 +40090,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
@@ -40088,7 +40116,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>18</v>
       </c>
@@ -40114,7 +40142,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>19</v>
       </c>
@@ -40140,7 +40168,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>20</v>
       </c>
@@ -40166,7 +40194,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
@@ -40192,7 +40220,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>22</v>
       </c>
@@ -48538,7 +48566,7 @@
         <v>1100000</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A337" s="9" t="s">
         <v>343</v>
       </c>
@@ -48564,7 +48592,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A338" s="9" t="s">
         <v>344</v>
       </c>
@@ -48590,7 +48618,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A339" s="9" t="s">
         <v>345</v>
       </c>
@@ -48616,7 +48644,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A340" s="9" t="s">
         <v>346</v>
       </c>
@@ -48642,7 +48670,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="s">
         <v>347</v>
       </c>
@@ -48668,7 +48696,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A342" s="15" t="s">
         <v>348</v>
       </c>
@@ -48693,8 +48721,36 @@
       <c r="H342" s="3">
         <v>1100000</v>
       </c>
+      <c r="J342" s="7">
+        <f>$J$1*B342</f>
+        <v>2200000</v>
+      </c>
+      <c r="K342" s="7">
+        <f>$K$1*C342</f>
+        <v>720000</v>
+      </c>
+      <c r="L342" s="7">
+        <f>$K$1*D342</f>
+        <v>840000</v>
+      </c>
+      <c r="M342" s="7">
+        <f>$M$1*E342</f>
+        <v>1450000</v>
+      </c>
+      <c r="N342" s="7">
+        <f>$N$1*F342</f>
+        <v>2400000</v>
+      </c>
+      <c r="O342" s="7">
+        <f>G342</f>
+        <v>950000</v>
+      </c>
+      <c r="P342" s="2">
+        <f>H342</f>
+        <v>1100000</v>
+      </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A343" s="15" t="s">
         <v>349</v>
       </c>
@@ -48719,190 +48775,414 @@
       <c r="H343" s="3">
         <v>1100000</v>
       </c>
+      <c r="J343" s="7">
+        <f t="shared" ref="J343:J358" si="0">$J$1*B343</f>
+        <v>2200000</v>
+      </c>
+      <c r="K343" s="7">
+        <f t="shared" ref="K343:K358" si="1">$K$1*C343</f>
+        <v>720000</v>
+      </c>
+      <c r="L343" s="7">
+        <f t="shared" ref="L343:L358" si="2">$K$1*D343</f>
+        <v>840000</v>
+      </c>
+      <c r="M343" s="7">
+        <f t="shared" ref="M343:M358" si="3">$M$1*E343</f>
+        <v>1450000</v>
+      </c>
+      <c r="N343" s="7">
+        <f t="shared" ref="N343:N358" si="4">$N$1*F343</f>
+        <v>2400000</v>
+      </c>
+      <c r="O343" s="7">
+        <f t="shared" ref="O343:O358" si="5">G343</f>
+        <v>950000</v>
+      </c>
+      <c r="P343" s="2">
+        <f t="shared" ref="P343:P358" si="6">H343</f>
+        <v>1100000</v>
+      </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
         <v>350</v>
       </c>
       <c r="B344" s="2">
-        <v>140000</v>
+        <v>80000</v>
       </c>
       <c r="C344" s="2">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="D344" s="2">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E344" s="2">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="F344" s="2">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="G344" s="2">
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="H344" s="2">
-        <v>700000</v>
+        <v>400000</v>
+      </c>
+      <c r="J344" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K344" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L344" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M344" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N344" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O344" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P344" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
         <v>351</v>
       </c>
       <c r="B345" s="2">
-        <v>140000</v>
+        <v>80000</v>
       </c>
       <c r="C345" s="2">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="D345" s="2">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E345" s="2">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="F345" s="2">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="G345" s="2">
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="H345" s="2">
-        <v>700000</v>
+        <v>400000</v>
+      </c>
+      <c r="J345" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K345" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L345" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M345" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N345" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O345" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P345" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
         <v>352</v>
       </c>
       <c r="B346" s="2">
-        <v>140000</v>
+        <v>80000</v>
       </c>
       <c r="C346" s="2">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="D346" s="2">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E346" s="2">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="F346" s="2">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="G346" s="2">
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="H346" s="2">
-        <v>700000</v>
+        <v>400000</v>
+      </c>
+      <c r="J346" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K346" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L346" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M346" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N346" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O346" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P346" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
         <v>353</v>
       </c>
       <c r="B347" s="2">
-        <v>140000</v>
+        <v>80000</v>
       </c>
       <c r="C347" s="2">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="D347" s="2">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E347" s="2">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="F347" s="2">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="G347" s="2">
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="H347" s="2">
-        <v>700000</v>
+        <v>400000</v>
+      </c>
+      <c r="J347" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K347" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L347" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M347" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N347" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O347" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P347" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
         <v>354</v>
       </c>
       <c r="B348" s="2">
-        <v>140000</v>
+        <v>80000</v>
       </c>
       <c r="C348" s="2">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="D348" s="2">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E348" s="2">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="F348" s="2">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="G348" s="2">
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="H348" s="2">
-        <v>700000</v>
+        <v>400000</v>
+      </c>
+      <c r="J348" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K348" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L348" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M348" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N348" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O348" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P348" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A349" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B349" s="4">
+      <c r="B349" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C349" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D349" s="3">
         <v>160000</v>
       </c>
-      <c r="C349" s="3">
+      <c r="E349" s="3">
         <v>170000</v>
       </c>
-      <c r="D349" s="3">
-        <v>240000</v>
-      </c>
-      <c r="E349" s="4">
-        <v>250000</v>
-      </c>
-      <c r="F349" s="4">
-        <v>300000</v>
+      <c r="F349" s="3">
+        <v>190000</v>
       </c>
       <c r="G349" s="3">
-        <v>750000</v>
+        <v>400000</v>
       </c>
       <c r="H349" s="3">
-        <v>900000</v>
+        <v>500000</v>
+      </c>
+      <c r="J349" s="7">
+        <f t="shared" si="0"/>
+        <v>1100000</v>
+      </c>
+      <c r="K349" s="7">
+        <f t="shared" si="1"/>
+        <v>390000</v>
+      </c>
+      <c r="L349" s="7">
+        <f t="shared" si="2"/>
+        <v>480000</v>
+      </c>
+      <c r="M349" s="7">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="N349" s="7">
+        <f t="shared" si="4"/>
+        <v>1140000</v>
+      </c>
+      <c r="O349" s="7">
+        <f t="shared" si="5"/>
+        <v>400000</v>
+      </c>
+      <c r="P349" s="2">
+        <f t="shared" si="6"/>
+        <v>500000</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A350" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="3">
+        <v>110000</v>
+      </c>
+      <c r="C350" s="3">
+        <v>130000</v>
+      </c>
+      <c r="D350" s="3">
         <v>160000</v>
       </c>
-      <c r="C350" s="3">
+      <c r="E350" s="3">
         <v>170000</v>
       </c>
-      <c r="D350" s="3">
-        <v>240000</v>
-      </c>
-      <c r="E350" s="4">
-        <v>250000</v>
-      </c>
-      <c r="F350" s="4">
-        <v>300000</v>
+      <c r="F350" s="3">
+        <v>190000</v>
       </c>
       <c r="G350" s="3">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="H350" s="3">
-        <v>950000</v>
+        <v>500000</v>
+      </c>
+      <c r="J350" s="7">
+        <f t="shared" si="0"/>
+        <v>1100000</v>
+      </c>
+      <c r="K350" s="7">
+        <f t="shared" si="1"/>
+        <v>390000</v>
+      </c>
+      <c r="L350" s="7">
+        <f t="shared" si="2"/>
+        <v>480000</v>
+      </c>
+      <c r="M350" s="7">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="N350" s="7">
+        <f t="shared" si="4"/>
+        <v>1140000</v>
+      </c>
+      <c r="O350" s="7">
+        <f t="shared" si="5"/>
+        <v>400000</v>
+      </c>
+      <c r="P350" s="2">
+        <f t="shared" si="6"/>
+        <v>500000</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
         <v>362</v>
       </c>
@@ -48927,8 +49207,36 @@
       <c r="H351" s="2">
         <v>400000</v>
       </c>
+      <c r="J351" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K351" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L351" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M351" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N351" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O351" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P351" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
         <v>363</v>
       </c>
@@ -48953,8 +49261,36 @@
       <c r="H352" s="2">
         <v>400000</v>
       </c>
+      <c r="J352" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K352" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L352" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M352" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N352" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O352" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P352" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
         <v>364</v>
       </c>
@@ -48979,8 +49315,36 @@
       <c r="H353" s="2">
         <v>400000</v>
       </c>
+      <c r="J353" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K353" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L353" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M353" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N353" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O353" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P353" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
         <v>365</v>
       </c>
@@ -49005,8 +49369,36 @@
       <c r="H354" s="2">
         <v>400000</v>
       </c>
+      <c r="J354" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K354" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L354" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M354" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N354" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O354" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P354" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
         <v>366</v>
       </c>
@@ -49031,8 +49423,36 @@
       <c r="H355" s="2">
         <v>400000</v>
       </c>
+      <c r="J355" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K355" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L355" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M355" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N355" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O355" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P355" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A356" s="17" t="s">
         <v>367</v>
       </c>
@@ -49057,8 +49477,36 @@
       <c r="H356" s="3">
         <v>500000</v>
       </c>
+      <c r="J356" s="7">
+        <f t="shared" si="0"/>
+        <v>1100000</v>
+      </c>
+      <c r="K356" s="7">
+        <f t="shared" si="1"/>
+        <v>390000</v>
+      </c>
+      <c r="L356" s="7">
+        <f t="shared" si="2"/>
+        <v>480000</v>
+      </c>
+      <c r="M356" s="7">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="N356" s="7">
+        <f t="shared" si="4"/>
+        <v>1140000</v>
+      </c>
+      <c r="O356" s="7">
+        <f t="shared" si="5"/>
+        <v>400000</v>
+      </c>
+      <c r="P356" s="2">
+        <f t="shared" si="6"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A357" s="18" t="s">
         <v>368</v>
       </c>
@@ -49083,8 +49531,36 @@
       <c r="H357" s="3">
         <v>500000</v>
       </c>
+      <c r="J357" s="7">
+        <f t="shared" si="0"/>
+        <v>1100000</v>
+      </c>
+      <c r="K357" s="7">
+        <f t="shared" si="1"/>
+        <v>390000</v>
+      </c>
+      <c r="L357" s="7">
+        <f t="shared" si="2"/>
+        <v>480000</v>
+      </c>
+      <c r="M357" s="7">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="N357" s="7">
+        <f t="shared" si="4"/>
+        <v>1140000</v>
+      </c>
+      <c r="O357" s="7">
+        <f t="shared" si="5"/>
+        <v>400000</v>
+      </c>
+      <c r="P357" s="2">
+        <f t="shared" si="6"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
         <v>369</v>
       </c>
@@ -49109,8 +49585,36 @@
       <c r="H358" s="2">
         <v>400000</v>
       </c>
+      <c r="J358" s="7">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K358" s="7">
+        <f t="shared" si="1"/>
+        <v>270000</v>
+      </c>
+      <c r="L358" s="7">
+        <f t="shared" si="2"/>
+        <v>285000</v>
+      </c>
+      <c r="M358" s="7">
+        <f t="shared" si="3"/>
+        <v>475000</v>
+      </c>
+      <c r="N358" s="7">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="O358" s="7">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="P358" s="2">
+        <f t="shared" si="6"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
         <v>370</v>
       </c>
@@ -49135,8 +49639,36 @@
       <c r="H359" s="2">
         <v>400000</v>
       </c>
+      <c r="J359" s="7">
+        <f t="shared" ref="J359:J377" si="7">$J$1*B359</f>
+        <v>800000</v>
+      </c>
+      <c r="K359" s="7">
+        <f t="shared" ref="K359:K377" si="8">$K$1*C359</f>
+        <v>270000</v>
+      </c>
+      <c r="L359" s="7">
+        <f t="shared" ref="L359:L377" si="9">$K$1*D359</f>
+        <v>285000</v>
+      </c>
+      <c r="M359" s="7">
+        <f t="shared" ref="M359:M377" si="10">$M$1*E359</f>
+        <v>475000</v>
+      </c>
+      <c r="N359" s="7">
+        <f t="shared" ref="N359:N377" si="11">$N$1*F359</f>
+        <v>600000</v>
+      </c>
+      <c r="O359" s="7">
+        <f t="shared" ref="O359:O377" si="12">G359</f>
+        <v>300000</v>
+      </c>
+      <c r="P359" s="2">
+        <f t="shared" ref="P359:P377" si="13">H359</f>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
         <v>371</v>
       </c>
@@ -49161,8 +49693,36 @@
       <c r="H360" s="2">
         <v>400000</v>
       </c>
+      <c r="J360" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K360" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L360" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M360" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N360" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O360" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P360" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
         <v>372</v>
       </c>
@@ -49187,8 +49747,36 @@
       <c r="H361" s="2">
         <v>400000</v>
       </c>
+      <c r="J361" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K361" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L361" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M361" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N361" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O361" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P361" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="s">
         <v>373</v>
       </c>
@@ -49213,8 +49801,36 @@
       <c r="H362" s="2">
         <v>400000</v>
       </c>
+      <c r="J362" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K362" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L362" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M362" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N362" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O362" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P362" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A363" s="17" t="s">
         <v>374</v>
       </c>
@@ -49239,8 +49855,36 @@
       <c r="H363" s="3">
         <v>500000</v>
       </c>
+      <c r="J363" s="7">
+        <f t="shared" si="7"/>
+        <v>1100000</v>
+      </c>
+      <c r="K363" s="7">
+        <f t="shared" si="8"/>
+        <v>390000</v>
+      </c>
+      <c r="L363" s="7">
+        <f t="shared" si="9"/>
+        <v>480000</v>
+      </c>
+      <c r="M363" s="7">
+        <f t="shared" si="10"/>
+        <v>850000</v>
+      </c>
+      <c r="N363" s="7">
+        <f t="shared" si="11"/>
+        <v>1140000</v>
+      </c>
+      <c r="O363" s="7">
+        <f t="shared" si="12"/>
+        <v>400000</v>
+      </c>
+      <c r="P363" s="2">
+        <f t="shared" si="13"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A364" s="18" t="s">
         <v>375</v>
       </c>
@@ -49265,8 +49909,36 @@
       <c r="H364" s="3">
         <v>500000</v>
       </c>
+      <c r="J364" s="7">
+        <f t="shared" si="7"/>
+        <v>1100000</v>
+      </c>
+      <c r="K364" s="7">
+        <f t="shared" si="8"/>
+        <v>390000</v>
+      </c>
+      <c r="L364" s="7">
+        <f t="shared" si="9"/>
+        <v>480000</v>
+      </c>
+      <c r="M364" s="7">
+        <f t="shared" si="10"/>
+        <v>850000</v>
+      </c>
+      <c r="N364" s="7">
+        <f t="shared" si="11"/>
+        <v>1140000</v>
+      </c>
+      <c r="O364" s="7">
+        <f t="shared" si="12"/>
+        <v>400000</v>
+      </c>
+      <c r="P364" s="2">
+        <f t="shared" si="13"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
         <v>376</v>
       </c>
@@ -49291,8 +49963,36 @@
       <c r="H365" s="2">
         <v>400000</v>
       </c>
+      <c r="J365" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K365" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L365" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M365" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N365" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O365" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P365" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
         <v>377</v>
       </c>
@@ -49317,8 +50017,36 @@
       <c r="H366" s="2">
         <v>400000</v>
       </c>
+      <c r="J366" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K366" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L366" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M366" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N366" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O366" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P366" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
         <v>378</v>
       </c>
@@ -49343,8 +50071,36 @@
       <c r="H367" s="2">
         <v>400000</v>
       </c>
+      <c r="J367" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K367" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L367" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M367" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N367" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O367" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P367" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
         <v>379</v>
       </c>
@@ -49369,8 +50125,36 @@
       <c r="H368" s="2">
         <v>400000</v>
       </c>
+      <c r="J368" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K368" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L368" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M368" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N368" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O368" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P368" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
         <v>380</v>
       </c>
@@ -49395,8 +50179,36 @@
       <c r="H369" s="2">
         <v>400000</v>
       </c>
+      <c r="J369" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K369" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L369" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M369" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N369" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O369" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P369" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A370" s="17" t="s">
         <v>381</v>
       </c>
@@ -49421,8 +50233,36 @@
       <c r="H370" s="3">
         <v>500000</v>
       </c>
+      <c r="J370" s="7">
+        <f t="shared" si="7"/>
+        <v>1100000</v>
+      </c>
+      <c r="K370" s="7">
+        <f t="shared" si="8"/>
+        <v>390000</v>
+      </c>
+      <c r="L370" s="7">
+        <f t="shared" si="9"/>
+        <v>480000</v>
+      </c>
+      <c r="M370" s="7">
+        <f t="shared" si="10"/>
+        <v>850000</v>
+      </c>
+      <c r="N370" s="7">
+        <f t="shared" si="11"/>
+        <v>1140000</v>
+      </c>
+      <c r="O370" s="7">
+        <f t="shared" si="12"/>
+        <v>400000</v>
+      </c>
+      <c r="P370" s="2">
+        <f t="shared" si="13"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A371" s="19" t="s">
         <v>382</v>
       </c>
@@ -49447,8 +50287,36 @@
       <c r="H371" s="3">
         <v>500000</v>
       </c>
+      <c r="J371" s="7">
+        <f t="shared" si="7"/>
+        <v>1100000</v>
+      </c>
+      <c r="K371" s="7">
+        <f t="shared" si="8"/>
+        <v>390000</v>
+      </c>
+      <c r="L371" s="7">
+        <f t="shared" si="9"/>
+        <v>480000</v>
+      </c>
+      <c r="M371" s="7">
+        <f t="shared" si="10"/>
+        <v>850000</v>
+      </c>
+      <c r="N371" s="7">
+        <f t="shared" si="11"/>
+        <v>1140000</v>
+      </c>
+      <c r="O371" s="7">
+        <f t="shared" si="12"/>
+        <v>400000</v>
+      </c>
+      <c r="P371" s="2">
+        <f t="shared" si="13"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A372" s="22">
         <v>46418</v>
       </c>
@@ -49473,8 +50341,40 @@
       <c r="H372" s="2">
         <v>400000</v>
       </c>
+      <c r="J372" s="23">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K372" s="23">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L372" s="23">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M372" s="23">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N372" s="23">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O372" s="23">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P372" s="5">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
+      <c r="Q372" s="24">
+        <f>SUM(J342:P372)</f>
+        <v>123930000</v>
+      </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A373" s="20">
         <v>46419</v>
       </c>
@@ -49499,8 +50399,36 @@
       <c r="H373" s="2">
         <v>400000</v>
       </c>
+      <c r="J373" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K373" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L373" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M373" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N373" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O373" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P373" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A374" s="20">
         <v>46420</v>
       </c>
@@ -49525,8 +50453,36 @@
       <c r="H374" s="2">
         <v>400000</v>
       </c>
+      <c r="J374" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K374" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L374" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M374" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N374" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O374" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P374" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A375" s="20">
         <v>46421</v>
       </c>
@@ -49551,8 +50507,36 @@
       <c r="H375" s="2">
         <v>400000</v>
       </c>
+      <c r="J375" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K375" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L375" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M375" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N375" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O375" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P375" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A376" s="20">
         <v>46422</v>
       </c>
@@ -49577,8 +50561,36 @@
       <c r="H376" s="2">
         <v>400000</v>
       </c>
+      <c r="J376" s="7">
+        <f t="shared" si="7"/>
+        <v>800000</v>
+      </c>
+      <c r="K376" s="7">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L376" s="7">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="M376" s="7">
+        <f t="shared" si="10"/>
+        <v>475000</v>
+      </c>
+      <c r="N376" s="7">
+        <f t="shared" si="11"/>
+        <v>600000</v>
+      </c>
+      <c r="O376" s="7">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="P376" s="2">
+        <f t="shared" si="13"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A377" s="19">
         <v>46423</v>
       </c>
@@ -49603,8 +50615,36 @@
       <c r="H377" s="3">
         <v>500000</v>
       </c>
+      <c r="J377" s="7">
+        <f t="shared" si="7"/>
+        <v>1100000</v>
+      </c>
+      <c r="K377" s="7">
+        <f t="shared" si="8"/>
+        <v>390000</v>
+      </c>
+      <c r="L377" s="7">
+        <f t="shared" si="9"/>
+        <v>480000</v>
+      </c>
+      <c r="M377" s="7">
+        <f t="shared" si="10"/>
+        <v>850000</v>
+      </c>
+      <c r="N377" s="7">
+        <f t="shared" si="11"/>
+        <v>1140000</v>
+      </c>
+      <c r="O377" s="7">
+        <f t="shared" si="12"/>
+        <v>400000</v>
+      </c>
+      <c r="P377" s="2">
+        <f t="shared" si="13"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A378" s="19">
         <v>46424</v>
       </c>
@@ -49629,8 +50669,36 @@
       <c r="H378" s="3">
         <v>500000</v>
       </c>
+      <c r="J378" s="7">
+        <f>$J$1*B378</f>
+        <v>1100000</v>
+      </c>
+      <c r="K378" s="7">
+        <f>$K$1*C378</f>
+        <v>390000</v>
+      </c>
+      <c r="L378" s="7">
+        <f>$K$1*D378</f>
+        <v>480000</v>
+      </c>
+      <c r="M378" s="7">
+        <f>$M$1*E378</f>
+        <v>850000</v>
+      </c>
+      <c r="N378" s="7">
+        <f>$N$1*F378</f>
+        <v>1140000</v>
+      </c>
+      <c r="O378" s="7">
+        <f>G378</f>
+        <v>400000</v>
+      </c>
+      <c r="P378" s="2">
+        <f>H378</f>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" s="19">
         <v>46425</v>
       </c>
@@ -49655,8 +50723,36 @@
       <c r="H379" s="3">
         <v>500000</v>
       </c>
+      <c r="J379" s="7">
+        <f t="shared" ref="J379:J395" si="14">$J$1*B379</f>
+        <v>1100000</v>
+      </c>
+      <c r="K379" s="7">
+        <f t="shared" ref="K379:K395" si="15">$K$1*C379</f>
+        <v>390000</v>
+      </c>
+      <c r="L379" s="7">
+        <f t="shared" ref="L379:L395" si="16">$K$1*D379</f>
+        <v>480000</v>
+      </c>
+      <c r="M379" s="7">
+        <f t="shared" ref="M379:M395" si="17">$M$1*E379</f>
+        <v>850000</v>
+      </c>
+      <c r="N379" s="7">
+        <f t="shared" ref="N379:N395" si="18">$N$1*F379</f>
+        <v>1140000</v>
+      </c>
+      <c r="O379" s="7">
+        <f t="shared" ref="O379:O395" si="19">G379</f>
+        <v>400000</v>
+      </c>
+      <c r="P379" s="2">
+        <f t="shared" ref="P379:P395" si="20">H379</f>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A380" s="19">
         <v>46426</v>
       </c>
@@ -49681,8 +50777,36 @@
       <c r="H380" s="3">
         <v>500000</v>
       </c>
+      <c r="J380" s="7">
+        <f t="shared" si="14"/>
+        <v>1100000</v>
+      </c>
+      <c r="K380" s="7">
+        <f t="shared" si="15"/>
+        <v>390000</v>
+      </c>
+      <c r="L380" s="7">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="M380" s="7">
+        <f t="shared" si="17"/>
+        <v>850000</v>
+      </c>
+      <c r="N380" s="7">
+        <f t="shared" si="18"/>
+        <v>1140000</v>
+      </c>
+      <c r="O380" s="7">
+        <f t="shared" si="19"/>
+        <v>400000</v>
+      </c>
+      <c r="P380" s="2">
+        <f t="shared" si="20"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A381" s="21">
         <v>46427</v>
       </c>
@@ -49707,8 +50831,36 @@
       <c r="H381" s="2">
         <v>400000</v>
       </c>
+      <c r="J381" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K381" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L381" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M381" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N381" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O381" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P381" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" s="20">
         <v>46428</v>
       </c>
@@ -49733,8 +50885,36 @@
       <c r="H382" s="2">
         <v>400000</v>
       </c>
+      <c r="J382" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K382" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L382" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M382" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N382" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O382" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P382" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A383" s="20">
         <v>46429</v>
       </c>
@@ -49759,8 +50939,36 @@
       <c r="H383" s="2">
         <v>400000</v>
       </c>
+      <c r="J383" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K383" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L383" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M383" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N383" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O383" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P383" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A384" s="19">
         <v>46430</v>
       </c>
@@ -49785,8 +50993,36 @@
       <c r="H384" s="3">
         <v>500000</v>
       </c>
+      <c r="J384" s="7">
+        <f t="shared" si="14"/>
+        <v>1100000</v>
+      </c>
+      <c r="K384" s="7">
+        <f t="shared" si="15"/>
+        <v>390000</v>
+      </c>
+      <c r="L384" s="7">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="M384" s="7">
+        <f t="shared" si="17"/>
+        <v>850000</v>
+      </c>
+      <c r="N384" s="7">
+        <f t="shared" si="18"/>
+        <v>1140000</v>
+      </c>
+      <c r="O384" s="7">
+        <f t="shared" si="19"/>
+        <v>400000</v>
+      </c>
+      <c r="P384" s="2">
+        <f t="shared" si="20"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A385" s="19">
         <v>46431</v>
       </c>
@@ -49811,8 +51047,36 @@
       <c r="H385" s="3">
         <v>500000</v>
       </c>
+      <c r="J385" s="7">
+        <f t="shared" si="14"/>
+        <v>1100000</v>
+      </c>
+      <c r="K385" s="7">
+        <f t="shared" si="15"/>
+        <v>390000</v>
+      </c>
+      <c r="L385" s="7">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="M385" s="7">
+        <f t="shared" si="17"/>
+        <v>850000</v>
+      </c>
+      <c r="N385" s="7">
+        <f t="shared" si="18"/>
+        <v>1140000</v>
+      </c>
+      <c r="O385" s="7">
+        <f t="shared" si="19"/>
+        <v>400000</v>
+      </c>
+      <c r="P385" s="2">
+        <f t="shared" si="20"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A386" s="21">
         <v>46432</v>
       </c>
@@ -49837,8 +51101,36 @@
       <c r="H386" s="2">
         <v>400000</v>
       </c>
+      <c r="J386" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K386" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L386" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M386" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N386" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O386" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P386" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A387" s="20">
         <v>46433</v>
       </c>
@@ -49863,8 +51155,36 @@
       <c r="H387" s="2">
         <v>400000</v>
       </c>
+      <c r="J387" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K387" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L387" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M387" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N387" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O387" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P387" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A388" s="20">
         <v>46434</v>
       </c>
@@ -49889,8 +51209,36 @@
       <c r="H388" s="2">
         <v>400000</v>
       </c>
+      <c r="J388" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K388" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L388" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M388" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N388" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O388" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P388" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A389" s="20">
         <v>46435</v>
       </c>
@@ -49915,8 +51263,36 @@
       <c r="H389" s="2">
         <v>400000</v>
       </c>
+      <c r="J389" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K389" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L389" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M389" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N389" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O389" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P389" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A390" s="20">
         <v>46436</v>
       </c>
@@ -49941,8 +51317,36 @@
       <c r="H390" s="2">
         <v>400000</v>
       </c>
+      <c r="J390" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K390" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L390" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M390" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N390" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O390" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P390" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A391" s="19">
         <v>46437</v>
       </c>
@@ -49967,8 +51371,36 @@
       <c r="H391" s="3">
         <v>500000</v>
       </c>
+      <c r="J391" s="7">
+        <f t="shared" si="14"/>
+        <v>1100000</v>
+      </c>
+      <c r="K391" s="7">
+        <f t="shared" si="15"/>
+        <v>390000</v>
+      </c>
+      <c r="L391" s="7">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="M391" s="7">
+        <f t="shared" si="17"/>
+        <v>850000</v>
+      </c>
+      <c r="N391" s="7">
+        <f t="shared" si="18"/>
+        <v>1140000</v>
+      </c>
+      <c r="O391" s="7">
+        <f t="shared" si="19"/>
+        <v>400000</v>
+      </c>
+      <c r="P391" s="2">
+        <f t="shared" si="20"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A392" s="19">
         <v>46438</v>
       </c>
@@ -49993,8 +51425,36 @@
       <c r="H392" s="3">
         <v>500000</v>
       </c>
+      <c r="J392" s="7">
+        <f t="shared" si="14"/>
+        <v>1100000</v>
+      </c>
+      <c r="K392" s="7">
+        <f t="shared" si="15"/>
+        <v>390000</v>
+      </c>
+      <c r="L392" s="7">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="M392" s="7">
+        <f t="shared" si="17"/>
+        <v>850000</v>
+      </c>
+      <c r="N392" s="7">
+        <f t="shared" si="18"/>
+        <v>1140000</v>
+      </c>
+      <c r="O392" s="7">
+        <f t="shared" si="19"/>
+        <v>400000</v>
+      </c>
+      <c r="P392" s="2">
+        <f t="shared" si="20"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A393" s="20">
         <v>46439</v>
       </c>
@@ -50019,8 +51479,36 @@
       <c r="H393" s="2">
         <v>400000</v>
       </c>
+      <c r="J393" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K393" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L393" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M393" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N393" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O393" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P393" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A394" s="20">
         <v>46440</v>
       </c>
@@ -50045,8 +51533,36 @@
       <c r="H394" s="2">
         <v>400000</v>
       </c>
+      <c r="J394" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K394" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L394" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M394" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N394" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O394" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P394" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A395" s="20">
         <v>46441</v>
       </c>
@@ -50071,8 +51587,36 @@
       <c r="H395" s="2">
         <v>400000</v>
       </c>
+      <c r="J395" s="7">
+        <f t="shared" si="14"/>
+        <v>800000</v>
+      </c>
+      <c r="K395" s="7">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="L395" s="7">
+        <f t="shared" si="16"/>
+        <v>285000</v>
+      </c>
+      <c r="M395" s="7">
+        <f t="shared" si="17"/>
+        <v>475000</v>
+      </c>
+      <c r="N395" s="7">
+        <f t="shared" si="18"/>
+        <v>600000</v>
+      </c>
+      <c r="O395" s="7">
+        <f t="shared" si="19"/>
+        <v>300000</v>
+      </c>
+      <c r="P395" s="2">
+        <f t="shared" si="20"/>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A396" s="20">
         <v>46442</v>
       </c>
@@ -50097,8 +51641,36 @@
       <c r="H396" s="2">
         <v>400000</v>
       </c>
+      <c r="J396" s="7">
+        <f>$J$1*B396</f>
+        <v>800000</v>
+      </c>
+      <c r="K396" s="7">
+        <f>$K$1*C396</f>
+        <v>270000</v>
+      </c>
+      <c r="L396" s="7">
+        <f>$K$1*D396</f>
+        <v>285000</v>
+      </c>
+      <c r="M396" s="7">
+        <f>$M$1*E396</f>
+        <v>475000</v>
+      </c>
+      <c r="N396" s="7">
+        <f>$N$1*F396</f>
+        <v>600000</v>
+      </c>
+      <c r="O396" s="7">
+        <f>G396</f>
+        <v>300000</v>
+      </c>
+      <c r="P396" s="2">
+        <f>H396</f>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A397" s="20">
         <v>46443</v>
       </c>
@@ -50123,8 +51695,36 @@
       <c r="H397" s="2">
         <v>400000</v>
       </c>
+      <c r="J397" s="7">
+        <f t="shared" ref="J397:J400" si="21">$J$1*B397</f>
+        <v>800000</v>
+      </c>
+      <c r="K397" s="7">
+        <f t="shared" ref="K397:K400" si="22">$K$1*C397</f>
+        <v>270000</v>
+      </c>
+      <c r="L397" s="7">
+        <f t="shared" ref="L397:L400" si="23">$K$1*D397</f>
+        <v>285000</v>
+      </c>
+      <c r="M397" s="7">
+        <f t="shared" ref="M397:M400" si="24">$M$1*E397</f>
+        <v>475000</v>
+      </c>
+      <c r="N397" s="7">
+        <f t="shared" ref="N397:N400" si="25">$N$1*F397</f>
+        <v>600000</v>
+      </c>
+      <c r="O397" s="7">
+        <f t="shared" ref="O397:O400" si="26">G397</f>
+        <v>300000</v>
+      </c>
+      <c r="P397" s="2">
+        <f t="shared" ref="P397:P400" si="27">H397</f>
+        <v>400000</v>
+      </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A398" s="19">
         <v>46444</v>
       </c>
@@ -50149,8 +51749,36 @@
       <c r="H398" s="3">
         <v>500000</v>
       </c>
+      <c r="J398" s="7">
+        <f t="shared" si="21"/>
+        <v>1100000</v>
+      </c>
+      <c r="K398" s="7">
+        <f t="shared" si="22"/>
+        <v>390000</v>
+      </c>
+      <c r="L398" s="7">
+        <f t="shared" si="23"/>
+        <v>480000</v>
+      </c>
+      <c r="M398" s="7">
+        <f t="shared" si="24"/>
+        <v>850000</v>
+      </c>
+      <c r="N398" s="7">
+        <f t="shared" si="25"/>
+        <v>1140000</v>
+      </c>
+      <c r="O398" s="7">
+        <f t="shared" si="26"/>
+        <v>400000</v>
+      </c>
+      <c r="P398" s="2">
+        <f t="shared" si="27"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A399" s="19">
         <v>46445</v>
       </c>
@@ -50175,8 +51803,36 @@
       <c r="H399" s="3">
         <v>500000</v>
       </c>
+      <c r="J399" s="7">
+        <f t="shared" si="21"/>
+        <v>1100000</v>
+      </c>
+      <c r="K399" s="7">
+        <f t="shared" si="22"/>
+        <v>390000</v>
+      </c>
+      <c r="L399" s="7">
+        <f t="shared" si="23"/>
+        <v>480000</v>
+      </c>
+      <c r="M399" s="7">
+        <f t="shared" si="24"/>
+        <v>850000</v>
+      </c>
+      <c r="N399" s="7">
+        <f t="shared" si="25"/>
+        <v>1140000</v>
+      </c>
+      <c r="O399" s="7">
+        <f t="shared" si="26"/>
+        <v>400000</v>
+      </c>
+      <c r="P399" s="2">
+        <f t="shared" si="27"/>
+        <v>500000</v>
+      </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A400" s="19">
         <v>46446</v>
       </c>
@@ -50201,573 +51857,4162 @@
       <c r="H400" s="3">
         <v>500000</v>
       </c>
+      <c r="J400" s="7">
+        <f t="shared" si="21"/>
+        <v>1100000</v>
+      </c>
+      <c r="K400" s="7">
+        <f t="shared" si="22"/>
+        <v>390000</v>
+      </c>
+      <c r="L400" s="7">
+        <f t="shared" si="23"/>
+        <v>480000</v>
+      </c>
+      <c r="M400" s="7">
+        <f t="shared" si="24"/>
+        <v>850000</v>
+      </c>
+      <c r="N400" s="7">
+        <f t="shared" si="25"/>
+        <v>1140000</v>
+      </c>
+      <c r="O400" s="7">
+        <f t="shared" si="26"/>
+        <v>400000</v>
+      </c>
+      <c r="P400" s="2">
+        <f t="shared" si="27"/>
+        <v>500000</v>
+      </c>
+      <c r="Q400" s="24">
+        <f>SUM(J373:P400)</f>
+        <v>106670000</v>
+      </c>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A401" s="20">
         <v>46447</v>
       </c>
+      <c r="J401" s="7">
+        <f t="shared" ref="J401:J464" si="28">$J$1*B401</f>
+        <v>0</v>
+      </c>
+      <c r="K401" s="7">
+        <f t="shared" ref="K401:K464" si="29">$K$1*C401</f>
+        <v>0</v>
+      </c>
+      <c r="L401" s="7">
+        <f t="shared" ref="L401:L464" si="30">$K$1*D401</f>
+        <v>0</v>
+      </c>
+      <c r="M401" s="7">
+        <f t="shared" ref="M401:M464" si="31">$M$1*E401</f>
+        <v>0</v>
+      </c>
+      <c r="N401" s="7">
+        <f t="shared" ref="N401:N464" si="32">$N$1*F401</f>
+        <v>0</v>
+      </c>
+      <c r="O401" s="7">
+        <f t="shared" ref="O401:O464" si="33">G401</f>
+        <v>0</v>
+      </c>
+      <c r="P401" s="2">
+        <f t="shared" ref="P401:P464" si="34">H401</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A402" s="20">
         <v>46448</v>
       </c>
+      <c r="J402" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K402" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L402" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M402" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N402" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O402" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P402" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A403" s="20">
         <v>46449</v>
       </c>
+      <c r="J403" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K403" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L403" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M403" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N403" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O403" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P403" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A404" s="20">
         <v>46450</v>
       </c>
+      <c r="J404" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K404" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L404" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M404" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N404" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O404" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P404" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A405" s="19">
         <v>46451</v>
       </c>
+      <c r="J405" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K405" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L405" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M405" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N405" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O405" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P405" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A406" s="19">
         <v>46452</v>
       </c>
+      <c r="J406" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K406" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L406" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M406" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N406" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O406" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P406" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A407" s="21">
         <v>46453</v>
       </c>
+      <c r="J407" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K407" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L407" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M407" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N407" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O407" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P407" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A408" s="20">
         <v>46454</v>
       </c>
+      <c r="J408" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K408" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L408" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M408" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N408" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O408" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P408" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A409" s="20">
         <v>46455</v>
       </c>
+      <c r="J409" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K409" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L409" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M409" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N409" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O409" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P409" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A410" s="20">
         <v>46456</v>
       </c>
+      <c r="J410" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K410" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L410" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M410" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N410" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O410" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P410" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A411" s="20">
         <v>46457</v>
       </c>
+      <c r="J411" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K411" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L411" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M411" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N411" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O411" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P411" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A412" s="19">
         <v>46458</v>
       </c>
+      <c r="J412" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K412" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L412" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M412" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N412" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O412" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P412" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A413" s="19">
         <v>46459</v>
       </c>
+      <c r="J413" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K413" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L413" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M413" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N413" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O413" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P413" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A414" s="21">
         <v>46460</v>
       </c>
+      <c r="J414" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K414" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L414" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M414" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N414" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O414" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P414" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A415" s="20">
         <v>46461</v>
       </c>
+      <c r="J415" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K415" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L415" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M415" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N415" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O415" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P415" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A416" s="20">
         <v>46462</v>
       </c>
+      <c r="J416" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K416" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L416" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M416" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N416" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O416" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P416" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A417" s="20">
         <v>46463</v>
       </c>
+      <c r="J417" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K417" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L417" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M417" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N417" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O417" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P417" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A418" s="20">
         <v>46464</v>
       </c>
+      <c r="J418" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K418" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L418" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M418" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N418" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O418" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P418" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A419" s="19">
         <v>46465</v>
       </c>
+      <c r="J419" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K419" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L419" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M419" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N419" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O419" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P419" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A420" s="19">
         <v>46466</v>
       </c>
+      <c r="J420" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K420" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L420" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M420" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N420" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O420" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P420" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A421" s="20">
         <v>46467</v>
       </c>
+      <c r="J421" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K421" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L421" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M421" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N421" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O421" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P421" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A422" s="20">
         <v>46468</v>
       </c>
+      <c r="J422" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K422" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L422" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M422" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N422" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O422" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P422" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A423" s="20">
         <v>46469</v>
       </c>
+      <c r="J423" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K423" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L423" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M423" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N423" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O423" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P423" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A424" s="20">
         <v>46470</v>
       </c>
+      <c r="J424" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K424" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L424" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M424" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N424" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O424" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P424" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A425" s="20">
         <v>46471</v>
       </c>
+      <c r="J425" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K425" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L425" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M425" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N425" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O425" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P425" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A426" s="19">
         <v>46472</v>
       </c>
+      <c r="J426" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K426" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L426" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M426" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N426" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O426" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P426" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A427" s="19">
         <v>46473</v>
       </c>
+      <c r="J427" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K427" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L427" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M427" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N427" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O427" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P427" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A428" s="20">
         <v>46474</v>
       </c>
+      <c r="J428" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K428" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L428" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M428" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N428" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O428" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P428" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A429" s="20">
         <v>46475</v>
       </c>
+      <c r="J429" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K429" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L429" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M429" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N429" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O429" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P429" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A430" s="20">
         <v>46476</v>
       </c>
+      <c r="J430" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K430" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L430" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M430" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N430" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O430" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P430" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A431" s="20">
         <v>46477</v>
       </c>
+      <c r="J431" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K431" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L431" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M431" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N431" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O431" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P431" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A432" s="20">
         <v>46478</v>
       </c>
+      <c r="J432" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K432" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L432" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M432" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N432" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O432" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P432" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A433" s="19">
         <v>46479</v>
       </c>
+      <c r="J433" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K433" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L433" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M433" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N433" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O433" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P433" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A434" s="19">
         <v>46480</v>
       </c>
+      <c r="J434" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K434" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L434" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M434" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N434" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O434" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P434" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A435" s="20">
         <v>46481</v>
       </c>
+      <c r="J435" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K435" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L435" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M435" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N435" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O435" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P435" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A436" s="20">
         <v>46482</v>
       </c>
+      <c r="J436" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K436" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L436" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M436" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N436" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O436" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P436" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A437" s="20">
         <v>46483</v>
       </c>
+      <c r="J437" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K437" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L437" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M437" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N437" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O437" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P437" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A438" s="20">
         <v>46484</v>
       </c>
+      <c r="J438" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K438" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L438" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M438" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N438" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O438" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P438" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A439" s="20">
         <v>46485</v>
       </c>
+      <c r="J439" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K439" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L439" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M439" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N439" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O439" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P439" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A440" s="19">
         <v>46486</v>
       </c>
+      <c r="J440" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K440" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L440" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M440" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N440" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O440" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P440" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A441" s="19">
         <v>46487</v>
       </c>
+      <c r="J441" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K441" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L441" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M441" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N441" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O441" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P441" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A442" s="20">
         <v>46488</v>
       </c>
+      <c r="J442" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K442" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L442" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M442" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N442" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O442" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P442" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A443" s="20">
         <v>46489</v>
       </c>
+      <c r="J443" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K443" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L443" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M443" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N443" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O443" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P443" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A444" s="20">
         <v>46490</v>
       </c>
+      <c r="J444" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K444" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L444" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M444" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N444" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O444" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P444" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A445" s="20">
         <v>46491</v>
       </c>
+      <c r="J445" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K445" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L445" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M445" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N445" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O445" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P445" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A446" s="20">
         <v>46492</v>
       </c>
+      <c r="J446" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K446" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L446" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M446" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N446" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O446" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P446" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A447" s="19">
         <v>46493</v>
       </c>
+      <c r="J447" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K447" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L447" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M447" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N447" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O447" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P447" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A448" s="19">
         <v>46494</v>
       </c>
+      <c r="J448" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K448" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L448" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M448" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N448" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O448" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P448" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A449" s="20">
         <v>46495</v>
       </c>
+      <c r="J449" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K449" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L449" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M449" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N449" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O449" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P449" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A450" s="20">
         <v>46496</v>
       </c>
+      <c r="J450" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K450" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L450" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M450" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N450" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O450" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P450" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A451" s="20">
         <v>46497</v>
       </c>
+      <c r="J451" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K451" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L451" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M451" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N451" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O451" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P451" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A452" s="20">
         <v>46498</v>
       </c>
+      <c r="J452" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K452" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L452" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M452" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N452" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O452" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P452" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A453" s="20">
         <v>46499</v>
       </c>
+      <c r="J453" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K453" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L453" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M453" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N453" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O453" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P453" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A454" s="19">
         <v>46500</v>
       </c>
+      <c r="J454" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K454" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L454" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M454" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N454" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O454" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P454" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A455" s="19">
         <v>46501</v>
       </c>
+      <c r="J455" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K455" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L455" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M455" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N455" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O455" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P455" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A456" s="20">
         <v>46502</v>
       </c>
+      <c r="J456" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K456" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L456" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M456" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N456" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O456" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P456" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A457" s="20">
         <v>46503</v>
       </c>
+      <c r="J457" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K457" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L457" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M457" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N457" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O457" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P457" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A458" s="20">
         <v>46504</v>
       </c>
+      <c r="J458" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K458" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L458" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M458" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N458" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O458" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P458" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A459" s="20">
         <v>46505</v>
       </c>
+      <c r="J459" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K459" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L459" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M459" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N459" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O459" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P459" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A460" s="20">
         <v>46506</v>
       </c>
+      <c r="J460" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K460" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L460" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M460" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N460" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O460" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P460" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A461" s="19">
         <v>46507</v>
       </c>
+      <c r="J461" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K461" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L461" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M461" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N461" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O461" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P461" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A462" s="19">
         <v>46508</v>
       </c>
+      <c r="J462" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K462" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L462" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M462" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N462" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O462" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P462" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A463" s="19">
         <v>46509</v>
       </c>
+      <c r="J463" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K463" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L463" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M463" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N463" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O463" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P463" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A464" s="19">
         <v>46510</v>
       </c>
+      <c r="J464" s="7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K464" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L464" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M464" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N464" s="7">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O464" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P464" s="2">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A465" s="19">
         <v>46511</v>
       </c>
+      <c r="J465" s="7">
+        <f t="shared" ref="J465:J520" si="35">$J$1*B465</f>
+        <v>0</v>
+      </c>
+      <c r="K465" s="7">
+        <f t="shared" ref="K465:K520" si="36">$K$1*C465</f>
+        <v>0</v>
+      </c>
+      <c r="L465" s="7">
+        <f t="shared" ref="L465:L520" si="37">$K$1*D465</f>
+        <v>0</v>
+      </c>
+      <c r="M465" s="7">
+        <f t="shared" ref="M465:M520" si="38">$M$1*E465</f>
+        <v>0</v>
+      </c>
+      <c r="N465" s="7">
+        <f t="shared" ref="N465:N520" si="39">$N$1*F465</f>
+        <v>0</v>
+      </c>
+      <c r="O465" s="7">
+        <f t="shared" ref="O465:O520" si="40">G465</f>
+        <v>0</v>
+      </c>
+      <c r="P465" s="2">
+        <f t="shared" ref="P465:P520" si="41">H465</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A466" s="20">
         <v>46512</v>
       </c>
+      <c r="B466" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C466" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D466" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E466" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F466" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G466" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H466" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J466" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K466" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L466" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M466" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N466" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O466" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P466" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A467" s="20">
         <v>46513</v>
       </c>
+      <c r="B467" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C467" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D467" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E467" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F467" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G467" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H467" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J467" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K467" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L467" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M467" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N467" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O467" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P467" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A468" s="20">
         <v>46514</v>
       </c>
+      <c r="B468" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C468" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D468" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E468" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F468" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G468" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H468" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J468" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K468" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L468" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M468" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N468" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O468" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P468" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A469" s="20">
         <v>46515</v>
       </c>
+      <c r="B469" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C469" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D469" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E469" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F469" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G469" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H469" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J469" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K469" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L469" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M469" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N469" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O469" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P469" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A470" s="20">
         <v>46516</v>
       </c>
+      <c r="B470" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C470" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D470" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E470" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F470" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G470" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H470" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J470" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K470" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L470" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M470" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N470" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O470" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P470" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A471" s="20">
         <v>46517</v>
       </c>
+      <c r="B471" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C471" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D471" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E471" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F471" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G471" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H471" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J471" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K471" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L471" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M471" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N471" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O471" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P471" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A472" s="20">
         <v>46518</v>
       </c>
+      <c r="B472" s="7">
+        <v>90000</v>
+      </c>
+      <c r="C472" s="7">
+        <v>110000</v>
+      </c>
+      <c r="D472" s="7">
+        <v>130000</v>
+      </c>
+      <c r="E472" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F472" s="7">
+        <v>150000</v>
+      </c>
+      <c r="G472" s="7">
+        <v>450000</v>
+      </c>
+      <c r="H472" s="7">
+        <v>650000</v>
+      </c>
+      <c r="J472" s="7">
+        <f t="shared" si="35"/>
+        <v>900000</v>
+      </c>
+      <c r="K472" s="7">
+        <f t="shared" si="36"/>
+        <v>330000</v>
+      </c>
+      <c r="L472" s="7">
+        <f t="shared" si="37"/>
+        <v>390000</v>
+      </c>
+      <c r="M472" s="7">
+        <f t="shared" si="38"/>
+        <v>700000</v>
+      </c>
+      <c r="N472" s="7">
+        <f t="shared" si="39"/>
+        <v>900000</v>
+      </c>
+      <c r="O472" s="7">
+        <f t="shared" si="40"/>
+        <v>450000</v>
+      </c>
+      <c r="P472" s="2">
+        <f t="shared" si="41"/>
+        <v>650000</v>
+      </c>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A473" s="19">
         <v>46519</v>
       </c>
+      <c r="B473" s="7">
+        <v>140000</v>
+      </c>
+      <c r="C473" s="7"/>
+      <c r="D473" s="7"/>
+      <c r="E473" s="7"/>
+      <c r="F473" s="7"/>
+      <c r="G473" s="7"/>
+      <c r="H473" s="7"/>
+      <c r="J473" s="7">
+        <f t="shared" si="35"/>
+        <v>1400000</v>
+      </c>
+      <c r="K473" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L473" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M473" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N473" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O473" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P473" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A474" s="19">
         <v>46520</v>
       </c>
+      <c r="B474" s="7">
+        <v>140000</v>
+      </c>
+      <c r="C474" s="7"/>
+      <c r="D474" s="7"/>
+      <c r="E474" s="7"/>
+      <c r="F474" s="7"/>
+      <c r="G474" s="7"/>
+      <c r="H474" s="7"/>
+      <c r="J474" s="7">
+        <f t="shared" si="35"/>
+        <v>1400000</v>
+      </c>
+      <c r="K474" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L474" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M474" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N474" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O474" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P474" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A475" s="19">
         <v>46521</v>
       </c>
+      <c r="B475" s="7">
+        <v>140000</v>
+      </c>
+      <c r="C475" s="7"/>
+      <c r="D475" s="7"/>
+      <c r="E475" s="7"/>
+      <c r="F475" s="7"/>
+      <c r="G475" s="7"/>
+      <c r="H475" s="7"/>
+      <c r="J475" s="7">
+        <f t="shared" si="35"/>
+        <v>1400000</v>
+      </c>
+      <c r="K475" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L475" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M475" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N475" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O475" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P475" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A476" s="19">
         <v>46522</v>
       </c>
+      <c r="B476" s="7">
+        <v>140000</v>
+      </c>
+      <c r="C476" s="7"/>
+      <c r="D476" s="7"/>
+      <c r="E476" s="7"/>
+      <c r="F476" s="7"/>
+      <c r="G476" s="7"/>
+      <c r="H476" s="7"/>
+      <c r="J476" s="7">
+        <f t="shared" si="35"/>
+        <v>1400000</v>
+      </c>
+      <c r="K476" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L476" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M476" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N476" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O476" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P476" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A477" s="20">
         <v>46523</v>
       </c>
+      <c r="B477" s="7"/>
+      <c r="C477" s="7"/>
+      <c r="D477" s="7"/>
+      <c r="E477" s="7"/>
+      <c r="F477" s="7"/>
+      <c r="G477" s="7"/>
+      <c r="H477" s="7"/>
+      <c r="J477" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K477" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L477" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M477" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N477" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O477" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P477" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A478" s="20">
         <v>46524</v>
       </c>
+      <c r="B478" s="7"/>
+      <c r="C478" s="7"/>
+      <c r="D478" s="7"/>
+      <c r="E478" s="7"/>
+      <c r="F478" s="7"/>
+      <c r="G478" s="7"/>
+      <c r="H478" s="7"/>
+      <c r="J478" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K478" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L478" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M478" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N478" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O478" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P478" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A479" s="20">
         <v>46525</v>
       </c>
+      <c r="J479" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K479" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L479" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M479" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N479" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O479" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P479" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A480" s="20">
         <v>46526</v>
       </c>
+      <c r="J480" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K480" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L480" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M480" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N480" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O480" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P480" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A481" s="20">
         <v>46527</v>
       </c>
+      <c r="J481" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K481" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L481" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M481" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N481" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O481" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P481" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A482" s="19">
         <v>46528</v>
       </c>
+      <c r="J482" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K482" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L482" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M482" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N482" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O482" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P482" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A483" s="19">
         <v>46529</v>
       </c>
+      <c r="J483" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K483" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L483" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M483" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N483" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O483" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P483" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A484" s="20">
         <v>46530</v>
       </c>
+      <c r="J484" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K484" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L484" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M484" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N484" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O484" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P484" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A485" s="20">
         <v>46531</v>
       </c>
+      <c r="J485" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K485" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L485" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M485" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N485" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O485" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P485" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A486" s="20">
         <v>46532</v>
       </c>
+      <c r="J486" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K486" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L486" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M486" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N486" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O486" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P486" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A487" s="20">
         <v>46533</v>
       </c>
+      <c r="J487" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K487" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L487" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M487" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N487" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O487" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P487" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A488" s="20">
         <v>46534</v>
       </c>
+      <c r="J488" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K488" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L488" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M488" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N488" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O488" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P488" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A489" s="19">
         <v>46535</v>
       </c>
+      <c r="J489" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K489" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L489" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M489" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N489" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O489" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P489" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A490" s="19">
         <v>46536</v>
       </c>
+      <c r="J490" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K490" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L490" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M490" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N490" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O490" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P490" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A491" s="20">
         <v>46537</v>
       </c>
+      <c r="J491" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K491" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L491" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M491" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N491" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O491" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P491" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A492" s="20">
         <v>46538</v>
       </c>
+      <c r="J492" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K492" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L492" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M492" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N492" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O492" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P492" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A493" s="20"/>
+      <c r="J493" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K493" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L493" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M493" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N493" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O493" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P493" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A494" s="20"/>
+      <c r="J494" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K494" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L494" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M494" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N494" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O494" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P494" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A495" s="20"/>
+      <c r="J495" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K495" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L495" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M495" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N495" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O495" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P495" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A496" s="20"/>
+      <c r="J496" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K496" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L496" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M496" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N496" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O496" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P496" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A497" s="20"/>
+      <c r="J497" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K497" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L497" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M497" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N497" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O497" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P497" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A498" s="20"/>
+      <c r="J498" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K498" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L498" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M498" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N498" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O498" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P498" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A499" s="20"/>
+      <c r="J499" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K499" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L499" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M499" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N499" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O499" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P499" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A500" s="20"/>
+      <c r="J500" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K500" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L500" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M500" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N500" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O500" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P500" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A501" s="20"/>
+      <c r="J501" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K501" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L501" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M501" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N501" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O501" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P501" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A502" s="20"/>
+      <c r="J502" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K502" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L502" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M502" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N502" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O502" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P502" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A503" s="20"/>
+      <c r="J503" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K503" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L503" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M503" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N503" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O503" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P503" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A504" s="20"/>
+      <c r="J504" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K504" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L504" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M504" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N504" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O504" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P504" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A505" s="20"/>
+      <c r="J505" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K505" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L505" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M505" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N505" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O505" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P505" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A506" s="20"/>
+      <c r="J506" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K506" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L506" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M506" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N506" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O506" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P506" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A507" s="20"/>
+      <c r="J507" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K507" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L507" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M507" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N507" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O507" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P507" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A508" s="20"/>
+      <c r="J508" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K508" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L508" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M508" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N508" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O508" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P508" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A509" s="20"/>
+      <c r="J509" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K509" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L509" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M509" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N509" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O509" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P509" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A510" s="20"/>
+      <c r="J510" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K510" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L510" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M510" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N510" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O510" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P510" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A511" s="20"/>
+      <c r="J511" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K511" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L511" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M511" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N511" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O511" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P511" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A512" s="20"/>
+      <c r="J512" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K512" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L512" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M512" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N512" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O512" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P512" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A513" s="20"/>
+      <c r="J513" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K513" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L513" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M513" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N513" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O513" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P513" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A514" s="20"/>
+      <c r="J514" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K514" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L514" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M514" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N514" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O514" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P514" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A515" s="20"/>
+      <c r="J515" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K515" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L515" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M515" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N515" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O515" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P515" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A516" s="20"/>
+      <c r="J516" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K516" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L516" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M516" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N516" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O516" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P516" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A517" s="20"/>
+      <c r="J517" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K517" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L517" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M517" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N517" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O517" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P517" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A518" s="20"/>
+      <c r="J518" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K518" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L518" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M518" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N518" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O518" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P518" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A519" s="20"/>
+      <c r="J519" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K519" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L519" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M519" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N519" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O519" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P519" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A520" s="20"/>
+      <c r="J520" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K520" s="7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L520" s="7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M520" s="7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N520" s="7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O520" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P520" s="2">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A521" s="20"/>
     </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A522" s="20"/>
     </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A523" s="20"/>
     </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A524" s="20"/>
     </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A525" s="20"/>
     </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A526" s="20"/>
     </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A527" s="20"/>
     </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A528" s="20"/>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.3">
@@ -50852,7 +56097,7 @@
       <c r="A555" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H346" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
